--- a/rss_islandr/templates/report_template.xlsx
+++ b/rss_islandr/templates/report_template.xlsx
@@ -397,7 +397,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
@@ -437,6 +437,9 @@
     <xf numFmtId="164" fontId="7" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -449,12 +452,12 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -464,8 +467,8 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -807,70 +810,70 @@
       <c r="O1" s="20"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="19"/>
+      <c r="B2" s="21"/>
       <c r="C2" s="3"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="19"/>
+      <c r="G2" s="21"/>
       <c r="H2" s="3"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="L2" s="23"/>
+      <c r="L2" s="24"/>
       <c r="M2" s="3"/>
       <c r="N2" s="1"/>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="15"/>
+      <c r="B3" s="16"/>
       <c r="C3" s="9"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="15"/>
+      <c r="G3" s="16"/>
       <c r="H3" s="3"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="L3" s="15"/>
+      <c r="L3" s="16"/>
       <c r="M3" s="9"/>
       <c r="N3" s="1"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="22"/>
+      <c r="G4" s="23"/>
       <c r="H4" s="3"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="22" t="s">
+      <c r="K4" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="L4" s="22"/>
+      <c r="L4" s="23"/>
       <c r="M4" s="9"/>
       <c r="N4" s="1"/>
       <c r="O4" s="2"/>
@@ -895,10 +898,10 @@
       <c r="O5" s="20"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="21"/>
+      <c r="B6" s="22"/>
       <c r="C6" s="4"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
@@ -914,10 +917,10 @@
       <c r="O6" s="2"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="21"/>
+      <c r="B7" s="22"/>
       <c r="C7" s="4"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -933,10 +936,10 @@
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="21"/>
+      <c r="B8" s="22"/>
       <c r="C8" s="4"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -952,11 +955,11 @@
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="5"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="25"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -990,182 +993,182 @@
       <c r="O10" s="20"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="16" t="s">
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="17"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="16" t="s">
+      <c r="E11" s="18"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="H11" s="17"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="16" t="s">
+      <c r="H11" s="18"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="K11" s="17"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="16" t="s">
+      <c r="K11" s="18"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="N11" s="17"/>
-      <c r="O11" s="18"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="19"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="19"/>
+      <c r="B12" s="21"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="19"/>
+      <c r="E12" s="21"/>
       <c r="F12" s="4"/>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="19"/>
+      <c r="H12" s="21"/>
       <c r="I12" s="4"/>
-      <c r="J12" s="19" t="s">
+      <c r="J12" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="K12" s="19"/>
+      <c r="K12" s="21"/>
       <c r="L12" s="4"/>
-      <c r="M12" s="19" t="s">
+      <c r="M12" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="N12" s="19"/>
+      <c r="N12" s="21"/>
       <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="15"/>
+      <c r="B13" s="16"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="15"/>
+      <c r="E13" s="16"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="15"/>
+      <c r="H13" s="16"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="15" t="s">
+      <c r="J13" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="K13" s="15"/>
+      <c r="K13" s="16"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="15" t="s">
+      <c r="M13" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="N13" s="15"/>
+      <c r="N13" s="16"/>
       <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="15"/>
+      <c r="B14" s="16"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="15"/>
+      <c r="E14" s="16"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="15"/>
+      <c r="H14" s="16"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="15" t="s">
+      <c r="J14" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="K14" s="15"/>
+      <c r="K14" s="16"/>
       <c r="L14" s="4"/>
-      <c r="M14" s="15" t="s">
+      <c r="M14" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="N14" s="15"/>
+      <c r="N14" s="16"/>
       <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="15"/>
+      <c r="B15" s="16"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="15"/>
+      <c r="E15" s="16"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="15" t="s">
+      <c r="J15" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="K15" s="15"/>
+      <c r="K15" s="16"/>
       <c r="L15" s="4"/>
-      <c r="M15" s="15" t="s">
+      <c r="M15" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="N15" s="15"/>
+      <c r="N15" s="16"/>
       <c r="O15" s="7"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="15"/>
+      <c r="B16" s="16"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
       <c r="I16" s="6"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
       <c r="L16" s="5"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
       <c r="O16" s="8"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="15"/>
+      <c r="B17" s="16"/>
       <c r="C17" s="12"/>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E17" s="15"/>
+      <c r="E17" s="16"/>
       <c r="F17" s="13"/>
-      <c r="G17" s="15" t="s">
+      <c r="G17" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H17" s="15"/>
+      <c r="H17" s="16"/>
       <c r="I17" s="13"/>
-      <c r="J17" s="15" t="s">
+      <c r="J17" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="K17" s="15"/>
+      <c r="K17" s="16"/>
       <c r="L17" s="13"/>
-      <c r="M17" s="15" t="s">
+      <c r="M17" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="N17" s="15"/>
+      <c r="N17" s="16"/>
       <c r="O17" s="14"/>
     </row>
     <row r="18" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
@@ -1188,120 +1191,176 @@
       <c r="O18" s="20"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="str">
+      <c r="A19" s="17" t="str">
         <f>A11</f>
         <v>Soil</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="16" t="str">
+      <c r="B19" s="18"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="17" t="str">
         <f t="shared" ref="D19" si="0">D11</f>
         <v>Ground water</v>
       </c>
-      <c r="E19" s="17"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="16" t="str">
+      <c r="E19" s="18"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="17" t="str">
         <f t="shared" ref="G19" si="1">G11</f>
         <v>Surface water</v>
       </c>
-      <c r="H19" s="17"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="16" t="str">
+      <c r="H19" s="18"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="17" t="str">
         <f t="shared" ref="J19" si="2">J11</f>
         <v>Air</v>
       </c>
-      <c r="K19" s="17"/>
-      <c r="L19" s="18"/>
-      <c r="M19" s="16" t="str">
+      <c r="K19" s="18"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="17" t="str">
         <f t="shared" ref="M19" si="3">M11</f>
         <v>Sediment</v>
       </c>
-      <c r="N19" s="17"/>
-      <c r="O19" s="18"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="19"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="19"/>
+      <c r="B20" s="21"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="19"/>
+      <c r="E20" s="21"/>
       <c r="F20" s="4"/>
-      <c r="G20" s="19" t="s">
+      <c r="G20" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="H20" s="19"/>
+      <c r="H20" s="21"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="19" t="s">
+      <c r="J20" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="K20" s="19"/>
+      <c r="K20" s="21"/>
       <c r="L20" s="4"/>
-      <c r="M20" s="19" t="s">
+      <c r="M20" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="N20" s="19"/>
+      <c r="N20" s="21"/>
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="15"/>
+      <c r="B21" s="16"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="E21" s="15"/>
+      <c r="E21" s="16"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="H21" s="15"/>
+      <c r="H21" s="16"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="15" t="s">
+      <c r="J21" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="K21" s="15"/>
+      <c r="K21" s="16"/>
       <c r="L21" s="4"/>
-      <c r="M21" s="15" t="s">
+      <c r="M21" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="N21" s="15"/>
+      <c r="N21" s="16"/>
       <c r="O21" s="7"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="15"/>
+      <c r="B22" s="16"/>
       <c r="C22" s="11"/>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="E22" s="15"/>
+      <c r="E22" s="16"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="15" t="s">
+      <c r="G22" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H22" s="15"/>
+      <c r="H22" s="16"/>
       <c r="I22" s="11"/>
-      <c r="J22" s="15" t="s">
+      <c r="J22" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="K22" s="15"/>
+      <c r="K22" s="16"/>
       <c r="L22" s="11"/>
-      <c r="M22" s="15" t="s">
+      <c r="M22" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="N22" s="15"/>
+      <c r="N22" s="16"/>
       <c r="O22" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="72">
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A5:O5"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="K4:L4"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="M11:O11"/>
@@ -1318,62 +1377,6 @@
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A5:O5"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="A18:O18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="M16:N16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/rss_islandr/templates/report_template.xlsx
+++ b/rss_islandr/templates/report_template.xlsx
@@ -397,7 +397,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
@@ -452,12 +452,12 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -466,9 +466,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -791,36 +788,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="21"/>
+      <c r="B2" s="20"/>
       <c r="C2" s="3"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="21"/>
+      <c r="G2" s="20"/>
       <c r="H2" s="3"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -879,23 +876,23 @@
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="21"/>
+      <c r="N5" s="21"/>
+      <c r="O5" s="21"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
@@ -959,7 +956,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="22"/>
-      <c r="C9" s="25"/>
+      <c r="C9" s="12"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -974,23 +971,23 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="20"/>
-      <c r="O10" s="20"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="21"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
@@ -1020,30 +1017,30 @@
       <c r="O11" s="19"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="21"/>
+      <c r="B12" s="20"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="21"/>
+      <c r="E12" s="20"/>
       <c r="F12" s="4"/>
-      <c r="G12" s="21" t="s">
+      <c r="G12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="21"/>
+      <c r="H12" s="20"/>
       <c r="I12" s="4"/>
-      <c r="J12" s="21" t="s">
+      <c r="J12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="K12" s="21"/>
+      <c r="K12" s="20"/>
       <c r="L12" s="4"/>
-      <c r="M12" s="21" t="s">
+      <c r="M12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="N12" s="21"/>
+      <c r="N12" s="20"/>
       <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -1172,23 +1169,23 @@
       <c r="O17" s="14"/>
     </row>
     <row r="18" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-      <c r="M18" s="20"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="20"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="21"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="str">
@@ -1223,30 +1220,30 @@
       <c r="O19" s="19"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="21"/>
+      <c r="B20" s="20"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="21" t="s">
+      <c r="D20" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="21"/>
+      <c r="E20" s="20"/>
       <c r="F20" s="4"/>
-      <c r="G20" s="21" t="s">
+      <c r="G20" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="H20" s="21"/>
+      <c r="H20" s="20"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="21" t="s">
+      <c r="J20" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="K20" s="21"/>
+      <c r="K20" s="20"/>
       <c r="L20" s="4"/>
-      <c r="M20" s="21" t="s">
+      <c r="M20" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="N20" s="21"/>
+      <c r="N20" s="20"/>
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -1305,16 +1302,52 @@
     </row>
   </sheetData>
   <mergeCells count="72">
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A5:O5"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="J17:K17"/>
     <mergeCell ref="A18:O18"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A20:B20"/>
@@ -1331,52 +1364,16 @@
     <mergeCell ref="M22:N22"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="G21:H21"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A5:O5"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="M16:N16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/rss_islandr/templates/report_template.xlsx
+++ b/rss_islandr/templates/report_template.xlsx
@@ -452,11 +452,11 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -777,47 +777,49 @@
   <dimension ref="A1:O22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.140625" customWidth="1"/>
+    <col min="1" max="2" width="10.7109375" customWidth="1"/>
     <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="5" width="10.7109375" customWidth="1"/>
     <col min="6" max="6" width="15.7109375" customWidth="1"/>
+    <col min="7" max="8" width="10.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" customWidth="1"/>
+    <col min="10" max="11" width="10.7109375" customWidth="1"/>
     <col min="12" max="12" width="15.7109375" customWidth="1"/>
-    <col min="14" max="14" width="10.28515625" customWidth="1"/>
+    <col min="13" max="14" width="10.7109375" customWidth="1"/>
     <col min="15" max="15" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="20"/>
+      <c r="B2" s="21"/>
       <c r="C2" s="3"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="21"/>
       <c r="H2" s="3"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -876,23 +878,23 @@
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="21"/>
-      <c r="N5" s="21"/>
-      <c r="O5" s="21"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
@@ -971,23 +973,23 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
-      <c r="O10" s="21"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
@@ -1017,30 +1019,30 @@
       <c r="O11" s="19"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="20"/>
+      <c r="B12" s="21"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="20"/>
+      <c r="E12" s="21"/>
       <c r="F12" s="4"/>
-      <c r="G12" s="20" t="s">
+      <c r="G12" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="20"/>
+      <c r="H12" s="21"/>
       <c r="I12" s="4"/>
-      <c r="J12" s="20" t="s">
+      <c r="J12" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="K12" s="20"/>
+      <c r="K12" s="21"/>
       <c r="L12" s="4"/>
-      <c r="M12" s="20" t="s">
+      <c r="M12" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="N12" s="20"/>
+      <c r="N12" s="21"/>
       <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -1169,23 +1171,23 @@
       <c r="O17" s="14"/>
     </row>
     <row r="18" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="21"/>
-      <c r="N18" s="21"/>
-      <c r="O18" s="21"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="str">
@@ -1220,30 +1222,30 @@
       <c r="O19" s="19"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="20"/>
+      <c r="B20" s="21"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="20" t="s">
+      <c r="D20" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="20"/>
+      <c r="E20" s="21"/>
       <c r="F20" s="4"/>
-      <c r="G20" s="20" t="s">
+      <c r="G20" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="H20" s="20"/>
+      <c r="H20" s="21"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="20" t="s">
+      <c r="J20" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="K20" s="20"/>
+      <c r="K20" s="21"/>
       <c r="L20" s="4"/>
-      <c r="M20" s="20" t="s">
+      <c r="M20" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="N20" s="20"/>
+      <c r="N20" s="21"/>
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -1302,6 +1304,62 @@
     </row>
   </sheetData>
   <mergeCells count="72">
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A5:O5"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="K4:L4"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="M11:O11"/>
@@ -1318,62 +1376,6 @@
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A5:O5"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="A18:O18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="M16:N16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/rss_islandr/templates/report_template.xlsx
+++ b/rss_islandr/templates/report_template.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="39">
   <si>
     <t>Soil</t>
   </si>
@@ -141,6 +141,9 @@
   </si>
   <si>
     <t>Coordinates (lat-lng)</t>
+  </si>
+  <si>
+    <t>Site Area [km²]</t>
   </si>
 </sst>
 </file>
@@ -397,7 +400,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
@@ -452,12 +455,12 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -465,6 +468,12 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -790,36 +799,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="21"/>
+      <c r="B2" s="20"/>
       <c r="C2" s="3"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="21"/>
+      <c r="G2" s="20"/>
       <c r="H2" s="3"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -877,47 +886,47 @@
       <c r="N4" s="1"/>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="26"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="2"/>
+    </row>
+    <row r="6" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="2"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="21"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="22"/>
       <c r="C7" s="4"/>
@@ -936,7 +945,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="22"/>
       <c r="C8" s="4"/>
@@ -973,23 +982,23 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="20"/>
-      <c r="O10" s="20"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="21"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
@@ -1019,30 +1028,30 @@
       <c r="O11" s="19"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="21"/>
+      <c r="B12" s="20"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="21"/>
+      <c r="E12" s="20"/>
       <c r="F12" s="4"/>
-      <c r="G12" s="21" t="s">
+      <c r="G12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="21"/>
+      <c r="H12" s="20"/>
       <c r="I12" s="4"/>
-      <c r="J12" s="21" t="s">
+      <c r="J12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="K12" s="21"/>
+      <c r="K12" s="20"/>
       <c r="L12" s="4"/>
-      <c r="M12" s="21" t="s">
+      <c r="M12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="N12" s="21"/>
+      <c r="N12" s="20"/>
       <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -1171,23 +1180,23 @@
       <c r="O17" s="14"/>
     </row>
     <row r="18" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-      <c r="M18" s="20"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="20"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="21"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="str">
@@ -1222,30 +1231,30 @@
       <c r="O19" s="19"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="21"/>
+      <c r="B20" s="20"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="21" t="s">
+      <c r="D20" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="21"/>
+      <c r="E20" s="20"/>
       <c r="F20" s="4"/>
-      <c r="G20" s="21" t="s">
+      <c r="G20" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="H20" s="21"/>
+      <c r="H20" s="20"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="21" t="s">
+      <c r="J20" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="K20" s="21"/>
+      <c r="K20" s="20"/>
       <c r="L20" s="4"/>
-      <c r="M20" s="21" t="s">
+      <c r="M20" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="N20" s="21"/>
+      <c r="N20" s="20"/>
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -1303,17 +1312,55 @@
       <c r="O22" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="72">
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J22:K22"/>
+  <mergeCells count="74">
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A6:O6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="J17:K17"/>
     <mergeCell ref="A18:O18"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A20:B20"/>
@@ -1330,52 +1377,16 @@
     <mergeCell ref="M22:N22"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="G21:H21"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A5:O5"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="M16:N16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/rss_islandr/templates/report_template.xlsx
+++ b/rss_islandr/templates/report_template.xlsx
@@ -4,10 +4,12 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11385"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11385" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="On-site on-site" sheetId="3" r:id="rId1"/>
+    <sheet name="On-site off-site" sheetId="2" r:id="rId2"/>
+    <sheet name="Off-site on-site" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="41">
   <si>
     <t>Soil</t>
   </si>
@@ -116,9 +118,6 @@
     <t>Source</t>
   </si>
   <si>
-    <t>Summary</t>
-  </si>
-  <si>
     <t>Assessment date</t>
   </si>
   <si>
@@ -144,6 +143,15 @@
   </si>
   <si>
     <t>Site Area [km²]</t>
+  </si>
+  <si>
+    <t>Summary (On-site to on-site contamination)</t>
+  </si>
+  <si>
+    <t>Summary (On-site to off-site contamination)</t>
+  </si>
+  <si>
+    <t>Summary (Off-site to on-site contamination)</t>
   </si>
 </sst>
 </file>
@@ -446,6 +454,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -455,25 +469,19 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -799,64 +807,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
+      <c r="A1" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="20"/>
+      <c r="B2" s="17"/>
       <c r="C2" s="3"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="20"/>
+      <c r="F2" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="17"/>
       <c r="H2" s="3"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2" s="24"/>
+      <c r="K2" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="26"/>
       <c r="M2" s="3"/>
       <c r="N2" s="1"/>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="9"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G3" s="16"/>
       <c r="H3" s="3"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L3" s="16"/>
       <c r="M3" s="9"/>
@@ -865,21 +873,21 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4" s="23"/>
       <c r="C4" s="15"/>
       <c r="D4" s="15"/>
       <c r="E4" s="1"/>
       <c r="F4" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G4" s="23"/>
       <c r="H4" s="3"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L4" s="23"/>
       <c r="M4" s="9"/>
@@ -887,42 +895,42 @@
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="26"/>
+      <c r="A5" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="25"/>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="26"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="25"/>
       <c r="H5" s="3"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="26"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="25"/>
       <c r="M5" s="9"/>
       <c r="N5" s="1"/>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
-      <c r="O6" s="21"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
@@ -982,76 +990,76 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
-      <c r="O10" s="21"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="17" t="s">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="18"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="17" t="s">
+      <c r="E11" s="20"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="H11" s="18"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="17" t="s">
+      <c r="H11" s="20"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="K11" s="18"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="17" t="s">
+      <c r="K11" s="20"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="N11" s="18"/>
-      <c r="O11" s="19"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="21"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="20"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="20"/>
+      <c r="E12" s="17"/>
       <c r="F12" s="4"/>
-      <c r="G12" s="20" t="s">
+      <c r="G12" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="20"/>
+      <c r="H12" s="17"/>
       <c r="I12" s="4"/>
-      <c r="J12" s="20" t="s">
+      <c r="J12" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="K12" s="20"/>
+      <c r="K12" s="17"/>
       <c r="L12" s="4"/>
-      <c r="M12" s="20" t="s">
+      <c r="M12" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="N12" s="20"/>
+      <c r="N12" s="17"/>
       <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -1180,81 +1188,81 @@
       <c r="O17" s="14"/>
     </row>
     <row r="18" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="21"/>
-      <c r="N18" s="21"/>
-      <c r="O18" s="21"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="18"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="str">
+      <c r="A19" s="19" t="str">
         <f>A11</f>
         <v>Soil</v>
       </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="17" t="str">
+      <c r="B19" s="20"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="19" t="str">
         <f t="shared" ref="D19" si="0">D11</f>
         <v>Ground water</v>
       </c>
-      <c r="E19" s="18"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="17" t="str">
+      <c r="E19" s="20"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="19" t="str">
         <f t="shared" ref="G19" si="1">G11</f>
         <v>Surface water</v>
       </c>
-      <c r="H19" s="18"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="17" t="str">
+      <c r="H19" s="20"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="19" t="str">
         <f t="shared" ref="J19" si="2">J11</f>
         <v>Air</v>
       </c>
-      <c r="K19" s="18"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="17" t="str">
+      <c r="K19" s="20"/>
+      <c r="L19" s="21"/>
+      <c r="M19" s="19" t="str">
         <f t="shared" ref="M19" si="3">M11</f>
         <v>Sediment</v>
       </c>
-      <c r="N19" s="18"/>
-      <c r="O19" s="19"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="21"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="20"/>
+      <c r="B20" s="17"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="20" t="s">
+      <c r="D20" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="20"/>
+      <c r="E20" s="17"/>
       <c r="F20" s="4"/>
-      <c r="G20" s="20" t="s">
+      <c r="G20" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="H20" s="20"/>
+      <c r="H20" s="17"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="20" t="s">
+      <c r="J20" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="K20" s="20"/>
+      <c r="K20" s="17"/>
       <c r="L20" s="4"/>
-      <c r="M20" s="20" t="s">
+      <c r="M20" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="N20" s="20"/>
+      <c r="N20" s="17"/>
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -1313,8 +1321,1230 @@
     </row>
   </sheetData>
   <mergeCells count="74">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="F5:G5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="A6:O6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="M22:N22"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="5" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" customWidth="1"/>
+    <col min="7" max="8" width="10.7109375" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" customWidth="1"/>
+    <col min="10" max="11" width="10.7109375" customWidth="1"/>
+    <col min="12" max="12" width="15.7109375" customWidth="1"/>
+    <col min="13" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="17"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="26"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="2"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="16"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="16"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="2"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="23"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="23"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="23"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="2"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="25"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="2"/>
+    </row>
+    <row r="6" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="22"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="22"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="2"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="22"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="2"/>
+    </row>
+    <row r="10" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="20"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="20"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="20"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="N11" s="20"/>
+      <c r="O11" s="21"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="17"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="17"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="H12" s="17"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="K12" s="17"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="N12" s="17"/>
+      <c r="O12" s="7"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="16"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="16"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="K13" s="16"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13" s="16"/>
+      <c r="O13" s="7"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="16"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="16"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="16"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" s="16"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="N14" s="16"/>
+      <c r="O14" s="7"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="16"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="K15" s="16"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="N15" s="16"/>
+      <c r="O15" s="7"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="16"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="8"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="16"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="16"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="H17" s="16"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="K17" s="16"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="N17" s="16"/>
+      <c r="O17" s="14"/>
+    </row>
+    <row r="18" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A18" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="18"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="19" t="str">
+        <f>A11</f>
+        <v>Soil</v>
+      </c>
+      <c r="B19" s="20"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="19" t="str">
+        <f t="shared" ref="D19" si="0">D11</f>
+        <v>Ground water</v>
+      </c>
+      <c r="E19" s="20"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="19" t="str">
+        <f t="shared" ref="G19" si="1">G11</f>
+        <v>Surface water</v>
+      </c>
+      <c r="H19" s="20"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="19" t="str">
+        <f t="shared" ref="J19" si="2">J11</f>
+        <v>Air</v>
+      </c>
+      <c r="K19" s="20"/>
+      <c r="L19" s="21"/>
+      <c r="M19" s="19" t="str">
+        <f t="shared" ref="M19" si="3">M11</f>
+        <v>Sediment</v>
+      </c>
+      <c r="N19" s="20"/>
+      <c r="O19" s="21"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="17"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="17"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="17"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="K20" s="17"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="N20" s="17"/>
+      <c r="O20" s="7"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="16"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="16"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="16"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="K21" s="16"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="N21" s="16"/>
+      <c r="O21" s="7"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="16"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="16"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="16"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="K22" s="16"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N22" s="16"/>
+      <c r="O22" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="74">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="K4:L4"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="A6:O6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="M22:N22"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="5" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" customWidth="1"/>
+    <col min="7" max="8" width="10.7109375" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" customWidth="1"/>
+    <col min="10" max="11" width="10.7109375" customWidth="1"/>
+    <col min="12" max="12" width="15.7109375" customWidth="1"/>
+    <col min="13" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="17"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="26"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="2"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="16"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="16"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="2"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="23"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="23"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="23"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="2"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="25"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="2"/>
+    </row>
+    <row r="6" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="22"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="22"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="2"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="22"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="2"/>
+    </row>
+    <row r="10" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="20"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="20"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="20"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="N11" s="20"/>
+      <c r="O11" s="21"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="17"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="17"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="H12" s="17"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="K12" s="17"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="N12" s="17"/>
+      <c r="O12" s="7"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="16"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="16"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="K13" s="16"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13" s="16"/>
+      <c r="O13" s="7"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="16"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="16"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="16"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" s="16"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="N14" s="16"/>
+      <c r="O14" s="7"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="16"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="K15" s="16"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="N15" s="16"/>
+      <c r="O15" s="7"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="16"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="8"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="16"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="16"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="H17" s="16"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="K17" s="16"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="N17" s="16"/>
+      <c r="O17" s="14"/>
+    </row>
+    <row r="18" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A18" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="18"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="19" t="str">
+        <f>A11</f>
+        <v>Soil</v>
+      </c>
+      <c r="B19" s="20"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="19" t="str">
+        <f t="shared" ref="D19" si="0">D11</f>
+        <v>Ground water</v>
+      </c>
+      <c r="E19" s="20"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="19" t="str">
+        <f t="shared" ref="G19" si="1">G11</f>
+        <v>Surface water</v>
+      </c>
+      <c r="H19" s="20"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="19" t="str">
+        <f t="shared" ref="J19" si="2">J11</f>
+        <v>Air</v>
+      </c>
+      <c r="K19" s="20"/>
+      <c r="L19" s="21"/>
+      <c r="M19" s="19" t="str">
+        <f t="shared" ref="M19" si="3">M11</f>
+        <v>Sediment</v>
+      </c>
+      <c r="N19" s="20"/>
+      <c r="O19" s="21"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="17"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="17"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="17"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="K20" s="17"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="N20" s="17"/>
+      <c r="O20" s="7"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="16"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="16"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="16"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="K21" s="16"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="N21" s="16"/>
+      <c r="O21" s="7"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="16"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="16"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="16"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="K22" s="16"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N22" s="16"/>
+      <c r="O22" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="74">
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="M11:O11"/>
@@ -1329,8 +2559,8 @@
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A6:O6"/>
     <mergeCell ref="A8:B8"/>
@@ -1345,35 +2575,35 @@
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
     <mergeCell ref="M12:N12"/>
     <mergeCell ref="M13:N13"/>
     <mergeCell ref="M14:N14"/>
     <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="K5:L5"/>
     <mergeCell ref="J12:K12"/>
     <mergeCell ref="J13:K13"/>
     <mergeCell ref="J14:K14"/>
     <mergeCell ref="J15:K15"/>
-    <mergeCell ref="J17:K17"/>
     <mergeCell ref="A18:O18"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A21:B21"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="M21:N21"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="D19:F19"/>
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="D22:E22"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="M21:N21"/>
     <mergeCell ref="M22:N22"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="G21:H21"/>
@@ -1382,11 +2612,13 @@
     <mergeCell ref="J20:K20"/>
     <mergeCell ref="J21:K21"/>
     <mergeCell ref="J22:K22"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="G15:H15"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="J16:K16"/>
     <mergeCell ref="M16:N16"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="D17:E17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/rss_islandr/templates/report_template.xlsx
+++ b/rss_islandr/templates/report_template.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11385" activeTab="2"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11385" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="On-site on-site" sheetId="3" r:id="rId1"/>
     <sheet name="On-site off-site" sheetId="2" r:id="rId2"/>
     <sheet name="Off-site on-site" sheetId="1" r:id="rId3"/>
+    <sheet name="pics" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -451,14 +452,26 @@
     <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -471,18 +484,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -807,23 +808,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
@@ -840,103 +841,103 @@
       <c r="H2" s="3"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="L2" s="26"/>
+      <c r="L2" s="18"/>
       <c r="M2" s="3"/>
       <c r="N2" s="1"/>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="16"/>
+      <c r="B3" s="19"/>
       <c r="C3" s="9"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="16"/>
+      <c r="G3" s="19"/>
       <c r="H3" s="3"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="16" t="s">
+      <c r="K3" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="16"/>
+      <c r="L3" s="19"/>
       <c r="M3" s="9"/>
       <c r="N3" s="1"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="23"/>
+      <c r="B4" s="20"/>
       <c r="C4" s="15"/>
       <c r="D4" s="15"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="23"/>
+      <c r="G4" s="20"/>
       <c r="H4" s="3"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="23" t="s">
+      <c r="K4" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="23"/>
+      <c r="L4" s="20"/>
       <c r="M4" s="9"/>
       <c r="N4" s="1"/>
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="25"/>
+      <c r="B5" s="22"/>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="25"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="22"/>
       <c r="H5" s="3"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="25"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="22"/>
       <c r="M5" s="9"/>
       <c r="N5" s="1"/>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="22"/>
+      <c r="B7" s="26"/>
       <c r="C7" s="4"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -952,10 +953,10 @@
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="22"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="4"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -971,10 +972,10 @@
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="22"/>
+      <c r="B9" s="26"/>
       <c r="C9" s="12"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -990,50 +991,50 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="18"/>
-      <c r="M10" s="18"/>
-      <c r="N10" s="18"/>
-      <c r="O10" s="18"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="19" t="s">
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="20"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="19" t="s">
+      <c r="E11" s="24"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H11" s="20"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="19" t="s">
+      <c r="H11" s="24"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="K11" s="20"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="19" t="s">
+      <c r="K11" s="24"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="N11" s="20"/>
-      <c r="O11" s="21"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="25"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
@@ -1063,180 +1064,180 @@
       <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="16"/>
+      <c r="B13" s="19"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="16"/>
+      <c r="E13" s="19"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="16"/>
+      <c r="H13" s="19"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="16" t="s">
+      <c r="J13" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="K13" s="16"/>
+      <c r="K13" s="19"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="16" t="s">
+      <c r="M13" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="N13" s="16"/>
+      <c r="N13" s="19"/>
       <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="16"/>
+      <c r="B14" s="19"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="16"/>
+      <c r="E14" s="19"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="16"/>
+      <c r="H14" s="19"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="16" t="s">
+      <c r="J14" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="K14" s="16"/>
+      <c r="K14" s="19"/>
       <c r="L14" s="4"/>
-      <c r="M14" s="16" t="s">
+      <c r="M14" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="N14" s="16"/>
+      <c r="N14" s="19"/>
       <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="16"/>
+      <c r="B15" s="19"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="16"/>
+      <c r="E15" s="19"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="16" t="s">
+      <c r="J15" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="K15" s="16"/>
+      <c r="K15" s="19"/>
       <c r="L15" s="4"/>
-      <c r="M15" s="16" t="s">
+      <c r="M15" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="N15" s="16"/>
+      <c r="N15" s="19"/>
       <c r="O15" s="7"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="16"/>
+      <c r="B16" s="19"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
       <c r="I16" s="6"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
       <c r="L16" s="5"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
       <c r="O16" s="8"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="16"/>
+      <c r="B17" s="19"/>
       <c r="C17" s="12"/>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="E17" s="16"/>
+      <c r="E17" s="19"/>
       <c r="F17" s="13"/>
-      <c r="G17" s="16" t="s">
+      <c r="G17" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="H17" s="16"/>
+      <c r="H17" s="19"/>
       <c r="I17" s="13"/>
-      <c r="J17" s="16" t="s">
+      <c r="J17" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="K17" s="16"/>
+      <c r="K17" s="19"/>
       <c r="L17" s="13"/>
-      <c r="M17" s="16" t="s">
+      <c r="M17" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="N17" s="16"/>
+      <c r="N17" s="19"/>
       <c r="O17" s="14"/>
     </row>
     <row r="18" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
-      <c r="M18" s="18"/>
-      <c r="N18" s="18"/>
-      <c r="O18" s="18"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="str">
+      <c r="A19" s="23" t="str">
         <f>A11</f>
         <v>Soil</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="19" t="str">
+      <c r="B19" s="24"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="23" t="str">
         <f t="shared" ref="D19" si="0">D11</f>
         <v>Ground water</v>
       </c>
-      <c r="E19" s="20"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="19" t="str">
+      <c r="E19" s="24"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="23" t="str">
         <f t="shared" ref="G19" si="1">G11</f>
         <v>Surface water</v>
       </c>
-      <c r="H19" s="20"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="19" t="str">
+      <c r="H19" s="24"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="23" t="str">
         <f t="shared" ref="J19" si="2">J11</f>
         <v>Air</v>
       </c>
-      <c r="K19" s="20"/>
-      <c r="L19" s="21"/>
-      <c r="M19" s="19" t="str">
+      <c r="K19" s="24"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="23" t="str">
         <f t="shared" ref="M19" si="3">M11</f>
         <v>Sediment</v>
       </c>
-      <c r="N19" s="20"/>
-      <c r="O19" s="21"/>
+      <c r="N19" s="24"/>
+      <c r="O19" s="25"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
@@ -1266,61 +1267,128 @@
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="16"/>
+      <c r="B21" s="19"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="E21" s="16"/>
+      <c r="E21" s="19"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="16" t="s">
+      <c r="G21" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="H21" s="16"/>
+      <c r="H21" s="19"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="16" t="s">
+      <c r="J21" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="K21" s="16"/>
+      <c r="K21" s="19"/>
       <c r="L21" s="4"/>
-      <c r="M21" s="16" t="s">
+      <c r="M21" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="N21" s="16"/>
+      <c r="N21" s="19"/>
       <c r="O21" s="7"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="16"/>
+      <c r="B22" s="19"/>
       <c r="C22" s="11"/>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="E22" s="16"/>
+      <c r="E22" s="19"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="16" t="s">
+      <c r="G22" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="H22" s="16"/>
+      <c r="H22" s="19"/>
       <c r="I22" s="11"/>
-      <c r="J22" s="16" t="s">
+      <c r="J22" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="K22" s="16"/>
+      <c r="K22" s="19"/>
       <c r="L22" s="11"/>
-      <c r="M22" s="16" t="s">
+      <c r="M22" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="N22" s="16"/>
+      <c r="N22" s="19"/>
       <c r="O22" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="74">
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="A6:O6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="K5:L5"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="F2:G2"/>
@@ -1328,73 +1396,6 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="K3:L3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="A6:O6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A18:O18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="M22:N22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -1419,23 +1420,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
@@ -1452,103 +1453,103 @@
       <c r="H2" s="3"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="L2" s="26"/>
+      <c r="L2" s="18"/>
       <c r="M2" s="3"/>
       <c r="N2" s="1"/>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="16"/>
+      <c r="B3" s="19"/>
       <c r="C3" s="9"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="16"/>
+      <c r="G3" s="19"/>
       <c r="H3" s="3"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="16" t="s">
+      <c r="K3" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="16"/>
+      <c r="L3" s="19"/>
       <c r="M3" s="9"/>
       <c r="N3" s="1"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="23"/>
+      <c r="B4" s="20"/>
       <c r="C4" s="15"/>
       <c r="D4" s="15"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="23"/>
+      <c r="G4" s="20"/>
       <c r="H4" s="3"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="23" t="s">
+      <c r="K4" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="23"/>
+      <c r="L4" s="20"/>
       <c r="M4" s="9"/>
       <c r="N4" s="1"/>
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="25"/>
+      <c r="B5" s="22"/>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="25"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="22"/>
       <c r="H5" s="3"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="25"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="22"/>
       <c r="M5" s="9"/>
       <c r="N5" s="1"/>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="22"/>
+      <c r="B7" s="26"/>
       <c r="C7" s="4"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -1564,10 +1565,10 @@
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="22"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="4"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -1583,10 +1584,10 @@
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="22"/>
+      <c r="B9" s="26"/>
       <c r="C9" s="12"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -1602,50 +1603,50 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="18"/>
-      <c r="M10" s="18"/>
-      <c r="N10" s="18"/>
-      <c r="O10" s="18"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="19" t="s">
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="20"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="19" t="s">
+      <c r="E11" s="24"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H11" s="20"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="19" t="s">
+      <c r="H11" s="24"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="K11" s="20"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="19" t="s">
+      <c r="K11" s="24"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="N11" s="20"/>
-      <c r="O11" s="21"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="25"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
@@ -1675,180 +1676,180 @@
       <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="16"/>
+      <c r="B13" s="19"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="16"/>
+      <c r="E13" s="19"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="16"/>
+      <c r="H13" s="19"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="16" t="s">
+      <c r="J13" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="K13" s="16"/>
+      <c r="K13" s="19"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="16" t="s">
+      <c r="M13" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="N13" s="16"/>
+      <c r="N13" s="19"/>
       <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="16"/>
+      <c r="B14" s="19"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="16"/>
+      <c r="E14" s="19"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="16"/>
+      <c r="H14" s="19"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="16" t="s">
+      <c r="J14" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="K14" s="16"/>
+      <c r="K14" s="19"/>
       <c r="L14" s="4"/>
-      <c r="M14" s="16" t="s">
+      <c r="M14" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="N14" s="16"/>
+      <c r="N14" s="19"/>
       <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="16"/>
+      <c r="B15" s="19"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="16"/>
+      <c r="E15" s="19"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="16" t="s">
+      <c r="J15" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="K15" s="16"/>
+      <c r="K15" s="19"/>
       <c r="L15" s="4"/>
-      <c r="M15" s="16" t="s">
+      <c r="M15" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="N15" s="16"/>
+      <c r="N15" s="19"/>
       <c r="O15" s="7"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="16"/>
+      <c r="B16" s="19"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
       <c r="I16" s="6"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
       <c r="L16" s="5"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
       <c r="O16" s="8"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="16"/>
+      <c r="B17" s="19"/>
       <c r="C17" s="12"/>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="E17" s="16"/>
+      <c r="E17" s="19"/>
       <c r="F17" s="13"/>
-      <c r="G17" s="16" t="s">
+      <c r="G17" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="H17" s="16"/>
+      <c r="H17" s="19"/>
       <c r="I17" s="13"/>
-      <c r="J17" s="16" t="s">
+      <c r="J17" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="K17" s="16"/>
+      <c r="K17" s="19"/>
       <c r="L17" s="13"/>
-      <c r="M17" s="16" t="s">
+      <c r="M17" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="N17" s="16"/>
+      <c r="N17" s="19"/>
       <c r="O17" s="14"/>
     </row>
     <row r="18" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
-      <c r="M18" s="18"/>
-      <c r="N18" s="18"/>
-      <c r="O18" s="18"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="str">
+      <c r="A19" s="23" t="str">
         <f>A11</f>
         <v>Soil</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="19" t="str">
+      <c r="B19" s="24"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="23" t="str">
         <f t="shared" ref="D19" si="0">D11</f>
         <v>Ground water</v>
       </c>
-      <c r="E19" s="20"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="19" t="str">
+      <c r="E19" s="24"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="23" t="str">
         <f t="shared" ref="G19" si="1">G11</f>
         <v>Surface water</v>
       </c>
-      <c r="H19" s="20"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="19" t="str">
+      <c r="H19" s="24"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="23" t="str">
         <f t="shared" ref="J19" si="2">J11</f>
         <v>Air</v>
       </c>
-      <c r="K19" s="20"/>
-      <c r="L19" s="21"/>
-      <c r="M19" s="19" t="str">
+      <c r="K19" s="24"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="23" t="str">
         <f t="shared" ref="M19" si="3">M11</f>
         <v>Sediment</v>
       </c>
-      <c r="N19" s="20"/>
-      <c r="O19" s="21"/>
+      <c r="N19" s="24"/>
+      <c r="O19" s="25"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
@@ -1878,61 +1879,128 @@
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="16"/>
+      <c r="B21" s="19"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="E21" s="16"/>
+      <c r="E21" s="19"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="16" t="s">
+      <c r="G21" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="H21" s="16"/>
+      <c r="H21" s="19"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="16" t="s">
+      <c r="J21" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="K21" s="16"/>
+      <c r="K21" s="19"/>
       <c r="L21" s="4"/>
-      <c r="M21" s="16" t="s">
+      <c r="M21" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="N21" s="16"/>
+      <c r="N21" s="19"/>
       <c r="O21" s="7"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="16"/>
+      <c r="B22" s="19"/>
       <c r="C22" s="11"/>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="E22" s="16"/>
+      <c r="E22" s="19"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="16" t="s">
+      <c r="G22" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="H22" s="16"/>
+      <c r="H22" s="19"/>
       <c r="I22" s="11"/>
-      <c r="J22" s="16" t="s">
+      <c r="J22" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="K22" s="16"/>
+      <c r="K22" s="19"/>
       <c r="L22" s="11"/>
-      <c r="M22" s="16" t="s">
+      <c r="M22" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="N22" s="16"/>
+      <c r="N22" s="19"/>
       <c r="O22" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="74">
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="A6:O6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="K5:L5"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="F2:G2"/>
@@ -1940,73 +2008,6 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="K3:L3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="A6:O6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A18:O18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="M22:N22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -2031,23 +2032,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
@@ -2064,103 +2065,103 @@
       <c r="H2" s="3"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="L2" s="26"/>
+      <c r="L2" s="18"/>
       <c r="M2" s="3"/>
       <c r="N2" s="1"/>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="16"/>
+      <c r="B3" s="19"/>
       <c r="C3" s="9"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="16"/>
+      <c r="G3" s="19"/>
       <c r="H3" s="3"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="16" t="s">
+      <c r="K3" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="16"/>
+      <c r="L3" s="19"/>
       <c r="M3" s="9"/>
       <c r="N3" s="1"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="23"/>
+      <c r="B4" s="20"/>
       <c r="C4" s="15"/>
       <c r="D4" s="15"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="23"/>
+      <c r="G4" s="20"/>
       <c r="H4" s="3"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="23" t="s">
+      <c r="K4" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="23"/>
+      <c r="L4" s="20"/>
       <c r="M4" s="9"/>
       <c r="N4" s="1"/>
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="25"/>
+      <c r="B5" s="22"/>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="25"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="22"/>
       <c r="H5" s="3"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="25"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="22"/>
       <c r="M5" s="9"/>
       <c r="N5" s="1"/>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="22"/>
+      <c r="B7" s="26"/>
       <c r="C7" s="4"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -2176,10 +2177,10 @@
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="22"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="4"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -2195,10 +2196,10 @@
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="22"/>
+      <c r="B9" s="26"/>
       <c r="C9" s="12"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -2214,50 +2215,50 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="18"/>
-      <c r="M10" s="18"/>
-      <c r="N10" s="18"/>
-      <c r="O10" s="18"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="19" t="s">
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="20"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="19" t="s">
+      <c r="E11" s="24"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H11" s="20"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="19" t="s">
+      <c r="H11" s="24"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="K11" s="20"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="19" t="s">
+      <c r="K11" s="24"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="N11" s="20"/>
-      <c r="O11" s="21"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="25"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
@@ -2287,180 +2288,180 @@
       <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="16"/>
+      <c r="B13" s="19"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="16"/>
+      <c r="E13" s="19"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="16"/>
+      <c r="H13" s="19"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="16" t="s">
+      <c r="J13" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="K13" s="16"/>
+      <c r="K13" s="19"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="16" t="s">
+      <c r="M13" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="N13" s="16"/>
+      <c r="N13" s="19"/>
       <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="16"/>
+      <c r="B14" s="19"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="16"/>
+      <c r="E14" s="19"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="16"/>
+      <c r="H14" s="19"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="16" t="s">
+      <c r="J14" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="K14" s="16"/>
+      <c r="K14" s="19"/>
       <c r="L14" s="4"/>
-      <c r="M14" s="16" t="s">
+      <c r="M14" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="N14" s="16"/>
+      <c r="N14" s="19"/>
       <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="16"/>
+      <c r="B15" s="19"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="16"/>
+      <c r="E15" s="19"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="16" t="s">
+      <c r="J15" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="K15" s="16"/>
+      <c r="K15" s="19"/>
       <c r="L15" s="4"/>
-      <c r="M15" s="16" t="s">
+      <c r="M15" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="N15" s="16"/>
+      <c r="N15" s="19"/>
       <c r="O15" s="7"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="16"/>
+      <c r="B16" s="19"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
       <c r="I16" s="6"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
       <c r="L16" s="5"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
       <c r="O16" s="8"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="16"/>
+      <c r="B17" s="19"/>
       <c r="C17" s="12"/>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="E17" s="16"/>
+      <c r="E17" s="19"/>
       <c r="F17" s="13"/>
-      <c r="G17" s="16" t="s">
+      <c r="G17" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="H17" s="16"/>
+      <c r="H17" s="19"/>
       <c r="I17" s="13"/>
-      <c r="J17" s="16" t="s">
+      <c r="J17" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="K17" s="16"/>
+      <c r="K17" s="19"/>
       <c r="L17" s="13"/>
-      <c r="M17" s="16" t="s">
+      <c r="M17" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="N17" s="16"/>
+      <c r="N17" s="19"/>
       <c r="O17" s="14"/>
     </row>
     <row r="18" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
-      <c r="M18" s="18"/>
-      <c r="N18" s="18"/>
-      <c r="O18" s="18"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="str">
+      <c r="A19" s="23" t="str">
         <f>A11</f>
         <v>Soil</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="19" t="str">
+      <c r="B19" s="24"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="23" t="str">
         <f t="shared" ref="D19" si="0">D11</f>
         <v>Ground water</v>
       </c>
-      <c r="E19" s="20"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="19" t="str">
+      <c r="E19" s="24"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="23" t="str">
         <f t="shared" ref="G19" si="1">G11</f>
         <v>Surface water</v>
       </c>
-      <c r="H19" s="20"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="19" t="str">
+      <c r="H19" s="24"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="23" t="str">
         <f t="shared" ref="J19" si="2">J11</f>
         <v>Air</v>
       </c>
-      <c r="K19" s="20"/>
-      <c r="L19" s="21"/>
-      <c r="M19" s="19" t="str">
+      <c r="K19" s="24"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="23" t="str">
         <f t="shared" ref="M19" si="3">M11</f>
         <v>Sediment</v>
       </c>
-      <c r="N19" s="20"/>
-      <c r="O19" s="21"/>
+      <c r="N19" s="24"/>
+      <c r="O19" s="25"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
@@ -2490,61 +2491,119 @@
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="16"/>
+      <c r="B21" s="19"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="E21" s="16"/>
+      <c r="E21" s="19"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="16" t="s">
+      <c r="G21" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="H21" s="16"/>
+      <c r="H21" s="19"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="16" t="s">
+      <c r="J21" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="K21" s="16"/>
+      <c r="K21" s="19"/>
       <c r="L21" s="4"/>
-      <c r="M21" s="16" t="s">
+      <c r="M21" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="N21" s="16"/>
+      <c r="N21" s="19"/>
       <c r="O21" s="7"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="16"/>
+      <c r="B22" s="19"/>
       <c r="C22" s="11"/>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="E22" s="16"/>
+      <c r="E22" s="19"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="16" t="s">
+      <c r="G22" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="H22" s="16"/>
+      <c r="H22" s="19"/>
       <c r="I22" s="11"/>
-      <c r="J22" s="16" t="s">
+      <c r="J22" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="K22" s="16"/>
+      <c r="K22" s="19"/>
       <c r="L22" s="11"/>
-      <c r="M22" s="16" t="s">
+      <c r="M22" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="N22" s="16"/>
+      <c r="N22" s="19"/>
       <c r="O22" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="74">
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A6:O6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="M11:O11"/>
@@ -2561,66 +2620,17 @@
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="D13:E13"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A6:O6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="A18:O18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="D17:E17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/rss_islandr/templates/report_template.xlsx
+++ b/rss_islandr/templates/report_template.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11385"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11385" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="On-site on-site" sheetId="3" r:id="rId1"/>
     <sheet name="On-site off-site" sheetId="2" r:id="rId2"/>
     <sheet name="Off-site on-site" sheetId="1" r:id="rId3"/>
-    <sheet name="pics" sheetId="4" r:id="rId4"/>
+    <sheet name="Maps" sheetId="4" r:id="rId4"/>
+    <sheet name="Coordinates" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="47">
   <si>
     <t>Soil</t>
   </si>
@@ -157,11 +158,30 @@
   <si>
     <t>Total Risk [%]</t>
   </si>
+  <si>
+    <t>Longitude</t>
+  </si>
+  <si>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>Area [km^2]</t>
+  </si>
+  <si>
+    <t>A/A</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+  </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -218,14 +238,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="4" tint="-0.249977111117893"/>
+      <color theme="3"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="161"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -260,8 +282,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -374,26 +402,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -402,14 +410,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
@@ -437,10 +459,15 @@
     <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" xfId="4" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="3" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -449,45 +476,38 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="4" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="4" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Calculation" xfId="3" builtinId="22"/>
+    <cellStyle name="Heading 4" xfId="4" builtinId="19"/>
     <cellStyle name="Input" xfId="2" builtinId="20"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Title" xfId="1" builtinId="15"/>
@@ -808,136 +828,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="12"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="3"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="12"/>
+      <c r="G2" s="15"/>
       <c r="H2" s="3"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="21"/>
+      <c r="L2" s="24"/>
       <c r="M2" s="3"/>
       <c r="N2" s="1"/>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="11"/>
+      <c r="B3" s="14"/>
       <c r="C3" s="9"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="11"/>
+      <c r="G3" s="14"/>
       <c r="H3" s="3"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="11"/>
+      <c r="L3" s="14"/>
       <c r="M3" s="9"/>
       <c r="N3" s="1"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="18"/>
+      <c r="G4" s="21"/>
       <c r="H4" s="3"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="18" t="s">
+      <c r="K4" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="18"/>
+      <c r="L4" s="21"/>
       <c r="M4" s="9"/>
       <c r="N4" s="1"/>
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="20"/>
+      <c r="B5" s="23"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="20"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="23"/>
       <c r="H5" s="3"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="20"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="23"/>
       <c r="M5" s="9"/>
       <c r="N5" s="1"/>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="17"/>
+      <c r="B7" s="20"/>
       <c r="C7" s="4"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -953,10 +973,10 @@
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="17"/>
+      <c r="B8" s="20"/>
       <c r="C8" s="4"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -972,11 +992,11 @@
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="22"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="13"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -991,334 +1011,334 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="14" t="s">
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="15"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="14" t="s">
+      <c r="E11" s="18"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="H11" s="15"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="14" t="s">
+      <c r="H11" s="18"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="15"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="14" t="s">
+      <c r="K11" s="18"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="N11" s="15"/>
-      <c r="O11" s="16"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="19"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="12"/>
+      <c r="B12" s="15"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="12"/>
+      <c r="E12" s="15"/>
       <c r="F12" s="4"/>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="12"/>
+      <c r="H12" s="15"/>
       <c r="I12" s="4"/>
-      <c r="J12" s="12" t="s">
+      <c r="J12" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="K12" s="12"/>
+      <c r="K12" s="15"/>
       <c r="L12" s="4"/>
-      <c r="M12" s="12" t="s">
+      <c r="M12" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="N12" s="12"/>
+      <c r="N12" s="15"/>
       <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="11"/>
+      <c r="B13" s="14"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="11"/>
+      <c r="E13" s="14"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="11"/>
+      <c r="H13" s="14"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="11" t="s">
+      <c r="J13" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="K13" s="11"/>
+      <c r="K13" s="14"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="11" t="s">
+      <c r="M13" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="N13" s="11"/>
+      <c r="N13" s="14"/>
       <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="11"/>
+      <c r="B14" s="14"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="11"/>
+      <c r="E14" s="14"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="11"/>
+      <c r="H14" s="14"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="11"/>
+      <c r="K14" s="14"/>
       <c r="L14" s="4"/>
-      <c r="M14" s="11" t="s">
+      <c r="M14" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="11"/>
+      <c r="N14" s="14"/>
       <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="11"/>
+      <c r="B15" s="14"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="11"/>
+      <c r="E15" s="14"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="11" t="s">
+      <c r="J15" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="11"/>
+      <c r="K15" s="14"/>
       <c r="L15" s="4"/>
-      <c r="M15" s="11" t="s">
+      <c r="M15" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="N15" s="11"/>
+      <c r="N15" s="14"/>
       <c r="O15" s="7"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="11"/>
+      <c r="B16" s="14"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
       <c r="I16" s="6"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
       <c r="L16" s="5"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
       <c r="O16" s="8"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="11" t="s">
+      <c r="B17" s="14"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="11"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="11" t="s">
+      <c r="E17" s="14"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="11"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="11" t="s">
+      <c r="H17" s="14"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="K17" s="11"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="11" t="s">
+      <c r="K17" s="14"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="N17" s="11"/>
-      <c r="O17" s="24"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="13"/>
     </row>
     <row r="18" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="str">
+      <c r="A19" s="17" t="str">
         <f>A11</f>
         <v>Soil</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="14" t="str">
+      <c r="B19" s="18"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="17" t="str">
         <f t="shared" ref="D19" si="0">D11</f>
         <v>Ground water</v>
       </c>
-      <c r="E19" s="15"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="14" t="str">
+      <c r="E19" s="18"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="17" t="str">
         <f t="shared" ref="G19" si="1">G11</f>
         <v>Surface water</v>
       </c>
-      <c r="H19" s="15"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="14" t="str">
+      <c r="H19" s="18"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="17" t="str">
         <f t="shared" ref="J19" si="2">J11</f>
         <v>Air</v>
       </c>
-      <c r="K19" s="15"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="14" t="str">
+      <c r="K19" s="18"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="17" t="str">
         <f t="shared" ref="M19" si="3">M11</f>
         <v>Sediment</v>
       </c>
-      <c r="N19" s="15"/>
-      <c r="O19" s="16"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="19"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="12"/>
+      <c r="B20" s="15"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E20" s="12"/>
+      <c r="E20" s="15"/>
       <c r="F20" s="4"/>
-      <c r="G20" s="12" t="s">
+      <c r="G20" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="H20" s="12"/>
+      <c r="H20" s="15"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="12" t="s">
+      <c r="J20" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K20" s="12"/>
+      <c r="K20" s="15"/>
       <c r="L20" s="4"/>
-      <c r="M20" s="12" t="s">
+      <c r="M20" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="N20" s="12"/>
+      <c r="N20" s="15"/>
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="11"/>
+      <c r="B21" s="14"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="11"/>
+      <c r="E21" s="14"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="11" t="s">
+      <c r="G21" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="11"/>
+      <c r="H21" s="14"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="11" t="s">
+      <c r="J21" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="11"/>
+      <c r="K21" s="14"/>
       <c r="L21" s="4"/>
-      <c r="M21" s="11" t="s">
+      <c r="M21" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="N21" s="11"/>
+      <c r="N21" s="14"/>
       <c r="O21" s="7"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="11" t="s">
+      <c r="B22" s="14"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="11"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="11" t="s">
+      <c r="E22" s="14"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="H22" s="11"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="11" t="s">
+      <c r="H22" s="14"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="26"/>
-      <c r="M22" s="11" t="s">
+      <c r="K22" s="14"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="N22" s="11"/>
-      <c r="O22" s="25"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="74">
@@ -1420,136 +1440,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="12"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="3"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="12"/>
+      <c r="G2" s="15"/>
       <c r="H2" s="3"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="21"/>
+      <c r="L2" s="24"/>
       <c r="M2" s="3"/>
       <c r="N2" s="1"/>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="11"/>
+      <c r="B3" s="14"/>
       <c r="C3" s="9"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="11"/>
+      <c r="G3" s="14"/>
       <c r="H3" s="3"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="11"/>
+      <c r="L3" s="14"/>
       <c r="M3" s="9"/>
       <c r="N3" s="1"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="18"/>
+      <c r="G4" s="21"/>
       <c r="H4" s="3"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="18" t="s">
+      <c r="K4" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="18"/>
+      <c r="L4" s="21"/>
       <c r="M4" s="9"/>
       <c r="N4" s="1"/>
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="20"/>
+      <c r="B5" s="23"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="20"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="23"/>
       <c r="H5" s="3"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="20"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="23"/>
       <c r="M5" s="9"/>
       <c r="N5" s="1"/>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="17"/>
+      <c r="B7" s="20"/>
       <c r="C7" s="4"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -1565,10 +1585,10 @@
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="17"/>
+      <c r="B8" s="20"/>
       <c r="C8" s="4"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -1584,11 +1604,11 @@
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="22"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="13"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -1603,334 +1623,334 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="14" t="s">
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="15"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="14" t="s">
+      <c r="E11" s="18"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="H11" s="15"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="14" t="s">
+      <c r="H11" s="18"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="15"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="14" t="s">
+      <c r="K11" s="18"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="N11" s="15"/>
-      <c r="O11" s="16"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="19"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="12"/>
+      <c r="B12" s="15"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="12"/>
+      <c r="E12" s="15"/>
       <c r="F12" s="4"/>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="12"/>
+      <c r="H12" s="15"/>
       <c r="I12" s="4"/>
-      <c r="J12" s="12" t="s">
+      <c r="J12" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="K12" s="12"/>
+      <c r="K12" s="15"/>
       <c r="L12" s="4"/>
-      <c r="M12" s="12" t="s">
+      <c r="M12" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="N12" s="12"/>
+      <c r="N12" s="15"/>
       <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="11"/>
+      <c r="B13" s="14"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="11"/>
+      <c r="E13" s="14"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="11"/>
+      <c r="H13" s="14"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="11" t="s">
+      <c r="J13" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="K13" s="11"/>
+      <c r="K13" s="14"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="11" t="s">
+      <c r="M13" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="N13" s="11"/>
+      <c r="N13" s="14"/>
       <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="11"/>
+      <c r="B14" s="14"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="11"/>
+      <c r="E14" s="14"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="11"/>
+      <c r="H14" s="14"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="11"/>
+      <c r="K14" s="14"/>
       <c r="L14" s="4"/>
-      <c r="M14" s="11" t="s">
+      <c r="M14" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="11"/>
+      <c r="N14" s="14"/>
       <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="11"/>
+      <c r="B15" s="14"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="11"/>
+      <c r="E15" s="14"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="11" t="s">
+      <c r="J15" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="11"/>
+      <c r="K15" s="14"/>
       <c r="L15" s="4"/>
-      <c r="M15" s="11" t="s">
+      <c r="M15" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="N15" s="11"/>
+      <c r="N15" s="14"/>
       <c r="O15" s="7"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="11"/>
+      <c r="B16" s="14"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
       <c r="I16" s="6"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
       <c r="L16" s="5"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
       <c r="O16" s="8"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="11" t="s">
+      <c r="B17" s="14"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="11"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="11" t="s">
+      <c r="E17" s="14"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="11"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="11" t="s">
+      <c r="H17" s="14"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="K17" s="11"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="11" t="s">
+      <c r="K17" s="14"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="N17" s="11"/>
-      <c r="O17" s="24"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="13"/>
     </row>
     <row r="18" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="str">
+      <c r="A19" s="17" t="str">
         <f>A11</f>
         <v>Soil</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="14" t="str">
+      <c r="B19" s="18"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="17" t="str">
         <f t="shared" ref="D19" si="0">D11</f>
         <v>Ground water</v>
       </c>
-      <c r="E19" s="15"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="14" t="str">
+      <c r="E19" s="18"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="17" t="str">
         <f t="shared" ref="G19" si="1">G11</f>
         <v>Surface water</v>
       </c>
-      <c r="H19" s="15"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="14" t="str">
+      <c r="H19" s="18"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="17" t="str">
         <f t="shared" ref="J19" si="2">J11</f>
         <v>Air</v>
       </c>
-      <c r="K19" s="15"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="14" t="str">
+      <c r="K19" s="18"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="17" t="str">
         <f t="shared" ref="M19" si="3">M11</f>
         <v>Sediment</v>
       </c>
-      <c r="N19" s="15"/>
-      <c r="O19" s="16"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="19"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="12"/>
+      <c r="B20" s="15"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E20" s="12"/>
+      <c r="E20" s="15"/>
       <c r="F20" s="4"/>
-      <c r="G20" s="12" t="s">
+      <c r="G20" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="H20" s="12"/>
+      <c r="H20" s="15"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="12" t="s">
+      <c r="J20" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K20" s="12"/>
+      <c r="K20" s="15"/>
       <c r="L20" s="4"/>
-      <c r="M20" s="12" t="s">
+      <c r="M20" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="N20" s="12"/>
+      <c r="N20" s="15"/>
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="11"/>
+      <c r="B21" s="14"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="11"/>
+      <c r="E21" s="14"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="11" t="s">
+      <c r="G21" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="11"/>
+      <c r="H21" s="14"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="11" t="s">
+      <c r="J21" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="11"/>
+      <c r="K21" s="14"/>
       <c r="L21" s="4"/>
-      <c r="M21" s="11" t="s">
+      <c r="M21" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="N21" s="11"/>
+      <c r="N21" s="14"/>
       <c r="O21" s="7"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="11" t="s">
+      <c r="B22" s="14"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="11"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="11" t="s">
+      <c r="E22" s="14"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="H22" s="11"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="11" t="s">
+      <c r="H22" s="14"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="26"/>
-      <c r="M22" s="11" t="s">
+      <c r="K22" s="14"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="N22" s="11"/>
-      <c r="O22" s="25"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="74">
@@ -2032,136 +2052,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="12"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="3"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="12"/>
+      <c r="G2" s="15"/>
       <c r="H2" s="3"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="21"/>
+      <c r="L2" s="24"/>
       <c r="M2" s="3"/>
       <c r="N2" s="1"/>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="11"/>
+      <c r="B3" s="14"/>
       <c r="C3" s="9"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="11"/>
+      <c r="G3" s="14"/>
       <c r="H3" s="3"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="11"/>
+      <c r="L3" s="14"/>
       <c r="M3" s="9"/>
       <c r="N3" s="1"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="18"/>
+      <c r="G4" s="21"/>
       <c r="H4" s="3"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="18" t="s">
+      <c r="K4" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="18"/>
+      <c r="L4" s="21"/>
       <c r="M4" s="9"/>
       <c r="N4" s="1"/>
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="20"/>
+      <c r="B5" s="23"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="20"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="23"/>
       <c r="H5" s="3"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="20"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="23"/>
       <c r="M5" s="9"/>
       <c r="N5" s="1"/>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="17"/>
+      <c r="B7" s="20"/>
       <c r="C7" s="4"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -2177,10 +2197,10 @@
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="17"/>
+      <c r="B8" s="20"/>
       <c r="C8" s="4"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -2196,11 +2216,11 @@
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="22"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="13"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -2215,334 +2235,334 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="14" t="s">
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="15"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="14" t="s">
+      <c r="E11" s="18"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="H11" s="15"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="14" t="s">
+      <c r="H11" s="18"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="15"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="14" t="s">
+      <c r="K11" s="18"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="N11" s="15"/>
-      <c r="O11" s="16"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="19"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="12"/>
+      <c r="B12" s="15"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="12"/>
+      <c r="E12" s="15"/>
       <c r="F12" s="4"/>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="12"/>
+      <c r="H12" s="15"/>
       <c r="I12" s="4"/>
-      <c r="J12" s="12" t="s">
+      <c r="J12" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="K12" s="12"/>
+      <c r="K12" s="15"/>
       <c r="L12" s="4"/>
-      <c r="M12" s="12" t="s">
+      <c r="M12" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="N12" s="12"/>
+      <c r="N12" s="15"/>
       <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="11"/>
+      <c r="B13" s="14"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="11"/>
+      <c r="E13" s="14"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="11"/>
+      <c r="H13" s="14"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="11" t="s">
+      <c r="J13" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="K13" s="11"/>
+      <c r="K13" s="14"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="11" t="s">
+      <c r="M13" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="N13" s="11"/>
+      <c r="N13" s="14"/>
       <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="11"/>
+      <c r="B14" s="14"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="11"/>
+      <c r="E14" s="14"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="11"/>
+      <c r="H14" s="14"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="11"/>
+      <c r="K14" s="14"/>
       <c r="L14" s="4"/>
-      <c r="M14" s="11" t="s">
+      <c r="M14" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="11"/>
+      <c r="N14" s="14"/>
       <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="11"/>
+      <c r="B15" s="14"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="11"/>
+      <c r="E15" s="14"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="11" t="s">
+      <c r="J15" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="11"/>
+      <c r="K15" s="14"/>
       <c r="L15" s="4"/>
-      <c r="M15" s="11" t="s">
+      <c r="M15" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="N15" s="11"/>
+      <c r="N15" s="14"/>
       <c r="O15" s="7"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="11"/>
+      <c r="B16" s="14"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
       <c r="I16" s="6"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
       <c r="L16" s="5"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
       <c r="O16" s="8"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="11" t="s">
+      <c r="B17" s="14"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="11"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="11" t="s">
+      <c r="E17" s="14"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="11"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="11" t="s">
+      <c r="H17" s="14"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="K17" s="11"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="11" t="s">
+      <c r="K17" s="14"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="N17" s="11"/>
-      <c r="O17" s="24"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="13"/>
     </row>
     <row r="18" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="str">
+      <c r="A19" s="17" t="str">
         <f>A11</f>
         <v>Soil</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="14" t="str">
+      <c r="B19" s="18"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="17" t="str">
         <f t="shared" ref="D19" si="0">D11</f>
         <v>Ground water</v>
       </c>
-      <c r="E19" s="15"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="14" t="str">
+      <c r="E19" s="18"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="17" t="str">
         <f t="shared" ref="G19" si="1">G11</f>
         <v>Surface water</v>
       </c>
-      <c r="H19" s="15"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="14" t="str">
+      <c r="H19" s="18"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="17" t="str">
         <f t="shared" ref="J19" si="2">J11</f>
         <v>Air</v>
       </c>
-      <c r="K19" s="15"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="14" t="str">
+      <c r="K19" s="18"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="17" t="str">
         <f t="shared" ref="M19" si="3">M11</f>
         <v>Sediment</v>
       </c>
-      <c r="N19" s="15"/>
-      <c r="O19" s="16"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="19"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="12"/>
+      <c r="B20" s="15"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E20" s="12"/>
+      <c r="E20" s="15"/>
       <c r="F20" s="4"/>
-      <c r="G20" s="12" t="s">
+      <c r="G20" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="H20" s="12"/>
+      <c r="H20" s="15"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="12" t="s">
+      <c r="J20" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="K20" s="12"/>
+      <c r="K20" s="15"/>
       <c r="L20" s="4"/>
-      <c r="M20" s="12" t="s">
+      <c r="M20" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="N20" s="12"/>
+      <c r="N20" s="15"/>
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="11"/>
+      <c r="B21" s="14"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="11"/>
+      <c r="E21" s="14"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="11" t="s">
+      <c r="G21" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="11"/>
+      <c r="H21" s="14"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="11" t="s">
+      <c r="J21" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="11"/>
+      <c r="K21" s="14"/>
       <c r="L21" s="4"/>
-      <c r="M21" s="11" t="s">
+      <c r="M21" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="N21" s="11"/>
+      <c r="N21" s="14"/>
       <c r="O21" s="7"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="11" t="s">
+      <c r="B22" s="14"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="11"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="11" t="s">
+      <c r="E22" s="14"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="H22" s="11"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="11" t="s">
+      <c r="H22" s="14"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="26"/>
-      <c r="M22" s="11" t="s">
+      <c r="K22" s="14"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="N22" s="11"/>
-      <c r="O22" s="25"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="74">
@@ -2633,4 +2653,2831 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E400"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" customWidth="1"/>
+    <col min="2" max="2" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" style="29" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="28"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="28"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="28"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="28"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="28"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="28"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="28"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="28"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="28"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="28"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="28"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="28"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="28"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="28"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="28"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="28"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="28"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="28"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="28"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="28"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="28"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="28"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="28"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="28"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="28"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="28"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="28"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="28"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="28"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="28"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="28"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="28"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="28"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="28"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="11"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="28"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="11"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="28"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="11"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="28"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="11"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="28"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="11"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="28"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="11"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="28"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="11"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="28"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="11"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="28"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="11"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="28"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="11"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="28"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="11"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="28"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="11"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="28"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="11"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="28"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="11"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="26"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="28"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="11"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="26"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="28"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="11"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="26"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="28"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="11"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="26"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="28"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="11"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="26"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="28"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="11"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="28"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="11"/>
+      <c r="B55" s="11"/>
+      <c r="C55" s="26"/>
+      <c r="D55" s="26"/>
+      <c r="E55" s="28"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="11"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="26"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="28"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="11"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="28"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="11"/>
+      <c r="B58" s="11"/>
+      <c r="C58" s="26"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="28"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="11"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="26"/>
+      <c r="D59" s="26"/>
+      <c r="E59" s="28"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="11"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="28"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="11"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="28"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="11"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="28"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="11"/>
+      <c r="B63" s="11"/>
+      <c r="C63" s="26"/>
+      <c r="D63" s="26"/>
+      <c r="E63" s="28"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="11"/>
+      <c r="B64" s="11"/>
+      <c r="C64" s="26"/>
+      <c r="D64" s="26"/>
+      <c r="E64" s="28"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="11"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="26"/>
+      <c r="D65" s="26"/>
+      <c r="E65" s="28"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="11"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="26"/>
+      <c r="D66" s="26"/>
+      <c r="E66" s="28"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="11"/>
+      <c r="B67" s="11"/>
+      <c r="C67" s="26"/>
+      <c r="D67" s="26"/>
+      <c r="E67" s="28"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="11"/>
+      <c r="B68" s="11"/>
+      <c r="C68" s="26"/>
+      <c r="D68" s="26"/>
+      <c r="E68" s="28"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="11"/>
+      <c r="B69" s="11"/>
+      <c r="C69" s="26"/>
+      <c r="D69" s="26"/>
+      <c r="E69" s="28"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="11"/>
+      <c r="B70" s="11"/>
+      <c r="C70" s="26"/>
+      <c r="D70" s="26"/>
+      <c r="E70" s="28"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="11"/>
+      <c r="B71" s="11"/>
+      <c r="C71" s="26"/>
+      <c r="D71" s="26"/>
+      <c r="E71" s="28"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="11"/>
+      <c r="B72" s="11"/>
+      <c r="C72" s="26"/>
+      <c r="D72" s="26"/>
+      <c r="E72" s="28"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="11"/>
+      <c r="B73" s="11"/>
+      <c r="C73" s="26"/>
+      <c r="D73" s="26"/>
+      <c r="E73" s="28"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="11"/>
+      <c r="B74" s="11"/>
+      <c r="C74" s="26"/>
+      <c r="D74" s="26"/>
+      <c r="E74" s="28"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="11"/>
+      <c r="B75" s="11"/>
+      <c r="C75" s="26"/>
+      <c r="D75" s="26"/>
+      <c r="E75" s="28"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="11"/>
+      <c r="B76" s="11"/>
+      <c r="C76" s="26"/>
+      <c r="D76" s="26"/>
+      <c r="E76" s="28"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="11"/>
+      <c r="B77" s="11"/>
+      <c r="C77" s="26"/>
+      <c r="D77" s="26"/>
+      <c r="E77" s="28"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="11"/>
+      <c r="B78" s="11"/>
+      <c r="C78" s="26"/>
+      <c r="D78" s="26"/>
+      <c r="E78" s="28"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="11"/>
+      <c r="B79" s="11"/>
+      <c r="C79" s="26"/>
+      <c r="D79" s="26"/>
+      <c r="E79" s="28"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="11"/>
+      <c r="B80" s="11"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="28"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="11"/>
+      <c r="B81" s="11"/>
+      <c r="C81" s="26"/>
+      <c r="D81" s="26"/>
+      <c r="E81" s="28"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="11"/>
+      <c r="B82" s="11"/>
+      <c r="C82" s="26"/>
+      <c r="D82" s="26"/>
+      <c r="E82" s="28"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="11"/>
+      <c r="B83" s="11"/>
+      <c r="C83" s="26"/>
+      <c r="D83" s="26"/>
+      <c r="E83" s="28"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="11"/>
+      <c r="B84" s="11"/>
+      <c r="C84" s="26"/>
+      <c r="D84" s="26"/>
+      <c r="E84" s="28"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="11"/>
+      <c r="B85" s="11"/>
+      <c r="C85" s="26"/>
+      <c r="D85" s="26"/>
+      <c r="E85" s="28"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="11"/>
+      <c r="B86" s="11"/>
+      <c r="C86" s="26"/>
+      <c r="D86" s="26"/>
+      <c r="E86" s="28"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="11"/>
+      <c r="B87" s="11"/>
+      <c r="C87" s="26"/>
+      <c r="D87" s="26"/>
+      <c r="E87" s="28"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="11"/>
+      <c r="B88" s="11"/>
+      <c r="C88" s="26"/>
+      <c r="D88" s="26"/>
+      <c r="E88" s="28"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="11"/>
+      <c r="B89" s="11"/>
+      <c r="C89" s="26"/>
+      <c r="D89" s="26"/>
+      <c r="E89" s="28"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="11"/>
+      <c r="B90" s="11"/>
+      <c r="C90" s="26"/>
+      <c r="D90" s="26"/>
+      <c r="E90" s="28"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="11"/>
+      <c r="B91" s="11"/>
+      <c r="C91" s="26"/>
+      <c r="D91" s="26"/>
+      <c r="E91" s="28"/>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="11"/>
+      <c r="B92" s="11"/>
+      <c r="C92" s="26"/>
+      <c r="D92" s="26"/>
+      <c r="E92" s="28"/>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="11"/>
+      <c r="B93" s="11"/>
+      <c r="C93" s="26"/>
+      <c r="D93" s="26"/>
+      <c r="E93" s="28"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="11"/>
+      <c r="B94" s="11"/>
+      <c r="C94" s="26"/>
+      <c r="D94" s="26"/>
+      <c r="E94" s="28"/>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="11"/>
+      <c r="B95" s="11"/>
+      <c r="C95" s="26"/>
+      <c r="D95" s="26"/>
+      <c r="E95" s="28"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="11"/>
+      <c r="B96" s="11"/>
+      <c r="C96" s="26"/>
+      <c r="D96" s="26"/>
+      <c r="E96" s="28"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="11"/>
+      <c r="B97" s="11"/>
+      <c r="C97" s="26"/>
+      <c r="D97" s="26"/>
+      <c r="E97" s="28"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="11"/>
+      <c r="B98" s="11"/>
+      <c r="C98" s="26"/>
+      <c r="D98" s="26"/>
+      <c r="E98" s="28"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="11"/>
+      <c r="B99" s="11"/>
+      <c r="C99" s="26"/>
+      <c r="D99" s="26"/>
+      <c r="E99" s="28"/>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="11"/>
+      <c r="B100" s="11"/>
+      <c r="C100" s="26"/>
+      <c r="D100" s="26"/>
+      <c r="E100" s="28"/>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="11"/>
+      <c r="B101" s="11"/>
+      <c r="C101" s="26"/>
+      <c r="D101" s="26"/>
+      <c r="E101" s="28"/>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="11"/>
+      <c r="B102" s="11"/>
+      <c r="C102" s="26"/>
+      <c r="D102" s="26"/>
+      <c r="E102" s="28"/>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="11"/>
+      <c r="B103" s="11"/>
+      <c r="C103" s="26"/>
+      <c r="D103" s="26"/>
+      <c r="E103" s="28"/>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="11"/>
+      <c r="B104" s="11"/>
+      <c r="C104" s="26"/>
+      <c r="D104" s="26"/>
+      <c r="E104" s="28"/>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="11"/>
+      <c r="B105" s="11"/>
+      <c r="C105" s="26"/>
+      <c r="D105" s="26"/>
+      <c r="E105" s="28"/>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="11"/>
+      <c r="B106" s="11"/>
+      <c r="C106" s="26"/>
+      <c r="D106" s="26"/>
+      <c r="E106" s="28"/>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="11"/>
+      <c r="B107" s="11"/>
+      <c r="C107" s="26"/>
+      <c r="D107" s="26"/>
+      <c r="E107" s="28"/>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="11"/>
+      <c r="B108" s="11"/>
+      <c r="C108" s="26"/>
+      <c r="D108" s="26"/>
+      <c r="E108" s="28"/>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="11"/>
+      <c r="B109" s="11"/>
+      <c r="C109" s="26"/>
+      <c r="D109" s="26"/>
+      <c r="E109" s="28"/>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="11"/>
+      <c r="B110" s="11"/>
+      <c r="C110" s="26"/>
+      <c r="D110" s="26"/>
+      <c r="E110" s="28"/>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="11"/>
+      <c r="B111" s="11"/>
+      <c r="C111" s="26"/>
+      <c r="D111" s="26"/>
+      <c r="E111" s="28"/>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="11"/>
+      <c r="B112" s="11"/>
+      <c r="C112" s="26"/>
+      <c r="D112" s="26"/>
+      <c r="E112" s="28"/>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="11"/>
+      <c r="B113" s="11"/>
+      <c r="C113" s="26"/>
+      <c r="D113" s="26"/>
+      <c r="E113" s="28"/>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="11"/>
+      <c r="B114" s="11"/>
+      <c r="C114" s="26"/>
+      <c r="D114" s="26"/>
+      <c r="E114" s="28"/>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="11"/>
+      <c r="B115" s="11"/>
+      <c r="C115" s="26"/>
+      <c r="D115" s="26"/>
+      <c r="E115" s="28"/>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="11"/>
+      <c r="B116" s="11"/>
+      <c r="C116" s="26"/>
+      <c r="D116" s="26"/>
+      <c r="E116" s="28"/>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="11"/>
+      <c r="B117" s="11"/>
+      <c r="C117" s="26"/>
+      <c r="D117" s="26"/>
+      <c r="E117" s="28"/>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="11"/>
+      <c r="B118" s="11"/>
+      <c r="C118" s="26"/>
+      <c r="D118" s="26"/>
+      <c r="E118" s="28"/>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="11"/>
+      <c r="B119" s="11"/>
+      <c r="C119" s="26"/>
+      <c r="D119" s="26"/>
+      <c r="E119" s="28"/>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="11"/>
+      <c r="B120" s="11"/>
+      <c r="C120" s="26"/>
+      <c r="D120" s="26"/>
+      <c r="E120" s="28"/>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="11"/>
+      <c r="B121" s="11"/>
+      <c r="C121" s="26"/>
+      <c r="D121" s="26"/>
+      <c r="E121" s="28"/>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="11"/>
+      <c r="B122" s="11"/>
+      <c r="C122" s="26"/>
+      <c r="D122" s="26"/>
+      <c r="E122" s="28"/>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="11"/>
+      <c r="B123" s="11"/>
+      <c r="C123" s="26"/>
+      <c r="D123" s="26"/>
+      <c r="E123" s="28"/>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="11"/>
+      <c r="B124" s="11"/>
+      <c r="C124" s="26"/>
+      <c r="D124" s="26"/>
+      <c r="E124" s="28"/>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="11"/>
+      <c r="B125" s="11"/>
+      <c r="C125" s="26"/>
+      <c r="D125" s="26"/>
+      <c r="E125" s="28"/>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="11"/>
+      <c r="B126" s="11"/>
+      <c r="C126" s="26"/>
+      <c r="D126" s="26"/>
+      <c r="E126" s="28"/>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="11"/>
+      <c r="B127" s="11"/>
+      <c r="C127" s="26"/>
+      <c r="D127" s="26"/>
+      <c r="E127" s="28"/>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="11"/>
+      <c r="B128" s="11"/>
+      <c r="C128" s="26"/>
+      <c r="D128" s="26"/>
+      <c r="E128" s="28"/>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="11"/>
+      <c r="B129" s="11"/>
+      <c r="C129" s="26"/>
+      <c r="D129" s="26"/>
+      <c r="E129" s="28"/>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="11"/>
+      <c r="B130" s="11"/>
+      <c r="C130" s="26"/>
+      <c r="D130" s="26"/>
+      <c r="E130" s="28"/>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="11"/>
+      <c r="B131" s="11"/>
+      <c r="C131" s="26"/>
+      <c r="D131" s="26"/>
+      <c r="E131" s="28"/>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="11"/>
+      <c r="B132" s="11"/>
+      <c r="C132" s="26"/>
+      <c r="D132" s="26"/>
+      <c r="E132" s="28"/>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="11"/>
+      <c r="B133" s="11"/>
+      <c r="C133" s="26"/>
+      <c r="D133" s="26"/>
+      <c r="E133" s="28"/>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="11"/>
+      <c r="B134" s="11"/>
+      <c r="C134" s="26"/>
+      <c r="D134" s="26"/>
+      <c r="E134" s="28"/>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" s="11"/>
+      <c r="B135" s="11"/>
+      <c r="C135" s="26"/>
+      <c r="D135" s="26"/>
+      <c r="E135" s="28"/>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="11"/>
+      <c r="B136" s="11"/>
+      <c r="C136" s="26"/>
+      <c r="D136" s="26"/>
+      <c r="E136" s="28"/>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="11"/>
+      <c r="B137" s="11"/>
+      <c r="C137" s="26"/>
+      <c r="D137" s="26"/>
+      <c r="E137" s="28"/>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="11"/>
+      <c r="B138" s="11"/>
+      <c r="C138" s="26"/>
+      <c r="D138" s="26"/>
+      <c r="E138" s="28"/>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="11"/>
+      <c r="B139" s="11"/>
+      <c r="C139" s="26"/>
+      <c r="D139" s="26"/>
+      <c r="E139" s="28"/>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="11"/>
+      <c r="B140" s="11"/>
+      <c r="C140" s="26"/>
+      <c r="D140" s="26"/>
+      <c r="E140" s="28"/>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" s="11"/>
+      <c r="B141" s="11"/>
+      <c r="C141" s="26"/>
+      <c r="D141" s="26"/>
+      <c r="E141" s="28"/>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="11"/>
+      <c r="B142" s="11"/>
+      <c r="C142" s="26"/>
+      <c r="D142" s="26"/>
+      <c r="E142" s="28"/>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="11"/>
+      <c r="B143" s="11"/>
+      <c r="C143" s="26"/>
+      <c r="D143" s="26"/>
+      <c r="E143" s="28"/>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" s="11"/>
+      <c r="B144" s="11"/>
+      <c r="C144" s="26"/>
+      <c r="D144" s="26"/>
+      <c r="E144" s="28"/>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" s="11"/>
+      <c r="B145" s="11"/>
+      <c r="C145" s="26"/>
+      <c r="D145" s="26"/>
+      <c r="E145" s="28"/>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" s="11"/>
+      <c r="B146" s="11"/>
+      <c r="C146" s="26"/>
+      <c r="D146" s="26"/>
+      <c r="E146" s="28"/>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" s="11"/>
+      <c r="B147" s="11"/>
+      <c r="C147" s="26"/>
+      <c r="D147" s="26"/>
+      <c r="E147" s="28"/>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" s="11"/>
+      <c r="B148" s="11"/>
+      <c r="C148" s="26"/>
+      <c r="D148" s="26"/>
+      <c r="E148" s="28"/>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" s="11"/>
+      <c r="B149" s="11"/>
+      <c r="C149" s="26"/>
+      <c r="D149" s="26"/>
+      <c r="E149" s="28"/>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" s="11"/>
+      <c r="B150" s="11"/>
+      <c r="C150" s="26"/>
+      <c r="D150" s="26"/>
+      <c r="E150" s="28"/>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" s="11"/>
+      <c r="B151" s="11"/>
+      <c r="C151" s="26"/>
+      <c r="D151" s="26"/>
+      <c r="E151" s="28"/>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" s="11"/>
+      <c r="B152" s="11"/>
+      <c r="C152" s="26"/>
+      <c r="D152" s="26"/>
+      <c r="E152" s="28"/>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" s="11"/>
+      <c r="B153" s="11"/>
+      <c r="C153" s="26"/>
+      <c r="D153" s="26"/>
+      <c r="E153" s="28"/>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" s="11"/>
+      <c r="B154" s="11"/>
+      <c r="C154" s="26"/>
+      <c r="D154" s="26"/>
+      <c r="E154" s="28"/>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" s="11"/>
+      <c r="B155" s="11"/>
+      <c r="C155" s="26"/>
+      <c r="D155" s="26"/>
+      <c r="E155" s="28"/>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" s="11"/>
+      <c r="B156" s="11"/>
+      <c r="C156" s="26"/>
+      <c r="D156" s="26"/>
+      <c r="E156" s="28"/>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" s="11"/>
+      <c r="B157" s="11"/>
+      <c r="C157" s="26"/>
+      <c r="D157" s="26"/>
+      <c r="E157" s="28"/>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" s="11"/>
+      <c r="B158" s="11"/>
+      <c r="C158" s="26"/>
+      <c r="D158" s="26"/>
+      <c r="E158" s="28"/>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" s="11"/>
+      <c r="B159" s="11"/>
+      <c r="C159" s="26"/>
+      <c r="D159" s="26"/>
+      <c r="E159" s="28"/>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" s="11"/>
+      <c r="B160" s="11"/>
+      <c r="C160" s="26"/>
+      <c r="D160" s="26"/>
+      <c r="E160" s="28"/>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" s="11"/>
+      <c r="B161" s="11"/>
+      <c r="C161" s="26"/>
+      <c r="D161" s="26"/>
+      <c r="E161" s="28"/>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" s="11"/>
+      <c r="B162" s="11"/>
+      <c r="C162" s="26"/>
+      <c r="D162" s="26"/>
+      <c r="E162" s="28"/>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" s="11"/>
+      <c r="B163" s="11"/>
+      <c r="C163" s="26"/>
+      <c r="D163" s="26"/>
+      <c r="E163" s="28"/>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" s="11"/>
+      <c r="B164" s="11"/>
+      <c r="C164" s="26"/>
+      <c r="D164" s="26"/>
+      <c r="E164" s="28"/>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" s="11"/>
+      <c r="B165" s="11"/>
+      <c r="C165" s="26"/>
+      <c r="D165" s="26"/>
+      <c r="E165" s="28"/>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" s="11"/>
+      <c r="B166" s="11"/>
+      <c r="C166" s="26"/>
+      <c r="D166" s="26"/>
+      <c r="E166" s="28"/>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" s="11"/>
+      <c r="B167" s="11"/>
+      <c r="C167" s="26"/>
+      <c r="D167" s="26"/>
+      <c r="E167" s="28"/>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" s="11"/>
+      <c r="B168" s="11"/>
+      <c r="C168" s="26"/>
+      <c r="D168" s="26"/>
+      <c r="E168" s="28"/>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" s="11"/>
+      <c r="B169" s="11"/>
+      <c r="C169" s="26"/>
+      <c r="D169" s="26"/>
+      <c r="E169" s="28"/>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" s="11"/>
+      <c r="B170" s="11"/>
+      <c r="C170" s="26"/>
+      <c r="D170" s="26"/>
+      <c r="E170" s="28"/>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" s="11"/>
+      <c r="B171" s="11"/>
+      <c r="C171" s="26"/>
+      <c r="D171" s="26"/>
+      <c r="E171" s="28"/>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" s="11"/>
+      <c r="B172" s="11"/>
+      <c r="C172" s="26"/>
+      <c r="D172" s="26"/>
+      <c r="E172" s="28"/>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" s="11"/>
+      <c r="B173" s="11"/>
+      <c r="C173" s="26"/>
+      <c r="D173" s="26"/>
+      <c r="E173" s="28"/>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" s="11"/>
+      <c r="B174" s="11"/>
+      <c r="C174" s="26"/>
+      <c r="D174" s="26"/>
+      <c r="E174" s="28"/>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" s="11"/>
+      <c r="B175" s="11"/>
+      <c r="C175" s="26"/>
+      <c r="D175" s="26"/>
+      <c r="E175" s="28"/>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" s="11"/>
+      <c r="B176" s="11"/>
+      <c r="C176" s="26"/>
+      <c r="D176" s="26"/>
+      <c r="E176" s="28"/>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" s="11"/>
+      <c r="B177" s="11"/>
+      <c r="C177" s="26"/>
+      <c r="D177" s="26"/>
+      <c r="E177" s="28"/>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" s="11"/>
+      <c r="B178" s="11"/>
+      <c r="C178" s="26"/>
+      <c r="D178" s="26"/>
+      <c r="E178" s="28"/>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" s="11"/>
+      <c r="B179" s="11"/>
+      <c r="C179" s="26"/>
+      <c r="D179" s="26"/>
+      <c r="E179" s="28"/>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" s="11"/>
+      <c r="B180" s="11"/>
+      <c r="C180" s="26"/>
+      <c r="D180" s="26"/>
+      <c r="E180" s="28"/>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" s="11"/>
+      <c r="B181" s="11"/>
+      <c r="C181" s="26"/>
+      <c r="D181" s="26"/>
+      <c r="E181" s="28"/>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" s="11"/>
+      <c r="B182" s="11"/>
+      <c r="C182" s="26"/>
+      <c r="D182" s="26"/>
+      <c r="E182" s="28"/>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" s="11"/>
+      <c r="B183" s="11"/>
+      <c r="C183" s="26"/>
+      <c r="D183" s="26"/>
+      <c r="E183" s="28"/>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" s="11"/>
+      <c r="B184" s="11"/>
+      <c r="C184" s="26"/>
+      <c r="D184" s="26"/>
+      <c r="E184" s="28"/>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" s="11"/>
+      <c r="B185" s="11"/>
+      <c r="C185" s="26"/>
+      <c r="D185" s="26"/>
+      <c r="E185" s="28"/>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" s="11"/>
+      <c r="B186" s="11"/>
+      <c r="C186" s="26"/>
+      <c r="D186" s="26"/>
+      <c r="E186" s="28"/>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" s="11"/>
+      <c r="B187" s="11"/>
+      <c r="C187" s="26"/>
+      <c r="D187" s="26"/>
+      <c r="E187" s="28"/>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" s="11"/>
+      <c r="B188" s="11"/>
+      <c r="C188" s="26"/>
+      <c r="D188" s="26"/>
+      <c r="E188" s="28"/>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" s="11"/>
+      <c r="B189" s="11"/>
+      <c r="C189" s="26"/>
+      <c r="D189" s="26"/>
+      <c r="E189" s="28"/>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" s="11"/>
+      <c r="B190" s="11"/>
+      <c r="C190" s="26"/>
+      <c r="D190" s="26"/>
+      <c r="E190" s="28"/>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" s="11"/>
+      <c r="B191" s="11"/>
+      <c r="C191" s="26"/>
+      <c r="D191" s="26"/>
+      <c r="E191" s="28"/>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" s="11"/>
+      <c r="B192" s="11"/>
+      <c r="C192" s="26"/>
+      <c r="D192" s="26"/>
+      <c r="E192" s="28"/>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193" s="11"/>
+      <c r="B193" s="11"/>
+      <c r="C193" s="26"/>
+      <c r="D193" s="26"/>
+      <c r="E193" s="28"/>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194" s="11"/>
+      <c r="B194" s="11"/>
+      <c r="C194" s="26"/>
+      <c r="D194" s="26"/>
+      <c r="E194" s="28"/>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A195" s="11"/>
+      <c r="B195" s="11"/>
+      <c r="C195" s="26"/>
+      <c r="D195" s="26"/>
+      <c r="E195" s="28"/>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A196" s="11"/>
+      <c r="B196" s="11"/>
+      <c r="C196" s="26"/>
+      <c r="D196" s="26"/>
+      <c r="E196" s="28"/>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" s="11"/>
+      <c r="B197" s="11"/>
+      <c r="C197" s="26"/>
+      <c r="D197" s="26"/>
+      <c r="E197" s="28"/>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198" s="11"/>
+      <c r="B198" s="11"/>
+      <c r="C198" s="26"/>
+      <c r="D198" s="26"/>
+      <c r="E198" s="28"/>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A199" s="11"/>
+      <c r="B199" s="11"/>
+      <c r="C199" s="26"/>
+      <c r="D199" s="26"/>
+      <c r="E199" s="28"/>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A200" s="11"/>
+      <c r="B200" s="11"/>
+      <c r="C200" s="26"/>
+      <c r="D200" s="26"/>
+      <c r="E200" s="28"/>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A201" s="11"/>
+      <c r="B201" s="11"/>
+      <c r="C201" s="26"/>
+      <c r="D201" s="26"/>
+      <c r="E201" s="28"/>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A202" s="11"/>
+      <c r="B202" s="11"/>
+      <c r="C202" s="26"/>
+      <c r="D202" s="26"/>
+      <c r="E202" s="28"/>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A203" s="11"/>
+      <c r="B203" s="11"/>
+      <c r="C203" s="26"/>
+      <c r="D203" s="26"/>
+      <c r="E203" s="28"/>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A204" s="11"/>
+      <c r="B204" s="11"/>
+      <c r="C204" s="26"/>
+      <c r="D204" s="26"/>
+      <c r="E204" s="28"/>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A205" s="11"/>
+      <c r="B205" s="11"/>
+      <c r="C205" s="26"/>
+      <c r="D205" s="26"/>
+      <c r="E205" s="28"/>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A206" s="11"/>
+      <c r="B206" s="11"/>
+      <c r="C206" s="26"/>
+      <c r="D206" s="26"/>
+      <c r="E206" s="28"/>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A207" s="11"/>
+      <c r="B207" s="11"/>
+      <c r="C207" s="26"/>
+      <c r="D207" s="26"/>
+      <c r="E207" s="28"/>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A208" s="11"/>
+      <c r="B208" s="11"/>
+      <c r="C208" s="26"/>
+      <c r="D208" s="26"/>
+      <c r="E208" s="28"/>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A209" s="11"/>
+      <c r="B209" s="11"/>
+      <c r="C209" s="26"/>
+      <c r="D209" s="26"/>
+      <c r="E209" s="28"/>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A210" s="11"/>
+      <c r="B210" s="11"/>
+      <c r="C210" s="26"/>
+      <c r="D210" s="26"/>
+      <c r="E210" s="28"/>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A211" s="11"/>
+      <c r="B211" s="11"/>
+      <c r="C211" s="26"/>
+      <c r="D211" s="26"/>
+      <c r="E211" s="28"/>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A212" s="11"/>
+      <c r="B212" s="11"/>
+      <c r="C212" s="26"/>
+      <c r="D212" s="26"/>
+      <c r="E212" s="28"/>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A213" s="11"/>
+      <c r="B213" s="11"/>
+      <c r="C213" s="26"/>
+      <c r="D213" s="26"/>
+      <c r="E213" s="28"/>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A214" s="11"/>
+      <c r="B214" s="11"/>
+      <c r="C214" s="26"/>
+      <c r="D214" s="26"/>
+      <c r="E214" s="28"/>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A215" s="11"/>
+      <c r="B215" s="11"/>
+      <c r="C215" s="26"/>
+      <c r="D215" s="26"/>
+      <c r="E215" s="28"/>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A216" s="11"/>
+      <c r="B216" s="11"/>
+      <c r="C216" s="26"/>
+      <c r="D216" s="26"/>
+      <c r="E216" s="28"/>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A217" s="11"/>
+      <c r="B217" s="11"/>
+      <c r="C217" s="26"/>
+      <c r="D217" s="26"/>
+      <c r="E217" s="28"/>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A218" s="11"/>
+      <c r="B218" s="11"/>
+      <c r="C218" s="26"/>
+      <c r="D218" s="26"/>
+      <c r="E218" s="28"/>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A219" s="11"/>
+      <c r="B219" s="11"/>
+      <c r="C219" s="26"/>
+      <c r="D219" s="26"/>
+      <c r="E219" s="28"/>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A220" s="11"/>
+      <c r="B220" s="11"/>
+      <c r="C220" s="26"/>
+      <c r="D220" s="26"/>
+      <c r="E220" s="28"/>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A221" s="11"/>
+      <c r="B221" s="11"/>
+      <c r="C221" s="26"/>
+      <c r="D221" s="26"/>
+      <c r="E221" s="28"/>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A222" s="11"/>
+      <c r="B222" s="11"/>
+      <c r="C222" s="26"/>
+      <c r="D222" s="26"/>
+      <c r="E222" s="28"/>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A223" s="11"/>
+      <c r="B223" s="11"/>
+      <c r="C223" s="26"/>
+      <c r="D223" s="26"/>
+      <c r="E223" s="28"/>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A224" s="11"/>
+      <c r="B224" s="11"/>
+      <c r="C224" s="26"/>
+      <c r="D224" s="26"/>
+      <c r="E224" s="28"/>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A225" s="11"/>
+      <c r="B225" s="11"/>
+      <c r="C225" s="26"/>
+      <c r="D225" s="26"/>
+      <c r="E225" s="28"/>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A226" s="11"/>
+      <c r="B226" s="11"/>
+      <c r="C226" s="26"/>
+      <c r="D226" s="26"/>
+      <c r="E226" s="28"/>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A227" s="11"/>
+      <c r="B227" s="11"/>
+      <c r="C227" s="26"/>
+      <c r="D227" s="26"/>
+      <c r="E227" s="28"/>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A228" s="11"/>
+      <c r="B228" s="11"/>
+      <c r="C228" s="26"/>
+      <c r="D228" s="26"/>
+      <c r="E228" s="28"/>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A229" s="11"/>
+      <c r="B229" s="11"/>
+      <c r="C229" s="26"/>
+      <c r="D229" s="26"/>
+      <c r="E229" s="28"/>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A230" s="11"/>
+      <c r="B230" s="11"/>
+      <c r="C230" s="26"/>
+      <c r="D230" s="26"/>
+      <c r="E230" s="28"/>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A231" s="11"/>
+      <c r="B231" s="11"/>
+      <c r="C231" s="26"/>
+      <c r="D231" s="26"/>
+      <c r="E231" s="28"/>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A232" s="11"/>
+      <c r="B232" s="11"/>
+      <c r="C232" s="26"/>
+      <c r="D232" s="26"/>
+      <c r="E232" s="28"/>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A233" s="11"/>
+      <c r="B233" s="11"/>
+      <c r="C233" s="26"/>
+      <c r="D233" s="26"/>
+      <c r="E233" s="28"/>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A234" s="11"/>
+      <c r="B234" s="11"/>
+      <c r="C234" s="26"/>
+      <c r="D234" s="26"/>
+      <c r="E234" s="28"/>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A235" s="11"/>
+      <c r="B235" s="11"/>
+      <c r="C235" s="26"/>
+      <c r="D235" s="26"/>
+      <c r="E235" s="28"/>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A236" s="11"/>
+      <c r="B236" s="11"/>
+      <c r="C236" s="26"/>
+      <c r="D236" s="26"/>
+      <c r="E236" s="28"/>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A237" s="11"/>
+      <c r="B237" s="11"/>
+      <c r="C237" s="26"/>
+      <c r="D237" s="26"/>
+      <c r="E237" s="28"/>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A238" s="11"/>
+      <c r="B238" s="11"/>
+      <c r="C238" s="26"/>
+      <c r="D238" s="26"/>
+      <c r="E238" s="28"/>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A239" s="11"/>
+      <c r="B239" s="11"/>
+      <c r="C239" s="26"/>
+      <c r="D239" s="26"/>
+      <c r="E239" s="28"/>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A240" s="11"/>
+      <c r="B240" s="11"/>
+      <c r="C240" s="26"/>
+      <c r="D240" s="26"/>
+      <c r="E240" s="28"/>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A241" s="11"/>
+      <c r="B241" s="11"/>
+      <c r="C241" s="26"/>
+      <c r="D241" s="26"/>
+      <c r="E241" s="28"/>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A242" s="11"/>
+      <c r="B242" s="11"/>
+      <c r="C242" s="26"/>
+      <c r="D242" s="26"/>
+      <c r="E242" s="28"/>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A243" s="11"/>
+      <c r="B243" s="11"/>
+      <c r="C243" s="26"/>
+      <c r="D243" s="26"/>
+      <c r="E243" s="28"/>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A244" s="11"/>
+      <c r="B244" s="11"/>
+      <c r="C244" s="26"/>
+      <c r="D244" s="26"/>
+      <c r="E244" s="28"/>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A245" s="11"/>
+      <c r="B245" s="11"/>
+      <c r="C245" s="26"/>
+      <c r="D245" s="26"/>
+      <c r="E245" s="28"/>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A246" s="11"/>
+      <c r="B246" s="11"/>
+      <c r="C246" s="26"/>
+      <c r="D246" s="26"/>
+      <c r="E246" s="28"/>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A247" s="11"/>
+      <c r="B247" s="11"/>
+      <c r="C247" s="26"/>
+      <c r="D247" s="26"/>
+      <c r="E247" s="28"/>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A248" s="11"/>
+      <c r="B248" s="11"/>
+      <c r="C248" s="26"/>
+      <c r="D248" s="26"/>
+      <c r="E248" s="28"/>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A249" s="11"/>
+      <c r="B249" s="11"/>
+      <c r="C249" s="26"/>
+      <c r="D249" s="26"/>
+      <c r="E249" s="28"/>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A250" s="11"/>
+      <c r="B250" s="11"/>
+      <c r="C250" s="26"/>
+      <c r="D250" s="26"/>
+      <c r="E250" s="28"/>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A251" s="11"/>
+      <c r="B251" s="11"/>
+      <c r="C251" s="26"/>
+      <c r="D251" s="26"/>
+      <c r="E251" s="28"/>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A252" s="11"/>
+      <c r="B252" s="11"/>
+      <c r="C252" s="26"/>
+      <c r="D252" s="26"/>
+      <c r="E252" s="28"/>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A253" s="11"/>
+      <c r="B253" s="11"/>
+      <c r="C253" s="26"/>
+      <c r="D253" s="26"/>
+      <c r="E253" s="28"/>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A254" s="11"/>
+      <c r="B254" s="11"/>
+      <c r="C254" s="26"/>
+      <c r="D254" s="26"/>
+      <c r="E254" s="28"/>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A255" s="11"/>
+      <c r="B255" s="11"/>
+      <c r="C255" s="26"/>
+      <c r="D255" s="26"/>
+      <c r="E255" s="28"/>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A256" s="11"/>
+      <c r="B256" s="11"/>
+      <c r="C256" s="26"/>
+      <c r="D256" s="26"/>
+      <c r="E256" s="28"/>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A257" s="11"/>
+      <c r="B257" s="11"/>
+      <c r="C257" s="26"/>
+      <c r="D257" s="26"/>
+      <c r="E257" s="28"/>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A258" s="11"/>
+      <c r="B258" s="11"/>
+      <c r="C258" s="26"/>
+      <c r="D258" s="26"/>
+      <c r="E258" s="28"/>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A259" s="11"/>
+      <c r="B259" s="11"/>
+      <c r="C259" s="26"/>
+      <c r="D259" s="26"/>
+      <c r="E259" s="28"/>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A260" s="11"/>
+      <c r="B260" s="11"/>
+      <c r="C260" s="26"/>
+      <c r="D260" s="26"/>
+      <c r="E260" s="28"/>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A261" s="11"/>
+      <c r="B261" s="11"/>
+      <c r="C261" s="26"/>
+      <c r="D261" s="26"/>
+      <c r="E261" s="28"/>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A262" s="11"/>
+      <c r="B262" s="11"/>
+      <c r="C262" s="26"/>
+      <c r="D262" s="26"/>
+      <c r="E262" s="28"/>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A263" s="11"/>
+      <c r="B263" s="11"/>
+      <c r="C263" s="26"/>
+      <c r="D263" s="26"/>
+      <c r="E263" s="28"/>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A264" s="11"/>
+      <c r="B264" s="11"/>
+      <c r="C264" s="26"/>
+      <c r="D264" s="26"/>
+      <c r="E264" s="28"/>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A265" s="11"/>
+      <c r="B265" s="11"/>
+      <c r="C265" s="26"/>
+      <c r="D265" s="26"/>
+      <c r="E265" s="28"/>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A266" s="11"/>
+      <c r="B266" s="11"/>
+      <c r="C266" s="26"/>
+      <c r="D266" s="26"/>
+      <c r="E266" s="28"/>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A267" s="11"/>
+      <c r="B267" s="11"/>
+      <c r="C267" s="26"/>
+      <c r="D267" s="26"/>
+      <c r="E267" s="28"/>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A268" s="11"/>
+      <c r="B268" s="11"/>
+      <c r="C268" s="26"/>
+      <c r="D268" s="26"/>
+      <c r="E268" s="28"/>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A269" s="11"/>
+      <c r="B269" s="11"/>
+      <c r="C269" s="26"/>
+      <c r="D269" s="26"/>
+      <c r="E269" s="28"/>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A270" s="11"/>
+      <c r="B270" s="11"/>
+      <c r="C270" s="26"/>
+      <c r="D270" s="26"/>
+      <c r="E270" s="28"/>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A271" s="11"/>
+      <c r="B271" s="11"/>
+      <c r="C271" s="26"/>
+      <c r="D271" s="26"/>
+      <c r="E271" s="28"/>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A272" s="11"/>
+      <c r="B272" s="11"/>
+      <c r="C272" s="26"/>
+      <c r="D272" s="26"/>
+      <c r="E272" s="28"/>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A273" s="11"/>
+      <c r="B273" s="11"/>
+      <c r="C273" s="26"/>
+      <c r="D273" s="26"/>
+      <c r="E273" s="28"/>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A274" s="11"/>
+      <c r="B274" s="11"/>
+      <c r="C274" s="26"/>
+      <c r="D274" s="26"/>
+      <c r="E274" s="28"/>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A275" s="11"/>
+      <c r="B275" s="11"/>
+      <c r="C275" s="26"/>
+      <c r="D275" s="26"/>
+      <c r="E275" s="28"/>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A276" s="11"/>
+      <c r="B276" s="11"/>
+      <c r="C276" s="26"/>
+      <c r="D276" s="26"/>
+      <c r="E276" s="28"/>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A277" s="11"/>
+      <c r="B277" s="11"/>
+      <c r="C277" s="26"/>
+      <c r="D277" s="26"/>
+      <c r="E277" s="28"/>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A278" s="11"/>
+      <c r="B278" s="11"/>
+      <c r="C278" s="26"/>
+      <c r="D278" s="26"/>
+      <c r="E278" s="28"/>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A279" s="11"/>
+      <c r="B279" s="11"/>
+      <c r="C279" s="26"/>
+      <c r="D279" s="26"/>
+      <c r="E279" s="28"/>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A280" s="11"/>
+      <c r="B280" s="11"/>
+      <c r="C280" s="26"/>
+      <c r="D280" s="26"/>
+      <c r="E280" s="28"/>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A281" s="11"/>
+      <c r="B281" s="11"/>
+      <c r="C281" s="26"/>
+      <c r="D281" s="26"/>
+      <c r="E281" s="28"/>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A282" s="11"/>
+      <c r="B282" s="11"/>
+      <c r="C282" s="26"/>
+      <c r="D282" s="26"/>
+      <c r="E282" s="28"/>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A283" s="11"/>
+      <c r="B283" s="11"/>
+      <c r="C283" s="26"/>
+      <c r="D283" s="26"/>
+      <c r="E283" s="28"/>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A284" s="11"/>
+      <c r="B284" s="11"/>
+      <c r="C284" s="26"/>
+      <c r="D284" s="26"/>
+      <c r="E284" s="28"/>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A285" s="11"/>
+      <c r="B285" s="11"/>
+      <c r="C285" s="26"/>
+      <c r="D285" s="26"/>
+      <c r="E285" s="28"/>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A286" s="11"/>
+      <c r="B286" s="11"/>
+      <c r="C286" s="26"/>
+      <c r="D286" s="26"/>
+      <c r="E286" s="28"/>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A287" s="11"/>
+      <c r="B287" s="11"/>
+      <c r="C287" s="26"/>
+      <c r="D287" s="26"/>
+      <c r="E287" s="28"/>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A288" s="11"/>
+      <c r="B288" s="11"/>
+      <c r="C288" s="26"/>
+      <c r="D288" s="26"/>
+      <c r="E288" s="28"/>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A289" s="11"/>
+      <c r="B289" s="11"/>
+      <c r="C289" s="26"/>
+      <c r="D289" s="26"/>
+      <c r="E289" s="28"/>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A290" s="11"/>
+      <c r="B290" s="11"/>
+      <c r="C290" s="26"/>
+      <c r="D290" s="26"/>
+      <c r="E290" s="28"/>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A291" s="11"/>
+      <c r="B291" s="11"/>
+      <c r="C291" s="26"/>
+      <c r="D291" s="26"/>
+      <c r="E291" s="28"/>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A292" s="11"/>
+      <c r="B292" s="11"/>
+      <c r="C292" s="26"/>
+      <c r="D292" s="26"/>
+      <c r="E292" s="28"/>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A293" s="11"/>
+      <c r="B293" s="11"/>
+      <c r="C293" s="26"/>
+      <c r="D293" s="26"/>
+      <c r="E293" s="28"/>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A294" s="11"/>
+      <c r="B294" s="11"/>
+      <c r="C294" s="26"/>
+      <c r="D294" s="26"/>
+      <c r="E294" s="28"/>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A295" s="11"/>
+      <c r="B295" s="11"/>
+      <c r="C295" s="26"/>
+      <c r="D295" s="26"/>
+      <c r="E295" s="28"/>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A296" s="11"/>
+      <c r="B296" s="11"/>
+      <c r="C296" s="26"/>
+      <c r="D296" s="26"/>
+      <c r="E296" s="28"/>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A297" s="11"/>
+      <c r="B297" s="11"/>
+      <c r="C297" s="26"/>
+      <c r="D297" s="26"/>
+      <c r="E297" s="28"/>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A298" s="11"/>
+      <c r="B298" s="11"/>
+      <c r="C298" s="26"/>
+      <c r="D298" s="26"/>
+      <c r="E298" s="28"/>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A299" s="11"/>
+      <c r="B299" s="11"/>
+      <c r="C299" s="26"/>
+      <c r="D299" s="26"/>
+      <c r="E299" s="28"/>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A300" s="11"/>
+      <c r="B300" s="11"/>
+      <c r="C300" s="26"/>
+      <c r="D300" s="26"/>
+      <c r="E300" s="28"/>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A301" s="11"/>
+      <c r="B301" s="11"/>
+      <c r="C301" s="26"/>
+      <c r="D301" s="26"/>
+      <c r="E301" s="28"/>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A302" s="11"/>
+      <c r="B302" s="11"/>
+      <c r="C302" s="26"/>
+      <c r="D302" s="26"/>
+      <c r="E302" s="28"/>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A303" s="11"/>
+      <c r="B303" s="11"/>
+      <c r="C303" s="26"/>
+      <c r="D303" s="26"/>
+      <c r="E303" s="28"/>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A304" s="11"/>
+      <c r="B304" s="11"/>
+      <c r="C304" s="26"/>
+      <c r="D304" s="26"/>
+      <c r="E304" s="28"/>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A305" s="11"/>
+      <c r="B305" s="11"/>
+      <c r="C305" s="26"/>
+      <c r="D305" s="26"/>
+      <c r="E305" s="28"/>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A306" s="11"/>
+      <c r="B306" s="11"/>
+      <c r="C306" s="26"/>
+      <c r="D306" s="26"/>
+      <c r="E306" s="28"/>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A307" s="11"/>
+      <c r="B307" s="11"/>
+      <c r="C307" s="26"/>
+      <c r="D307" s="26"/>
+      <c r="E307" s="28"/>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A308" s="11"/>
+      <c r="B308" s="11"/>
+      <c r="C308" s="26"/>
+      <c r="D308" s="26"/>
+      <c r="E308" s="28"/>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A309" s="11"/>
+      <c r="B309" s="11"/>
+      <c r="C309" s="26"/>
+      <c r="D309" s="26"/>
+      <c r="E309" s="28"/>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A310" s="11"/>
+      <c r="B310" s="11"/>
+      <c r="C310" s="26"/>
+      <c r="D310" s="26"/>
+      <c r="E310" s="28"/>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A311" s="11"/>
+      <c r="B311" s="11"/>
+      <c r="C311" s="26"/>
+      <c r="D311" s="26"/>
+      <c r="E311" s="28"/>
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A312" s="11"/>
+      <c r="B312" s="11"/>
+      <c r="C312" s="26"/>
+      <c r="D312" s="26"/>
+      <c r="E312" s="28"/>
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A313" s="11"/>
+      <c r="B313" s="11"/>
+      <c r="C313" s="26"/>
+      <c r="D313" s="26"/>
+      <c r="E313" s="28"/>
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A314" s="11"/>
+      <c r="B314" s="11"/>
+      <c r="C314" s="26"/>
+      <c r="D314" s="26"/>
+      <c r="E314" s="28"/>
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A315" s="11"/>
+      <c r="B315" s="11"/>
+      <c r="C315" s="26"/>
+      <c r="D315" s="26"/>
+      <c r="E315" s="28"/>
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A316" s="11"/>
+      <c r="B316" s="11"/>
+      <c r="C316" s="26"/>
+      <c r="D316" s="26"/>
+      <c r="E316" s="28"/>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A317" s="11"/>
+      <c r="B317" s="11"/>
+      <c r="C317" s="26"/>
+      <c r="D317" s="26"/>
+      <c r="E317" s="28"/>
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A318" s="11"/>
+      <c r="B318" s="11"/>
+      <c r="C318" s="26"/>
+      <c r="D318" s="26"/>
+      <c r="E318" s="28"/>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A319" s="11"/>
+      <c r="B319" s="11"/>
+      <c r="C319" s="26"/>
+      <c r="D319" s="26"/>
+      <c r="E319" s="28"/>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A320" s="11"/>
+      <c r="B320" s="11"/>
+      <c r="C320" s="26"/>
+      <c r="D320" s="26"/>
+      <c r="E320" s="28"/>
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A321" s="11"/>
+      <c r="B321" s="11"/>
+      <c r="C321" s="26"/>
+      <c r="D321" s="26"/>
+      <c r="E321" s="28"/>
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A322" s="11"/>
+      <c r="B322" s="11"/>
+      <c r="C322" s="26"/>
+      <c r="D322" s="26"/>
+      <c r="E322" s="28"/>
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A323" s="11"/>
+      <c r="B323" s="11"/>
+      <c r="C323" s="26"/>
+      <c r="D323" s="26"/>
+      <c r="E323" s="28"/>
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A324" s="11"/>
+      <c r="B324" s="11"/>
+      <c r="C324" s="26"/>
+      <c r="D324" s="26"/>
+      <c r="E324" s="28"/>
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A325" s="11"/>
+      <c r="B325" s="11"/>
+      <c r="C325" s="26"/>
+      <c r="D325" s="26"/>
+      <c r="E325" s="28"/>
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A326" s="11"/>
+      <c r="B326" s="11"/>
+      <c r="C326" s="26"/>
+      <c r="D326" s="26"/>
+      <c r="E326" s="28"/>
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A327" s="11"/>
+      <c r="B327" s="11"/>
+      <c r="C327" s="26"/>
+      <c r="D327" s="26"/>
+      <c r="E327" s="28"/>
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A328" s="11"/>
+      <c r="B328" s="11"/>
+      <c r="C328" s="26"/>
+      <c r="D328" s="26"/>
+      <c r="E328" s="28"/>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A329" s="11"/>
+      <c r="B329" s="11"/>
+      <c r="C329" s="26"/>
+      <c r="D329" s="26"/>
+      <c r="E329" s="28"/>
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A330" s="11"/>
+      <c r="B330" s="11"/>
+      <c r="C330" s="26"/>
+      <c r="D330" s="26"/>
+      <c r="E330" s="28"/>
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A331" s="11"/>
+      <c r="B331" s="11"/>
+      <c r="C331" s="26"/>
+      <c r="D331" s="26"/>
+      <c r="E331" s="28"/>
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A332" s="11"/>
+      <c r="B332" s="11"/>
+      <c r="C332" s="26"/>
+      <c r="D332" s="26"/>
+      <c r="E332" s="28"/>
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A333" s="11"/>
+      <c r="B333" s="11"/>
+      <c r="C333" s="26"/>
+      <c r="D333" s="26"/>
+      <c r="E333" s="28"/>
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A334" s="11"/>
+      <c r="B334" s="11"/>
+      <c r="C334" s="26"/>
+      <c r="D334" s="26"/>
+      <c r="E334" s="28"/>
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A335" s="11"/>
+      <c r="B335" s="11"/>
+      <c r="C335" s="26"/>
+      <c r="D335" s="26"/>
+      <c r="E335" s="28"/>
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A336" s="11"/>
+      <c r="B336" s="11"/>
+      <c r="C336" s="26"/>
+      <c r="D336" s="26"/>
+      <c r="E336" s="28"/>
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A337" s="11"/>
+      <c r="B337" s="11"/>
+      <c r="C337" s="26"/>
+      <c r="D337" s="26"/>
+      <c r="E337" s="28"/>
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A338" s="11"/>
+      <c r="B338" s="11"/>
+      <c r="C338" s="26"/>
+      <c r="D338" s="26"/>
+      <c r="E338" s="28"/>
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A339" s="11"/>
+      <c r="B339" s="11"/>
+      <c r="C339" s="26"/>
+      <c r="D339" s="26"/>
+      <c r="E339" s="28"/>
+    </row>
+    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A340" s="11"/>
+      <c r="B340" s="11"/>
+      <c r="C340" s="26"/>
+      <c r="D340" s="26"/>
+      <c r="E340" s="28"/>
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A341" s="11"/>
+      <c r="B341" s="11"/>
+      <c r="C341" s="26"/>
+      <c r="D341" s="26"/>
+      <c r="E341" s="28"/>
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A342" s="11"/>
+      <c r="B342" s="11"/>
+      <c r="C342" s="26"/>
+      <c r="D342" s="26"/>
+      <c r="E342" s="28"/>
+    </row>
+    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A343" s="11"/>
+      <c r="B343" s="11"/>
+      <c r="C343" s="26"/>
+      <c r="D343" s="26"/>
+      <c r="E343" s="28"/>
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A344" s="11"/>
+      <c r="B344" s="11"/>
+      <c r="C344" s="26"/>
+      <c r="D344" s="26"/>
+      <c r="E344" s="28"/>
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A345" s="11"/>
+      <c r="B345" s="11"/>
+      <c r="C345" s="26"/>
+      <c r="D345" s="26"/>
+      <c r="E345" s="28"/>
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A346" s="11"/>
+      <c r="B346" s="11"/>
+      <c r="C346" s="26"/>
+      <c r="D346" s="26"/>
+      <c r="E346" s="28"/>
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A347" s="11"/>
+      <c r="B347" s="11"/>
+      <c r="C347" s="26"/>
+      <c r="D347" s="26"/>
+      <c r="E347" s="28"/>
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A348" s="11"/>
+      <c r="B348" s="11"/>
+      <c r="C348" s="26"/>
+      <c r="D348" s="26"/>
+      <c r="E348" s="28"/>
+    </row>
+    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A349" s="11"/>
+      <c r="B349" s="11"/>
+      <c r="C349" s="26"/>
+      <c r="D349" s="26"/>
+      <c r="E349" s="28"/>
+    </row>
+    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A350" s="11"/>
+      <c r="B350" s="11"/>
+      <c r="C350" s="26"/>
+      <c r="D350" s="26"/>
+      <c r="E350" s="28"/>
+    </row>
+    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A351" s="11"/>
+      <c r="B351" s="11"/>
+      <c r="C351" s="26"/>
+      <c r="D351" s="26"/>
+      <c r="E351" s="28"/>
+    </row>
+    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A352" s="11"/>
+      <c r="B352" s="11"/>
+      <c r="C352" s="26"/>
+      <c r="D352" s="26"/>
+      <c r="E352" s="28"/>
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A353" s="11"/>
+      <c r="B353" s="11"/>
+      <c r="C353" s="26"/>
+      <c r="D353" s="26"/>
+      <c r="E353" s="28"/>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A354" s="11"/>
+      <c r="B354" s="11"/>
+      <c r="C354" s="26"/>
+      <c r="D354" s="26"/>
+      <c r="E354" s="28"/>
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A355" s="11"/>
+      <c r="B355" s="11"/>
+      <c r="C355" s="26"/>
+      <c r="D355" s="26"/>
+      <c r="E355" s="28"/>
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A356" s="11"/>
+      <c r="B356" s="11"/>
+      <c r="C356" s="26"/>
+      <c r="D356" s="26"/>
+      <c r="E356" s="28"/>
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A357" s="11"/>
+      <c r="B357" s="11"/>
+      <c r="C357" s="26"/>
+      <c r="D357" s="26"/>
+      <c r="E357" s="28"/>
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A358" s="11"/>
+      <c r="B358" s="11"/>
+      <c r="C358" s="26"/>
+      <c r="D358" s="26"/>
+      <c r="E358" s="28"/>
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A359" s="11"/>
+      <c r="B359" s="11"/>
+      <c r="C359" s="26"/>
+      <c r="D359" s="26"/>
+      <c r="E359" s="28"/>
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A360" s="11"/>
+      <c r="B360" s="11"/>
+      <c r="C360" s="26"/>
+      <c r="D360" s="26"/>
+      <c r="E360" s="28"/>
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A361" s="11"/>
+      <c r="B361" s="11"/>
+      <c r="C361" s="26"/>
+      <c r="D361" s="26"/>
+      <c r="E361" s="28"/>
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A362" s="11"/>
+      <c r="B362" s="11"/>
+      <c r="C362" s="26"/>
+      <c r="D362" s="26"/>
+      <c r="E362" s="28"/>
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A363" s="11"/>
+      <c r="B363" s="11"/>
+      <c r="C363" s="26"/>
+      <c r="D363" s="26"/>
+      <c r="E363" s="28"/>
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A364" s="11"/>
+      <c r="B364" s="11"/>
+      <c r="C364" s="26"/>
+      <c r="D364" s="26"/>
+      <c r="E364" s="28"/>
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A365" s="11"/>
+      <c r="B365" s="11"/>
+      <c r="C365" s="26"/>
+      <c r="D365" s="26"/>
+      <c r="E365" s="28"/>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A366" s="11"/>
+      <c r="B366" s="11"/>
+      <c r="C366" s="26"/>
+      <c r="D366" s="26"/>
+      <c r="E366" s="28"/>
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A367" s="11"/>
+      <c r="B367" s="11"/>
+      <c r="C367" s="26"/>
+      <c r="D367" s="26"/>
+      <c r="E367" s="28"/>
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A368" s="11"/>
+      <c r="B368" s="11"/>
+      <c r="C368" s="26"/>
+      <c r="D368" s="26"/>
+      <c r="E368" s="28"/>
+    </row>
+    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A369" s="11"/>
+      <c r="B369" s="11"/>
+      <c r="C369" s="26"/>
+      <c r="D369" s="26"/>
+      <c r="E369" s="28"/>
+    </row>
+    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A370" s="11"/>
+      <c r="B370" s="11"/>
+      <c r="C370" s="26"/>
+      <c r="D370" s="26"/>
+      <c r="E370" s="28"/>
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A371" s="11"/>
+      <c r="B371" s="11"/>
+      <c r="C371" s="26"/>
+      <c r="D371" s="26"/>
+      <c r="E371" s="28"/>
+    </row>
+    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A372" s="11"/>
+      <c r="B372" s="11"/>
+      <c r="C372" s="26"/>
+      <c r="D372" s="26"/>
+      <c r="E372" s="28"/>
+    </row>
+    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A373" s="11"/>
+      <c r="B373" s="11"/>
+      <c r="C373" s="26"/>
+      <c r="D373" s="26"/>
+      <c r="E373" s="28"/>
+    </row>
+    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A374" s="11"/>
+      <c r="B374" s="11"/>
+      <c r="C374" s="26"/>
+      <c r="D374" s="26"/>
+      <c r="E374" s="28"/>
+    </row>
+    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A375" s="11"/>
+      <c r="B375" s="11"/>
+      <c r="C375" s="26"/>
+      <c r="D375" s="26"/>
+      <c r="E375" s="28"/>
+    </row>
+    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A376" s="11"/>
+      <c r="B376" s="11"/>
+      <c r="C376" s="26"/>
+      <c r="D376" s="26"/>
+      <c r="E376" s="28"/>
+    </row>
+    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A377" s="11"/>
+      <c r="B377" s="11"/>
+      <c r="C377" s="26"/>
+      <c r="D377" s="26"/>
+      <c r="E377" s="28"/>
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A378" s="11"/>
+      <c r="B378" s="11"/>
+      <c r="C378" s="26"/>
+      <c r="D378" s="26"/>
+      <c r="E378" s="28"/>
+    </row>
+    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A379" s="11"/>
+      <c r="B379" s="11"/>
+      <c r="C379" s="26"/>
+      <c r="D379" s="26"/>
+      <c r="E379" s="28"/>
+    </row>
+    <row r="380" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A380" s="11"/>
+      <c r="B380" s="11"/>
+      <c r="C380" s="26"/>
+      <c r="D380" s="26"/>
+      <c r="E380" s="28"/>
+    </row>
+    <row r="381" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A381" s="11"/>
+      <c r="B381" s="11"/>
+      <c r="C381" s="26"/>
+      <c r="D381" s="26"/>
+      <c r="E381" s="28"/>
+    </row>
+    <row r="382" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A382" s="11"/>
+      <c r="B382" s="11"/>
+      <c r="C382" s="26"/>
+      <c r="D382" s="26"/>
+      <c r="E382" s="28"/>
+    </row>
+    <row r="383" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A383" s="11"/>
+      <c r="B383" s="11"/>
+      <c r="C383" s="26"/>
+      <c r="D383" s="26"/>
+      <c r="E383" s="28"/>
+    </row>
+    <row r="384" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A384" s="11"/>
+      <c r="B384" s="11"/>
+      <c r="C384" s="26"/>
+      <c r="D384" s="26"/>
+      <c r="E384" s="28"/>
+    </row>
+    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A385" s="11"/>
+      <c r="B385" s="11"/>
+      <c r="C385" s="26"/>
+      <c r="D385" s="26"/>
+      <c r="E385" s="28"/>
+    </row>
+    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A386" s="11"/>
+      <c r="B386" s="11"/>
+      <c r="C386" s="26"/>
+      <c r="D386" s="26"/>
+      <c r="E386" s="28"/>
+    </row>
+    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A387" s="11"/>
+      <c r="B387" s="11"/>
+      <c r="C387" s="26"/>
+      <c r="D387" s="26"/>
+      <c r="E387" s="28"/>
+    </row>
+    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A388" s="11"/>
+      <c r="B388" s="11"/>
+      <c r="C388" s="26"/>
+      <c r="D388" s="26"/>
+      <c r="E388" s="28"/>
+    </row>
+    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A389" s="11"/>
+      <c r="B389" s="11"/>
+      <c r="C389" s="26"/>
+      <c r="D389" s="26"/>
+      <c r="E389" s="28"/>
+    </row>
+    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A390" s="11"/>
+      <c r="B390" s="11"/>
+      <c r="C390" s="26"/>
+      <c r="D390" s="26"/>
+      <c r="E390" s="28"/>
+    </row>
+    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A391" s="11"/>
+      <c r="B391" s="11"/>
+      <c r="C391" s="26"/>
+      <c r="D391" s="26"/>
+      <c r="E391" s="28"/>
+    </row>
+    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A392" s="11"/>
+      <c r="B392" s="11"/>
+      <c r="C392" s="26"/>
+      <c r="D392" s="26"/>
+      <c r="E392" s="28"/>
+    </row>
+    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A393" s="11"/>
+      <c r="B393" s="11"/>
+      <c r="C393" s="26"/>
+      <c r="D393" s="26"/>
+      <c r="E393" s="28"/>
+    </row>
+    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A394" s="11"/>
+      <c r="B394" s="11"/>
+      <c r="C394" s="26"/>
+      <c r="D394" s="26"/>
+      <c r="E394" s="28"/>
+    </row>
+    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A395" s="11"/>
+      <c r="B395" s="11"/>
+      <c r="C395" s="26"/>
+      <c r="D395" s="26"/>
+      <c r="E395" s="28"/>
+    </row>
+    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A396" s="11"/>
+      <c r="B396" s="11"/>
+      <c r="C396" s="26"/>
+      <c r="D396" s="26"/>
+      <c r="E396" s="28"/>
+    </row>
+    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A397" s="11"/>
+      <c r="B397" s="11"/>
+      <c r="C397" s="26"/>
+      <c r="D397" s="26"/>
+      <c r="E397" s="28"/>
+    </row>
+    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A398" s="11"/>
+      <c r="B398" s="11"/>
+      <c r="C398" s="26"/>
+      <c r="D398" s="26"/>
+      <c r="E398" s="28"/>
+    </row>
+    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A399" s="11"/>
+      <c r="B399" s="11"/>
+      <c r="C399" s="26"/>
+      <c r="D399" s="26"/>
+      <c r="E399" s="28"/>
+    </row>
+    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A400" s="11"/>
+      <c r="B400" s="11"/>
+      <c r="C400" s="26"/>
+      <c r="D400" s="26"/>
+      <c r="E400" s="28"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/rss_islandr/templates/report_template.xlsx
+++ b/rss_islandr/templates/report_template.xlsx
@@ -464,14 +464,33 @@
     <xf numFmtId="10" fontId="3" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -485,25 +504,6 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Calculation" xfId="3" builtinId="22"/>
@@ -828,136 +828,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="20"/>
       <c r="C2" s="3"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="15"/>
+      <c r="G2" s="20"/>
       <c r="H2" s="3"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="24" t="s">
+      <c r="K2" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="24"/>
+      <c r="L2" s="21"/>
       <c r="M2" s="3"/>
       <c r="N2" s="1"/>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="14"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="9"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="14"/>
+      <c r="G3" s="22"/>
       <c r="H3" s="3"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="14"/>
+      <c r="L3" s="22"/>
       <c r="M3" s="9"/>
       <c r="N3" s="1"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="21"/>
+      <c r="G4" s="23"/>
       <c r="H4" s="3"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="21" t="s">
+      <c r="K4" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="21"/>
+      <c r="L4" s="23"/>
       <c r="M4" s="9"/>
       <c r="N4" s="1"/>
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="23"/>
+      <c r="B5" s="25"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="23"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="25"/>
       <c r="H5" s="3"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="23"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="25"/>
       <c r="M5" s="9"/>
       <c r="N5" s="1"/>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="20"/>
+      <c r="B7" s="29"/>
       <c r="C7" s="4"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -973,10 +973,10 @@
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="20"/>
+      <c r="B8" s="29"/>
       <c r="C8" s="4"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -992,10 +992,10 @@
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="20"/>
+      <c r="B9" s="29"/>
       <c r="C9" s="13"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -1011,337 +1011,404 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="17" t="s">
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="18"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="17" t="s">
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="H11" s="18"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="17" t="s">
+      <c r="H11" s="27"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="18"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="17" t="s">
+      <c r="K11" s="27"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="N11" s="18"/>
-      <c r="O11" s="19"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="28"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="15"/>
+      <c r="B12" s="20"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="15"/>
+      <c r="E12" s="20"/>
       <c r="F12" s="4"/>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="15"/>
+      <c r="H12" s="20"/>
       <c r="I12" s="4"/>
-      <c r="J12" s="15" t="s">
+      <c r="J12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="K12" s="15"/>
+      <c r="K12" s="20"/>
       <c r="L12" s="4"/>
-      <c r="M12" s="15" t="s">
+      <c r="M12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="N12" s="15"/>
+      <c r="N12" s="20"/>
       <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="14"/>
+      <c r="B13" s="22"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="14"/>
+      <c r="E13" s="22"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="14"/>
+      <c r="H13" s="22"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="14" t="s">
+      <c r="J13" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="K13" s="14"/>
+      <c r="K13" s="22"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="14" t="s">
+      <c r="M13" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="N13" s="14"/>
+      <c r="N13" s="22"/>
       <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="14"/>
+      <c r="B14" s="22"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="14"/>
+      <c r="E14" s="22"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="14"/>
+      <c r="H14" s="22"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="14" t="s">
+      <c r="J14" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="14"/>
+      <c r="K14" s="22"/>
       <c r="L14" s="4"/>
-      <c r="M14" s="14" t="s">
+      <c r="M14" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="14"/>
+      <c r="N14" s="22"/>
       <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="14"/>
+      <c r="B15" s="22"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="14"/>
+      <c r="E15" s="22"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="14" t="s">
+      <c r="J15" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="14"/>
+      <c r="K15" s="22"/>
       <c r="L15" s="4"/>
-      <c r="M15" s="14" t="s">
+      <c r="M15" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="N15" s="14"/>
+      <c r="N15" s="22"/>
       <c r="O15" s="7"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="14"/>
+      <c r="B16" s="22"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
       <c r="I16" s="6"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
       <c r="L16" s="5"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
       <c r="O16" s="8"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="14"/>
+      <c r="B17" s="22"/>
       <c r="C17" s="13"/>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="14"/>
+      <c r="E17" s="22"/>
       <c r="F17" s="13"/>
-      <c r="G17" s="14" t="s">
+      <c r="G17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="14"/>
+      <c r="H17" s="22"/>
       <c r="I17" s="13"/>
-      <c r="J17" s="14" t="s">
+      <c r="J17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="K17" s="14"/>
+      <c r="K17" s="22"/>
       <c r="L17" s="13"/>
-      <c r="M17" s="14" t="s">
+      <c r="M17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="N17" s="14"/>
+      <c r="N17" s="22"/>
       <c r="O17" s="13"/>
     </row>
     <row r="18" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="str">
+      <c r="A19" s="26" t="str">
         <f>A11</f>
         <v>Soil</v>
       </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="17" t="str">
+      <c r="B19" s="27"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="26" t="str">
         <f t="shared" ref="D19" si="0">D11</f>
         <v>Ground water</v>
       </c>
-      <c r="E19" s="18"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="17" t="str">
+      <c r="E19" s="27"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="26" t="str">
         <f t="shared" ref="G19" si="1">G11</f>
         <v>Surface water</v>
       </c>
-      <c r="H19" s="18"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="17" t="str">
+      <c r="H19" s="27"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="26" t="str">
         <f t="shared" ref="J19" si="2">J11</f>
         <v>Air</v>
       </c>
-      <c r="K19" s="18"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="17" t="str">
+      <c r="K19" s="27"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="26" t="str">
         <f t="shared" ref="M19" si="3">M11</f>
         <v>Sediment</v>
       </c>
-      <c r="N19" s="18"/>
-      <c r="O19" s="19"/>
+      <c r="N19" s="27"/>
+      <c r="O19" s="28"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="15"/>
+      <c r="B20" s="20"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E20" s="15"/>
+      <c r="E20" s="20"/>
       <c r="F20" s="4"/>
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H20" s="15"/>
+      <c r="H20" s="20"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="15" t="s">
+      <c r="J20" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="K20" s="15"/>
+      <c r="K20" s="20"/>
       <c r="L20" s="4"/>
-      <c r="M20" s="15" t="s">
+      <c r="M20" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="N20" s="15"/>
+      <c r="N20" s="20"/>
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="14"/>
+      <c r="B21" s="22"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="14"/>
+      <c r="E21" s="22"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="14" t="s">
+      <c r="G21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="14"/>
+      <c r="H21" s="22"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="14" t="s">
+      <c r="J21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="14"/>
+      <c r="K21" s="22"/>
       <c r="L21" s="4"/>
-      <c r="M21" s="14" t="s">
+      <c r="M21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="N21" s="14"/>
+      <c r="N21" s="22"/>
       <c r="O21" s="7"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="14"/>
+      <c r="B22" s="22"/>
       <c r="C22" s="13"/>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="14"/>
+      <c r="E22" s="22"/>
       <c r="F22" s="13"/>
-      <c r="G22" s="14" t="s">
+      <c r="G22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="H22" s="14"/>
+      <c r="H22" s="22"/>
       <c r="I22" s="13"/>
-      <c r="J22" s="14" t="s">
+      <c r="J22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="K22" s="14"/>
+      <c r="K22" s="22"/>
       <c r="L22" s="13"/>
-      <c r="M22" s="14" t="s">
+      <c r="M22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="N22" s="14"/>
+      <c r="N22" s="22"/>
       <c r="O22" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="74">
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="A6:O6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="K5:L5"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="F2:G2"/>
@@ -1349,73 +1416,6 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="K3:L3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="A6:O6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A18:O18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="M22:N22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -1440,136 +1440,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="20"/>
       <c r="C2" s="3"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="15"/>
+      <c r="G2" s="20"/>
       <c r="H2" s="3"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="24" t="s">
+      <c r="K2" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="24"/>
+      <c r="L2" s="21"/>
       <c r="M2" s="3"/>
       <c r="N2" s="1"/>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="14"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="9"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="14"/>
+      <c r="G3" s="22"/>
       <c r="H3" s="3"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="14"/>
+      <c r="L3" s="22"/>
       <c r="M3" s="9"/>
       <c r="N3" s="1"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="21"/>
+      <c r="G4" s="23"/>
       <c r="H4" s="3"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="21" t="s">
+      <c r="K4" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="21"/>
+      <c r="L4" s="23"/>
       <c r="M4" s="9"/>
       <c r="N4" s="1"/>
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="23"/>
+      <c r="B5" s="25"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="23"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="25"/>
       <c r="H5" s="3"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="23"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="25"/>
       <c r="M5" s="9"/>
       <c r="N5" s="1"/>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="20"/>
+      <c r="B7" s="29"/>
       <c r="C7" s="4"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -1585,10 +1585,10 @@
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="20"/>
+      <c r="B8" s="29"/>
       <c r="C8" s="4"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -1604,10 +1604,10 @@
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="20"/>
+      <c r="B9" s="29"/>
       <c r="C9" s="13"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -1623,337 +1623,404 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="17" t="s">
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="18"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="17" t="s">
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="H11" s="18"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="17" t="s">
+      <c r="H11" s="27"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="18"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="17" t="s">
+      <c r="K11" s="27"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="N11" s="18"/>
-      <c r="O11" s="19"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="28"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="15"/>
+      <c r="B12" s="20"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="15"/>
+      <c r="E12" s="20"/>
       <c r="F12" s="4"/>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="15"/>
+      <c r="H12" s="20"/>
       <c r="I12" s="4"/>
-      <c r="J12" s="15" t="s">
+      <c r="J12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="K12" s="15"/>
+      <c r="K12" s="20"/>
       <c r="L12" s="4"/>
-      <c r="M12" s="15" t="s">
+      <c r="M12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="N12" s="15"/>
+      <c r="N12" s="20"/>
       <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="14"/>
+      <c r="B13" s="22"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="14"/>
+      <c r="E13" s="22"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="14"/>
+      <c r="H13" s="22"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="14" t="s">
+      <c r="J13" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="K13" s="14"/>
+      <c r="K13" s="22"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="14" t="s">
+      <c r="M13" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="N13" s="14"/>
+      <c r="N13" s="22"/>
       <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="14"/>
+      <c r="B14" s="22"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="14"/>
+      <c r="E14" s="22"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="14"/>
+      <c r="H14" s="22"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="14" t="s">
+      <c r="J14" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="14"/>
+      <c r="K14" s="22"/>
       <c r="L14" s="4"/>
-      <c r="M14" s="14" t="s">
+      <c r="M14" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="14"/>
+      <c r="N14" s="22"/>
       <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="14"/>
+      <c r="B15" s="22"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="14"/>
+      <c r="E15" s="22"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="14" t="s">
+      <c r="J15" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="14"/>
+      <c r="K15" s="22"/>
       <c r="L15" s="4"/>
-      <c r="M15" s="14" t="s">
+      <c r="M15" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="N15" s="14"/>
+      <c r="N15" s="22"/>
       <c r="O15" s="7"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="14"/>
+      <c r="B16" s="22"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
       <c r="I16" s="6"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
       <c r="L16" s="5"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
       <c r="O16" s="8"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="14"/>
+      <c r="B17" s="22"/>
       <c r="C17" s="13"/>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="14"/>
+      <c r="E17" s="22"/>
       <c r="F17" s="13"/>
-      <c r="G17" s="14" t="s">
+      <c r="G17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="14"/>
+      <c r="H17" s="22"/>
       <c r="I17" s="13"/>
-      <c r="J17" s="14" t="s">
+      <c r="J17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="K17" s="14"/>
+      <c r="K17" s="22"/>
       <c r="L17" s="13"/>
-      <c r="M17" s="14" t="s">
+      <c r="M17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="N17" s="14"/>
+      <c r="N17" s="22"/>
       <c r="O17" s="13"/>
     </row>
     <row r="18" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="str">
+      <c r="A19" s="26" t="str">
         <f>A11</f>
         <v>Soil</v>
       </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="17" t="str">
+      <c r="B19" s="27"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="26" t="str">
         <f t="shared" ref="D19" si="0">D11</f>
         <v>Ground water</v>
       </c>
-      <c r="E19" s="18"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="17" t="str">
+      <c r="E19" s="27"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="26" t="str">
         <f t="shared" ref="G19" si="1">G11</f>
         <v>Surface water</v>
       </c>
-      <c r="H19" s="18"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="17" t="str">
+      <c r="H19" s="27"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="26" t="str">
         <f t="shared" ref="J19" si="2">J11</f>
         <v>Air</v>
       </c>
-      <c r="K19" s="18"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="17" t="str">
+      <c r="K19" s="27"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="26" t="str">
         <f t="shared" ref="M19" si="3">M11</f>
         <v>Sediment</v>
       </c>
-      <c r="N19" s="18"/>
-      <c r="O19" s="19"/>
+      <c r="N19" s="27"/>
+      <c r="O19" s="28"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="15"/>
+      <c r="B20" s="20"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E20" s="15"/>
+      <c r="E20" s="20"/>
       <c r="F20" s="4"/>
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H20" s="15"/>
+      <c r="H20" s="20"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="15" t="s">
+      <c r="J20" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="K20" s="15"/>
+      <c r="K20" s="20"/>
       <c r="L20" s="4"/>
-      <c r="M20" s="15" t="s">
+      <c r="M20" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="N20" s="15"/>
+      <c r="N20" s="20"/>
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="14"/>
+      <c r="B21" s="22"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="14"/>
+      <c r="E21" s="22"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="14" t="s">
+      <c r="G21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="14"/>
+      <c r="H21" s="22"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="14" t="s">
+      <c r="J21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="14"/>
+      <c r="K21" s="22"/>
       <c r="L21" s="4"/>
-      <c r="M21" s="14" t="s">
+      <c r="M21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="N21" s="14"/>
+      <c r="N21" s="22"/>
       <c r="O21" s="7"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="14"/>
+      <c r="B22" s="22"/>
       <c r="C22" s="13"/>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="14"/>
+      <c r="E22" s="22"/>
       <c r="F22" s="13"/>
-      <c r="G22" s="14" t="s">
+      <c r="G22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="H22" s="14"/>
+      <c r="H22" s="22"/>
       <c r="I22" s="13"/>
-      <c r="J22" s="14" t="s">
+      <c r="J22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="K22" s="14"/>
+      <c r="K22" s="22"/>
       <c r="L22" s="13"/>
-      <c r="M22" s="14" t="s">
+      <c r="M22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="N22" s="14"/>
+      <c r="N22" s="22"/>
       <c r="O22" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="74">
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="A6:O6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="K5:L5"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="F2:G2"/>
@@ -1961,73 +2028,6 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="K3:L3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="A6:O6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A18:O18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="M22:N22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -2052,136 +2052,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="20"/>
       <c r="C2" s="3"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="15"/>
+      <c r="G2" s="20"/>
       <c r="H2" s="3"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="24" t="s">
+      <c r="K2" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="24"/>
+      <c r="L2" s="21"/>
       <c r="M2" s="3"/>
       <c r="N2" s="1"/>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="14"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="9"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="14"/>
+      <c r="G3" s="22"/>
       <c r="H3" s="3"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="14"/>
+      <c r="L3" s="22"/>
       <c r="M3" s="9"/>
       <c r="N3" s="1"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="21"/>
+      <c r="G4" s="23"/>
       <c r="H4" s="3"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="21" t="s">
+      <c r="K4" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="21"/>
+      <c r="L4" s="23"/>
       <c r="M4" s="9"/>
       <c r="N4" s="1"/>
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="23"/>
+      <c r="B5" s="25"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="23"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="25"/>
       <c r="H5" s="3"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="23"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="25"/>
       <c r="M5" s="9"/>
       <c r="N5" s="1"/>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="20"/>
+      <c r="B7" s="29"/>
       <c r="C7" s="4"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -2197,10 +2197,10 @@
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="20"/>
+      <c r="B8" s="29"/>
       <c r="C8" s="4"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -2216,10 +2216,10 @@
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="20"/>
+      <c r="B9" s="29"/>
       <c r="C9" s="13"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -2235,337 +2235,395 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="17" t="s">
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="18"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="17" t="s">
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="H11" s="18"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="17" t="s">
+      <c r="H11" s="27"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="18"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="17" t="s">
+      <c r="K11" s="27"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="N11" s="18"/>
-      <c r="O11" s="19"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="28"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="15"/>
+      <c r="B12" s="20"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="15"/>
+      <c r="E12" s="20"/>
       <c r="F12" s="4"/>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="15"/>
+      <c r="H12" s="20"/>
       <c r="I12" s="4"/>
-      <c r="J12" s="15" t="s">
+      <c r="J12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="K12" s="15"/>
+      <c r="K12" s="20"/>
       <c r="L12" s="4"/>
-      <c r="M12" s="15" t="s">
+      <c r="M12" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="N12" s="15"/>
+      <c r="N12" s="20"/>
       <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="14"/>
+      <c r="B13" s="22"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="14"/>
+      <c r="E13" s="22"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="14"/>
+      <c r="H13" s="22"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="14" t="s">
+      <c r="J13" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="K13" s="14"/>
+      <c r="K13" s="22"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="14" t="s">
+      <c r="M13" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="N13" s="14"/>
+      <c r="N13" s="22"/>
       <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="14"/>
+      <c r="B14" s="22"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="14"/>
+      <c r="E14" s="22"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="14"/>
+      <c r="H14" s="22"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="14" t="s">
+      <c r="J14" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="14"/>
+      <c r="K14" s="22"/>
       <c r="L14" s="4"/>
-      <c r="M14" s="14" t="s">
+      <c r="M14" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="14"/>
+      <c r="N14" s="22"/>
       <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="14"/>
+      <c r="B15" s="22"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="14"/>
+      <c r="E15" s="22"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="14" t="s">
+      <c r="J15" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="14"/>
+      <c r="K15" s="22"/>
       <c r="L15" s="4"/>
-      <c r="M15" s="14" t="s">
+      <c r="M15" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="N15" s="14"/>
+      <c r="N15" s="22"/>
       <c r="O15" s="7"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="14"/>
+      <c r="B16" s="22"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
       <c r="I16" s="6"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
       <c r="L16" s="5"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
       <c r="O16" s="8"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="14"/>
+      <c r="B17" s="22"/>
       <c r="C17" s="13"/>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="14"/>
+      <c r="E17" s="22"/>
       <c r="F17" s="13"/>
-      <c r="G17" s="14" t="s">
+      <c r="G17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="14"/>
+      <c r="H17" s="22"/>
       <c r="I17" s="13"/>
-      <c r="J17" s="14" t="s">
+      <c r="J17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="K17" s="14"/>
+      <c r="K17" s="22"/>
       <c r="L17" s="13"/>
-      <c r="M17" s="14" t="s">
+      <c r="M17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="N17" s="14"/>
+      <c r="N17" s="22"/>
       <c r="O17" s="13"/>
     </row>
     <row r="18" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="str">
+      <c r="A19" s="26" t="str">
         <f>A11</f>
         <v>Soil</v>
       </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="17" t="str">
+      <c r="B19" s="27"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="26" t="str">
         <f t="shared" ref="D19" si="0">D11</f>
         <v>Ground water</v>
       </c>
-      <c r="E19" s="18"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="17" t="str">
+      <c r="E19" s="27"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="26" t="str">
         <f t="shared" ref="G19" si="1">G11</f>
         <v>Surface water</v>
       </c>
-      <c r="H19" s="18"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="17" t="str">
+      <c r="H19" s="27"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="26" t="str">
         <f t="shared" ref="J19" si="2">J11</f>
         <v>Air</v>
       </c>
-      <c r="K19" s="18"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="17" t="str">
+      <c r="K19" s="27"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="26" t="str">
         <f t="shared" ref="M19" si="3">M11</f>
         <v>Sediment</v>
       </c>
-      <c r="N19" s="18"/>
-      <c r="O19" s="19"/>
+      <c r="N19" s="27"/>
+      <c r="O19" s="28"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="15"/>
+      <c r="B20" s="20"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E20" s="15"/>
+      <c r="E20" s="20"/>
       <c r="F20" s="4"/>
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H20" s="15"/>
+      <c r="H20" s="20"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="15" t="s">
+      <c r="J20" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="K20" s="15"/>
+      <c r="K20" s="20"/>
       <c r="L20" s="4"/>
-      <c r="M20" s="15" t="s">
+      <c r="M20" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="N20" s="15"/>
+      <c r="N20" s="20"/>
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="14"/>
+      <c r="B21" s="22"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="14"/>
+      <c r="E21" s="22"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="14" t="s">
+      <c r="G21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="14"/>
+      <c r="H21" s="22"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="14" t="s">
+      <c r="J21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="14"/>
+      <c r="K21" s="22"/>
       <c r="L21" s="4"/>
-      <c r="M21" s="14" t="s">
+      <c r="M21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="N21" s="14"/>
+      <c r="N21" s="22"/>
       <c r="O21" s="7"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="14"/>
+      <c r="B22" s="22"/>
       <c r="C22" s="13"/>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="14"/>
+      <c r="E22" s="22"/>
       <c r="F22" s="13"/>
-      <c r="G22" s="14" t="s">
+      <c r="G22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="H22" s="14"/>
+      <c r="H22" s="22"/>
       <c r="I22" s="13"/>
-      <c r="J22" s="14" t="s">
+      <c r="J22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="K22" s="14"/>
+      <c r="K22" s="22"/>
       <c r="L22" s="13"/>
-      <c r="M22" s="14" t="s">
+      <c r="M22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="N22" s="14"/>
+      <c r="N22" s="22"/>
       <c r="O22" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="74">
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A6:O6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="M11:O11"/>
@@ -2582,64 +2640,6 @@
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="D13:E13"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A6:O6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="A18:O18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="D17:E17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -2662,9 +2662,9 @@
   <cols>
     <col min="1" max="1" width="18.42578125" customWidth="1"/>
     <col min="2" max="2" width="4.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2687,2795 +2687,2795 @@
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="28"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="17"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="11"/>
       <c r="B3" s="11"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="28"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="17"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="28"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="17"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="28"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="17"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="28"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="17"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="28"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="17"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="28"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="17"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="28"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="17"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="11"/>
       <c r="B10" s="11"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="28"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="17"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="28"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="17"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="28"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="17"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="28"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="17"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="11"/>
       <c r="B14" s="11"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="28"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="17"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="11"/>
       <c r="B15" s="11"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="28"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="17"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="11"/>
       <c r="B16" s="11"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="28"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="17"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="28"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="17"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
       <c r="B18" s="11"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="28"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="17"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
       <c r="B19" s="11"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="28"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="17"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="11"/>
       <c r="B20" s="11"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="28"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="17"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="11"/>
       <c r="B21" s="11"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="28"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="17"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="11"/>
       <c r="B22" s="11"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="28"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="17"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="11"/>
       <c r="B23" s="11"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="28"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="17"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="11"/>
       <c r="B24" s="11"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="28"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="17"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="11"/>
       <c r="B25" s="11"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="28"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="17"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
       <c r="B26" s="11"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="28"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="17"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="11"/>
       <c r="B27" s="11"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="28"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="17"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="11"/>
       <c r="B28" s="11"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="28"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="17"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="11"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="28"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="17"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="11"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="28"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="17"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="11"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="28"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="17"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="11"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="28"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="17"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
       <c r="B33" s="11"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="28"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="17"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
       <c r="B34" s="11"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="28"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="17"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="11"/>
       <c r="B35" s="11"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="28"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="17"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
       <c r="B36" s="11"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="26"/>
-      <c r="E36" s="28"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="17"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="11"/>
       <c r="B37" s="11"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="28"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="17"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="11"/>
       <c r="B38" s="11"/>
-      <c r="C38" s="26"/>
-      <c r="D38" s="26"/>
-      <c r="E38" s="28"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="17"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="11"/>
       <c r="B39" s="11"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="28"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="17"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="11"/>
       <c r="B40" s="11"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="28"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="17"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="11"/>
       <c r="B41" s="11"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="28"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="17"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="11"/>
       <c r="B42" s="11"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="28"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="17"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="11"/>
       <c r="B43" s="11"/>
-      <c r="C43" s="26"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="28"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="17"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="11"/>
       <c r="B44" s="11"/>
-      <c r="C44" s="26"/>
-      <c r="D44" s="26"/>
-      <c r="E44" s="28"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="17"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="11"/>
       <c r="B45" s="11"/>
-      <c r="C45" s="26"/>
-      <c r="D45" s="26"/>
-      <c r="E45" s="28"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="17"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="11"/>
       <c r="B46" s="11"/>
-      <c r="C46" s="26"/>
-      <c r="D46" s="26"/>
-      <c r="E46" s="28"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="17"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="11"/>
       <c r="B47" s="11"/>
-      <c r="C47" s="26"/>
-      <c r="D47" s="26"/>
-      <c r="E47" s="28"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="17"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="11"/>
       <c r="B48" s="11"/>
-      <c r="C48" s="26"/>
-      <c r="D48" s="26"/>
-      <c r="E48" s="28"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="17"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="11"/>
       <c r="B49" s="11"/>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="28"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="17"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="11"/>
       <c r="B50" s="11"/>
-      <c r="C50" s="26"/>
-      <c r="D50" s="26"/>
-      <c r="E50" s="28"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="17"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="11"/>
       <c r="B51" s="11"/>
-      <c r="C51" s="26"/>
-      <c r="D51" s="26"/>
-      <c r="E51" s="28"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="17"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="11"/>
       <c r="B52" s="11"/>
-      <c r="C52" s="26"/>
-      <c r="D52" s="26"/>
-      <c r="E52" s="28"/>
+      <c r="C52" s="15"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="17"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="11"/>
       <c r="B53" s="11"/>
-      <c r="C53" s="26"/>
-      <c r="D53" s="26"/>
-      <c r="E53" s="28"/>
+      <c r="C53" s="15"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="17"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="11"/>
       <c r="B54" s="11"/>
-      <c r="C54" s="26"/>
-      <c r="D54" s="26"/>
-      <c r="E54" s="28"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="17"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="11"/>
       <c r="B55" s="11"/>
-      <c r="C55" s="26"/>
-      <c r="D55" s="26"/>
-      <c r="E55" s="28"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="17"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="11"/>
       <c r="B56" s="11"/>
-      <c r="C56" s="26"/>
-      <c r="D56" s="26"/>
-      <c r="E56" s="28"/>
+      <c r="C56" s="15"/>
+      <c r="D56" s="15"/>
+      <c r="E56" s="17"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="11"/>
       <c r="B57" s="11"/>
-      <c r="C57" s="26"/>
-      <c r="D57" s="26"/>
-      <c r="E57" s="28"/>
+      <c r="C57" s="15"/>
+      <c r="D57" s="15"/>
+      <c r="E57" s="17"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="11"/>
       <c r="B58" s="11"/>
-      <c r="C58" s="26"/>
-      <c r="D58" s="26"/>
-      <c r="E58" s="28"/>
+      <c r="C58" s="15"/>
+      <c r="D58" s="15"/>
+      <c r="E58" s="17"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="11"/>
       <c r="B59" s="11"/>
-      <c r="C59" s="26"/>
-      <c r="D59" s="26"/>
-      <c r="E59" s="28"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="17"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="11"/>
       <c r="B60" s="11"/>
-      <c r="C60" s="26"/>
-      <c r="D60" s="26"/>
-      <c r="E60" s="28"/>
+      <c r="C60" s="15"/>
+      <c r="D60" s="15"/>
+      <c r="E60" s="17"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="11"/>
       <c r="B61" s="11"/>
-      <c r="C61" s="26"/>
-      <c r="D61" s="26"/>
-      <c r="E61" s="28"/>
+      <c r="C61" s="15"/>
+      <c r="D61" s="15"/>
+      <c r="E61" s="17"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="11"/>
       <c r="B62" s="11"/>
-      <c r="C62" s="26"/>
-      <c r="D62" s="26"/>
-      <c r="E62" s="28"/>
+      <c r="C62" s="15"/>
+      <c r="D62" s="15"/>
+      <c r="E62" s="17"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="11"/>
       <c r="B63" s="11"/>
-      <c r="C63" s="26"/>
-      <c r="D63" s="26"/>
-      <c r="E63" s="28"/>
+      <c r="C63" s="15"/>
+      <c r="D63" s="15"/>
+      <c r="E63" s="17"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="11"/>
       <c r="B64" s="11"/>
-      <c r="C64" s="26"/>
-      <c r="D64" s="26"/>
-      <c r="E64" s="28"/>
+      <c r="C64" s="15"/>
+      <c r="D64" s="15"/>
+      <c r="E64" s="17"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="11"/>
       <c r="B65" s="11"/>
-      <c r="C65" s="26"/>
-      <c r="D65" s="26"/>
-      <c r="E65" s="28"/>
+      <c r="C65" s="15"/>
+      <c r="D65" s="15"/>
+      <c r="E65" s="17"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="11"/>
       <c r="B66" s="11"/>
-      <c r="C66" s="26"/>
-      <c r="D66" s="26"/>
-      <c r="E66" s="28"/>
+      <c r="C66" s="15"/>
+      <c r="D66" s="15"/>
+      <c r="E66" s="17"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="11"/>
       <c r="B67" s="11"/>
-      <c r="C67" s="26"/>
-      <c r="D67" s="26"/>
-      <c r="E67" s="28"/>
+      <c r="C67" s="15"/>
+      <c r="D67" s="15"/>
+      <c r="E67" s="17"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="11"/>
       <c r="B68" s="11"/>
-      <c r="C68" s="26"/>
-      <c r="D68" s="26"/>
-      <c r="E68" s="28"/>
+      <c r="C68" s="15"/>
+      <c r="D68" s="15"/>
+      <c r="E68" s="17"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="11"/>
       <c r="B69" s="11"/>
-      <c r="C69" s="26"/>
-      <c r="D69" s="26"/>
-      <c r="E69" s="28"/>
+      <c r="C69" s="15"/>
+      <c r="D69" s="15"/>
+      <c r="E69" s="17"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="11"/>
       <c r="B70" s="11"/>
-      <c r="C70" s="26"/>
-      <c r="D70" s="26"/>
-      <c r="E70" s="28"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="17"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="11"/>
       <c r="B71" s="11"/>
-      <c r="C71" s="26"/>
-      <c r="D71" s="26"/>
-      <c r="E71" s="28"/>
+      <c r="C71" s="15"/>
+      <c r="D71" s="15"/>
+      <c r="E71" s="17"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="11"/>
       <c r="B72" s="11"/>
-      <c r="C72" s="26"/>
-      <c r="D72" s="26"/>
-      <c r="E72" s="28"/>
+      <c r="C72" s="15"/>
+      <c r="D72" s="15"/>
+      <c r="E72" s="17"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="11"/>
       <c r="B73" s="11"/>
-      <c r="C73" s="26"/>
-      <c r="D73" s="26"/>
-      <c r="E73" s="28"/>
+      <c r="C73" s="15"/>
+      <c r="D73" s="15"/>
+      <c r="E73" s="17"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="11"/>
       <c r="B74" s="11"/>
-      <c r="C74" s="26"/>
-      <c r="D74" s="26"/>
-      <c r="E74" s="28"/>
+      <c r="C74" s="15"/>
+      <c r="D74" s="15"/>
+      <c r="E74" s="17"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="11"/>
       <c r="B75" s="11"/>
-      <c r="C75" s="26"/>
-      <c r="D75" s="26"/>
-      <c r="E75" s="28"/>
+      <c r="C75" s="15"/>
+      <c r="D75" s="15"/>
+      <c r="E75" s="17"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="11"/>
       <c r="B76" s="11"/>
-      <c r="C76" s="26"/>
-      <c r="D76" s="26"/>
-      <c r="E76" s="28"/>
+      <c r="C76" s="15"/>
+      <c r="D76" s="15"/>
+      <c r="E76" s="17"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="11"/>
       <c r="B77" s="11"/>
-      <c r="C77" s="26"/>
-      <c r="D77" s="26"/>
-      <c r="E77" s="28"/>
+      <c r="C77" s="15"/>
+      <c r="D77" s="15"/>
+      <c r="E77" s="17"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="11"/>
       <c r="B78" s="11"/>
-      <c r="C78" s="26"/>
-      <c r="D78" s="26"/>
-      <c r="E78" s="28"/>
+      <c r="C78" s="15"/>
+      <c r="D78" s="15"/>
+      <c r="E78" s="17"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="11"/>
       <c r="B79" s="11"/>
-      <c r="C79" s="26"/>
-      <c r="D79" s="26"/>
-      <c r="E79" s="28"/>
+      <c r="C79" s="15"/>
+      <c r="D79" s="15"/>
+      <c r="E79" s="17"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="11"/>
       <c r="B80" s="11"/>
-      <c r="C80" s="26"/>
-      <c r="D80" s="26"/>
-      <c r="E80" s="28"/>
+      <c r="C80" s="15"/>
+      <c r="D80" s="15"/>
+      <c r="E80" s="17"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="11"/>
       <c r="B81" s="11"/>
-      <c r="C81" s="26"/>
-      <c r="D81" s="26"/>
-      <c r="E81" s="28"/>
+      <c r="C81" s="15"/>
+      <c r="D81" s="15"/>
+      <c r="E81" s="17"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="11"/>
       <c r="B82" s="11"/>
-      <c r="C82" s="26"/>
-      <c r="D82" s="26"/>
-      <c r="E82" s="28"/>
+      <c r="C82" s="15"/>
+      <c r="D82" s="15"/>
+      <c r="E82" s="17"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="11"/>
       <c r="B83" s="11"/>
-      <c r="C83" s="26"/>
-      <c r="D83" s="26"/>
-      <c r="E83" s="28"/>
+      <c r="C83" s="15"/>
+      <c r="D83" s="15"/>
+      <c r="E83" s="17"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="11"/>
       <c r="B84" s="11"/>
-      <c r="C84" s="26"/>
-      <c r="D84" s="26"/>
-      <c r="E84" s="28"/>
+      <c r="C84" s="15"/>
+      <c r="D84" s="15"/>
+      <c r="E84" s="17"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="11"/>
       <c r="B85" s="11"/>
-      <c r="C85" s="26"/>
-      <c r="D85" s="26"/>
-      <c r="E85" s="28"/>
+      <c r="C85" s="15"/>
+      <c r="D85" s="15"/>
+      <c r="E85" s="17"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="11"/>
       <c r="B86" s="11"/>
-      <c r="C86" s="26"/>
-      <c r="D86" s="26"/>
-      <c r="E86" s="28"/>
+      <c r="C86" s="15"/>
+      <c r="D86" s="15"/>
+      <c r="E86" s="17"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="11"/>
       <c r="B87" s="11"/>
-      <c r="C87" s="26"/>
-      <c r="D87" s="26"/>
-      <c r="E87" s="28"/>
+      <c r="C87" s="15"/>
+      <c r="D87" s="15"/>
+      <c r="E87" s="17"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="11"/>
       <c r="B88" s="11"/>
-      <c r="C88" s="26"/>
-      <c r="D88" s="26"/>
-      <c r="E88" s="28"/>
+      <c r="C88" s="15"/>
+      <c r="D88" s="15"/>
+      <c r="E88" s="17"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="11"/>
       <c r="B89" s="11"/>
-      <c r="C89" s="26"/>
-      <c r="D89" s="26"/>
-      <c r="E89" s="28"/>
+      <c r="C89" s="15"/>
+      <c r="D89" s="15"/>
+      <c r="E89" s="17"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="11"/>
       <c r="B90" s="11"/>
-      <c r="C90" s="26"/>
-      <c r="D90" s="26"/>
-      <c r="E90" s="28"/>
+      <c r="C90" s="15"/>
+      <c r="D90" s="15"/>
+      <c r="E90" s="17"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="11"/>
       <c r="B91" s="11"/>
-      <c r="C91" s="26"/>
-      <c r="D91" s="26"/>
-      <c r="E91" s="28"/>
+      <c r="C91" s="15"/>
+      <c r="D91" s="15"/>
+      <c r="E91" s="17"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="11"/>
       <c r="B92" s="11"/>
-      <c r="C92" s="26"/>
-      <c r="D92" s="26"/>
-      <c r="E92" s="28"/>
+      <c r="C92" s="15"/>
+      <c r="D92" s="15"/>
+      <c r="E92" s="17"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="11"/>
       <c r="B93" s="11"/>
-      <c r="C93" s="26"/>
-      <c r="D93" s="26"/>
-      <c r="E93" s="28"/>
+      <c r="C93" s="15"/>
+      <c r="D93" s="15"/>
+      <c r="E93" s="17"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="11"/>
       <c r="B94" s="11"/>
-      <c r="C94" s="26"/>
-      <c r="D94" s="26"/>
-      <c r="E94" s="28"/>
+      <c r="C94" s="15"/>
+      <c r="D94" s="15"/>
+      <c r="E94" s="17"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="11"/>
       <c r="B95" s="11"/>
-      <c r="C95" s="26"/>
-      <c r="D95" s="26"/>
-      <c r="E95" s="28"/>
+      <c r="C95" s="15"/>
+      <c r="D95" s="15"/>
+      <c r="E95" s="17"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="11"/>
       <c r="B96" s="11"/>
-      <c r="C96" s="26"/>
-      <c r="D96" s="26"/>
-      <c r="E96" s="28"/>
+      <c r="C96" s="15"/>
+      <c r="D96" s="15"/>
+      <c r="E96" s="17"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="11"/>
       <c r="B97" s="11"/>
-      <c r="C97" s="26"/>
-      <c r="D97" s="26"/>
-      <c r="E97" s="28"/>
+      <c r="C97" s="15"/>
+      <c r="D97" s="15"/>
+      <c r="E97" s="17"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="11"/>
       <c r="B98" s="11"/>
-      <c r="C98" s="26"/>
-      <c r="D98" s="26"/>
-      <c r="E98" s="28"/>
+      <c r="C98" s="15"/>
+      <c r="D98" s="15"/>
+      <c r="E98" s="17"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="11"/>
       <c r="B99" s="11"/>
-      <c r="C99" s="26"/>
-      <c r="D99" s="26"/>
-      <c r="E99" s="28"/>
+      <c r="C99" s="15"/>
+      <c r="D99" s="15"/>
+      <c r="E99" s="17"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="11"/>
       <c r="B100" s="11"/>
-      <c r="C100" s="26"/>
-      <c r="D100" s="26"/>
-      <c r="E100" s="28"/>
+      <c r="C100" s="15"/>
+      <c r="D100" s="15"/>
+      <c r="E100" s="17"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="11"/>
       <c r="B101" s="11"/>
-      <c r="C101" s="26"/>
-      <c r="D101" s="26"/>
-      <c r="E101" s="28"/>
+      <c r="C101" s="15"/>
+      <c r="D101" s="15"/>
+      <c r="E101" s="17"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="11"/>
       <c r="B102" s="11"/>
-      <c r="C102" s="26"/>
-      <c r="D102" s="26"/>
-      <c r="E102" s="28"/>
+      <c r="C102" s="15"/>
+      <c r="D102" s="15"/>
+      <c r="E102" s="17"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="11"/>
       <c r="B103" s="11"/>
-      <c r="C103" s="26"/>
-      <c r="D103" s="26"/>
-      <c r="E103" s="28"/>
+      <c r="C103" s="15"/>
+      <c r="D103" s="15"/>
+      <c r="E103" s="17"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="11"/>
       <c r="B104" s="11"/>
-      <c r="C104" s="26"/>
-      <c r="D104" s="26"/>
-      <c r="E104" s="28"/>
+      <c r="C104" s="15"/>
+      <c r="D104" s="15"/>
+      <c r="E104" s="17"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="11"/>
       <c r="B105" s="11"/>
-      <c r="C105" s="26"/>
-      <c r="D105" s="26"/>
-      <c r="E105" s="28"/>
+      <c r="C105" s="15"/>
+      <c r="D105" s="15"/>
+      <c r="E105" s="17"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="11"/>
       <c r="B106" s="11"/>
-      <c r="C106" s="26"/>
-      <c r="D106" s="26"/>
-      <c r="E106" s="28"/>
+      <c r="C106" s="15"/>
+      <c r="D106" s="15"/>
+      <c r="E106" s="17"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="11"/>
       <c r="B107" s="11"/>
-      <c r="C107" s="26"/>
-      <c r="D107" s="26"/>
-      <c r="E107" s="28"/>
+      <c r="C107" s="15"/>
+      <c r="D107" s="15"/>
+      <c r="E107" s="17"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="11"/>
       <c r="B108" s="11"/>
-      <c r="C108" s="26"/>
-      <c r="D108" s="26"/>
-      <c r="E108" s="28"/>
+      <c r="C108" s="15"/>
+      <c r="D108" s="15"/>
+      <c r="E108" s="17"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="11"/>
       <c r="B109" s="11"/>
-      <c r="C109" s="26"/>
-      <c r="D109" s="26"/>
-      <c r="E109" s="28"/>
+      <c r="C109" s="15"/>
+      <c r="D109" s="15"/>
+      <c r="E109" s="17"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="11"/>
       <c r="B110" s="11"/>
-      <c r="C110" s="26"/>
-      <c r="D110" s="26"/>
-      <c r="E110" s="28"/>
+      <c r="C110" s="15"/>
+      <c r="D110" s="15"/>
+      <c r="E110" s="17"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="11"/>
       <c r="B111" s="11"/>
-      <c r="C111" s="26"/>
-      <c r="D111" s="26"/>
-      <c r="E111" s="28"/>
+      <c r="C111" s="15"/>
+      <c r="D111" s="15"/>
+      <c r="E111" s="17"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="11"/>
       <c r="B112" s="11"/>
-      <c r="C112" s="26"/>
-      <c r="D112" s="26"/>
-      <c r="E112" s="28"/>
+      <c r="C112" s="15"/>
+      <c r="D112" s="15"/>
+      <c r="E112" s="17"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="11"/>
       <c r="B113" s="11"/>
-      <c r="C113" s="26"/>
-      <c r="D113" s="26"/>
-      <c r="E113" s="28"/>
+      <c r="C113" s="15"/>
+      <c r="D113" s="15"/>
+      <c r="E113" s="17"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="11"/>
       <c r="B114" s="11"/>
-      <c r="C114" s="26"/>
-      <c r="D114" s="26"/>
-      <c r="E114" s="28"/>
+      <c r="C114" s="15"/>
+      <c r="D114" s="15"/>
+      <c r="E114" s="17"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="11"/>
       <c r="B115" s="11"/>
-      <c r="C115" s="26"/>
-      <c r="D115" s="26"/>
-      <c r="E115" s="28"/>
+      <c r="C115" s="15"/>
+      <c r="D115" s="15"/>
+      <c r="E115" s="17"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="11"/>
       <c r="B116" s="11"/>
-      <c r="C116" s="26"/>
-      <c r="D116" s="26"/>
-      <c r="E116" s="28"/>
+      <c r="C116" s="15"/>
+      <c r="D116" s="15"/>
+      <c r="E116" s="17"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="11"/>
       <c r="B117" s="11"/>
-      <c r="C117" s="26"/>
-      <c r="D117" s="26"/>
-      <c r="E117" s="28"/>
+      <c r="C117" s="15"/>
+      <c r="D117" s="15"/>
+      <c r="E117" s="17"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="11"/>
       <c r="B118" s="11"/>
-      <c r="C118" s="26"/>
-      <c r="D118" s="26"/>
-      <c r="E118" s="28"/>
+      <c r="C118" s="15"/>
+      <c r="D118" s="15"/>
+      <c r="E118" s="17"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="11"/>
       <c r="B119" s="11"/>
-      <c r="C119" s="26"/>
-      <c r="D119" s="26"/>
-      <c r="E119" s="28"/>
+      <c r="C119" s="15"/>
+      <c r="D119" s="15"/>
+      <c r="E119" s="17"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="11"/>
       <c r="B120" s="11"/>
-      <c r="C120" s="26"/>
-      <c r="D120" s="26"/>
-      <c r="E120" s="28"/>
+      <c r="C120" s="15"/>
+      <c r="D120" s="15"/>
+      <c r="E120" s="17"/>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="11"/>
       <c r="B121" s="11"/>
-      <c r="C121" s="26"/>
-      <c r="D121" s="26"/>
-      <c r="E121" s="28"/>
+      <c r="C121" s="15"/>
+      <c r="D121" s="15"/>
+      <c r="E121" s="17"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="11"/>
       <c r="B122" s="11"/>
-      <c r="C122" s="26"/>
-      <c r="D122" s="26"/>
-      <c r="E122" s="28"/>
+      <c r="C122" s="15"/>
+      <c r="D122" s="15"/>
+      <c r="E122" s="17"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="11"/>
       <c r="B123" s="11"/>
-      <c r="C123" s="26"/>
-      <c r="D123" s="26"/>
-      <c r="E123" s="28"/>
+      <c r="C123" s="15"/>
+      <c r="D123" s="15"/>
+      <c r="E123" s="17"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="11"/>
       <c r="B124" s="11"/>
-      <c r="C124" s="26"/>
-      <c r="D124" s="26"/>
-      <c r="E124" s="28"/>
+      <c r="C124" s="15"/>
+      <c r="D124" s="15"/>
+      <c r="E124" s="17"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="11"/>
       <c r="B125" s="11"/>
-      <c r="C125" s="26"/>
-      <c r="D125" s="26"/>
-      <c r="E125" s="28"/>
+      <c r="C125" s="15"/>
+      <c r="D125" s="15"/>
+      <c r="E125" s="17"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="11"/>
       <c r="B126" s="11"/>
-      <c r="C126" s="26"/>
-      <c r="D126" s="26"/>
-      <c r="E126" s="28"/>
+      <c r="C126" s="15"/>
+      <c r="D126" s="15"/>
+      <c r="E126" s="17"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="11"/>
       <c r="B127" s="11"/>
-      <c r="C127" s="26"/>
-      <c r="D127" s="26"/>
-      <c r="E127" s="28"/>
+      <c r="C127" s="15"/>
+      <c r="D127" s="15"/>
+      <c r="E127" s="17"/>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="11"/>
       <c r="B128" s="11"/>
-      <c r="C128" s="26"/>
-      <c r="D128" s="26"/>
-      <c r="E128" s="28"/>
+      <c r="C128" s="15"/>
+      <c r="D128" s="15"/>
+      <c r="E128" s="17"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="11"/>
       <c r="B129" s="11"/>
-      <c r="C129" s="26"/>
-      <c r="D129" s="26"/>
-      <c r="E129" s="28"/>
+      <c r="C129" s="15"/>
+      <c r="D129" s="15"/>
+      <c r="E129" s="17"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="11"/>
       <c r="B130" s="11"/>
-      <c r="C130" s="26"/>
-      <c r="D130" s="26"/>
-      <c r="E130" s="28"/>
+      <c r="C130" s="15"/>
+      <c r="D130" s="15"/>
+      <c r="E130" s="17"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="11"/>
       <c r="B131" s="11"/>
-      <c r="C131" s="26"/>
-      <c r="D131" s="26"/>
-      <c r="E131" s="28"/>
+      <c r="C131" s="15"/>
+      <c r="D131" s="15"/>
+      <c r="E131" s="17"/>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="11"/>
       <c r="B132" s="11"/>
-      <c r="C132" s="26"/>
-      <c r="D132" s="26"/>
-      <c r="E132" s="28"/>
+      <c r="C132" s="15"/>
+      <c r="D132" s="15"/>
+      <c r="E132" s="17"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="11"/>
       <c r="B133" s="11"/>
-      <c r="C133" s="26"/>
-      <c r="D133" s="26"/>
-      <c r="E133" s="28"/>
+      <c r="C133" s="15"/>
+      <c r="D133" s="15"/>
+      <c r="E133" s="17"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="11"/>
       <c r="B134" s="11"/>
-      <c r="C134" s="26"/>
-      <c r="D134" s="26"/>
-      <c r="E134" s="28"/>
+      <c r="C134" s="15"/>
+      <c r="D134" s="15"/>
+      <c r="E134" s="17"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="11"/>
       <c r="B135" s="11"/>
-      <c r="C135" s="26"/>
-      <c r="D135" s="26"/>
-      <c r="E135" s="28"/>
+      <c r="C135" s="15"/>
+      <c r="D135" s="15"/>
+      <c r="E135" s="17"/>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="11"/>
       <c r="B136" s="11"/>
-      <c r="C136" s="26"/>
-      <c r="D136" s="26"/>
-      <c r="E136" s="28"/>
+      <c r="C136" s="15"/>
+      <c r="D136" s="15"/>
+      <c r="E136" s="17"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="11"/>
       <c r="B137" s="11"/>
-      <c r="C137" s="26"/>
-      <c r="D137" s="26"/>
-      <c r="E137" s="28"/>
+      <c r="C137" s="15"/>
+      <c r="D137" s="15"/>
+      <c r="E137" s="17"/>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="11"/>
       <c r="B138" s="11"/>
-      <c r="C138" s="26"/>
-      <c r="D138" s="26"/>
-      <c r="E138" s="28"/>
+      <c r="C138" s="15"/>
+      <c r="D138" s="15"/>
+      <c r="E138" s="17"/>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="11"/>
       <c r="B139" s="11"/>
-      <c r="C139" s="26"/>
-      <c r="D139" s="26"/>
-      <c r="E139" s="28"/>
+      <c r="C139" s="15"/>
+      <c r="D139" s="15"/>
+      <c r="E139" s="17"/>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="11"/>
       <c r="B140" s="11"/>
-      <c r="C140" s="26"/>
-      <c r="D140" s="26"/>
-      <c r="E140" s="28"/>
+      <c r="C140" s="15"/>
+      <c r="D140" s="15"/>
+      <c r="E140" s="17"/>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="11"/>
       <c r="B141" s="11"/>
-      <c r="C141" s="26"/>
-      <c r="D141" s="26"/>
-      <c r="E141" s="28"/>
+      <c r="C141" s="15"/>
+      <c r="D141" s="15"/>
+      <c r="E141" s="17"/>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="11"/>
       <c r="B142" s="11"/>
-      <c r="C142" s="26"/>
-      <c r="D142" s="26"/>
-      <c r="E142" s="28"/>
+      <c r="C142" s="15"/>
+      <c r="D142" s="15"/>
+      <c r="E142" s="17"/>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="11"/>
       <c r="B143" s="11"/>
-      <c r="C143" s="26"/>
-      <c r="D143" s="26"/>
-      <c r="E143" s="28"/>
+      <c r="C143" s="15"/>
+      <c r="D143" s="15"/>
+      <c r="E143" s="17"/>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="11"/>
       <c r="B144" s="11"/>
-      <c r="C144" s="26"/>
-      <c r="D144" s="26"/>
-      <c r="E144" s="28"/>
+      <c r="C144" s="15"/>
+      <c r="D144" s="15"/>
+      <c r="E144" s="17"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="11"/>
       <c r="B145" s="11"/>
-      <c r="C145" s="26"/>
-      <c r="D145" s="26"/>
-      <c r="E145" s="28"/>
+      <c r="C145" s="15"/>
+      <c r="D145" s="15"/>
+      <c r="E145" s="17"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="11"/>
       <c r="B146" s="11"/>
-      <c r="C146" s="26"/>
-      <c r="D146" s="26"/>
-      <c r="E146" s="28"/>
+      <c r="C146" s="15"/>
+      <c r="D146" s="15"/>
+      <c r="E146" s="17"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="11"/>
       <c r="B147" s="11"/>
-      <c r="C147" s="26"/>
-      <c r="D147" s="26"/>
-      <c r="E147" s="28"/>
+      <c r="C147" s="15"/>
+      <c r="D147" s="15"/>
+      <c r="E147" s="17"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="11"/>
       <c r="B148" s="11"/>
-      <c r="C148" s="26"/>
-      <c r="D148" s="26"/>
-      <c r="E148" s="28"/>
+      <c r="C148" s="15"/>
+      <c r="D148" s="15"/>
+      <c r="E148" s="17"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="11"/>
       <c r="B149" s="11"/>
-      <c r="C149" s="26"/>
-      <c r="D149" s="26"/>
-      <c r="E149" s="28"/>
+      <c r="C149" s="15"/>
+      <c r="D149" s="15"/>
+      <c r="E149" s="17"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="11"/>
       <c r="B150" s="11"/>
-      <c r="C150" s="26"/>
-      <c r="D150" s="26"/>
-      <c r="E150" s="28"/>
+      <c r="C150" s="15"/>
+      <c r="D150" s="15"/>
+      <c r="E150" s="17"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="11"/>
       <c r="B151" s="11"/>
-      <c r="C151" s="26"/>
-      <c r="D151" s="26"/>
-      <c r="E151" s="28"/>
+      <c r="C151" s="15"/>
+      <c r="D151" s="15"/>
+      <c r="E151" s="17"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="11"/>
       <c r="B152" s="11"/>
-      <c r="C152" s="26"/>
-      <c r="D152" s="26"/>
-      <c r="E152" s="28"/>
+      <c r="C152" s="15"/>
+      <c r="D152" s="15"/>
+      <c r="E152" s="17"/>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="11"/>
       <c r="B153" s="11"/>
-      <c r="C153" s="26"/>
-      <c r="D153" s="26"/>
-      <c r="E153" s="28"/>
+      <c r="C153" s="15"/>
+      <c r="D153" s="15"/>
+      <c r="E153" s="17"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="11"/>
       <c r="B154" s="11"/>
-      <c r="C154" s="26"/>
-      <c r="D154" s="26"/>
-      <c r="E154" s="28"/>
+      <c r="C154" s="15"/>
+      <c r="D154" s="15"/>
+      <c r="E154" s="17"/>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="11"/>
       <c r="B155" s="11"/>
-      <c r="C155" s="26"/>
-      <c r="D155" s="26"/>
-      <c r="E155" s="28"/>
+      <c r="C155" s="15"/>
+      <c r="D155" s="15"/>
+      <c r="E155" s="17"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="11"/>
       <c r="B156" s="11"/>
-      <c r="C156" s="26"/>
-      <c r="D156" s="26"/>
-      <c r="E156" s="28"/>
+      <c r="C156" s="15"/>
+      <c r="D156" s="15"/>
+      <c r="E156" s="17"/>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="11"/>
       <c r="B157" s="11"/>
-      <c r="C157" s="26"/>
-      <c r="D157" s="26"/>
-      <c r="E157" s="28"/>
+      <c r="C157" s="15"/>
+      <c r="D157" s="15"/>
+      <c r="E157" s="17"/>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="11"/>
       <c r="B158" s="11"/>
-      <c r="C158" s="26"/>
-      <c r="D158" s="26"/>
-      <c r="E158" s="28"/>
+      <c r="C158" s="15"/>
+      <c r="D158" s="15"/>
+      <c r="E158" s="17"/>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="11"/>
       <c r="B159" s="11"/>
-      <c r="C159" s="26"/>
-      <c r="D159" s="26"/>
-      <c r="E159" s="28"/>
+      <c r="C159" s="15"/>
+      <c r="D159" s="15"/>
+      <c r="E159" s="17"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="11"/>
       <c r="B160" s="11"/>
-      <c r="C160" s="26"/>
-      <c r="D160" s="26"/>
-      <c r="E160" s="28"/>
+      <c r="C160" s="15"/>
+      <c r="D160" s="15"/>
+      <c r="E160" s="17"/>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="11"/>
       <c r="B161" s="11"/>
-      <c r="C161" s="26"/>
-      <c r="D161" s="26"/>
-      <c r="E161" s="28"/>
+      <c r="C161" s="15"/>
+      <c r="D161" s="15"/>
+      <c r="E161" s="17"/>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="11"/>
       <c r="B162" s="11"/>
-      <c r="C162" s="26"/>
-      <c r="D162" s="26"/>
-      <c r="E162" s="28"/>
+      <c r="C162" s="15"/>
+      <c r="D162" s="15"/>
+      <c r="E162" s="17"/>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="11"/>
       <c r="B163" s="11"/>
-      <c r="C163" s="26"/>
-      <c r="D163" s="26"/>
-      <c r="E163" s="28"/>
+      <c r="C163" s="15"/>
+      <c r="D163" s="15"/>
+      <c r="E163" s="17"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="11"/>
       <c r="B164" s="11"/>
-      <c r="C164" s="26"/>
-      <c r="D164" s="26"/>
-      <c r="E164" s="28"/>
+      <c r="C164" s="15"/>
+      <c r="D164" s="15"/>
+      <c r="E164" s="17"/>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="11"/>
       <c r="B165" s="11"/>
-      <c r="C165" s="26"/>
-      <c r="D165" s="26"/>
-      <c r="E165" s="28"/>
+      <c r="C165" s="15"/>
+      <c r="D165" s="15"/>
+      <c r="E165" s="17"/>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="11"/>
       <c r="B166" s="11"/>
-      <c r="C166" s="26"/>
-      <c r="D166" s="26"/>
-      <c r="E166" s="28"/>
+      <c r="C166" s="15"/>
+      <c r="D166" s="15"/>
+      <c r="E166" s="17"/>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="11"/>
       <c r="B167" s="11"/>
-      <c r="C167" s="26"/>
-      <c r="D167" s="26"/>
-      <c r="E167" s="28"/>
+      <c r="C167" s="15"/>
+      <c r="D167" s="15"/>
+      <c r="E167" s="17"/>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="11"/>
       <c r="B168" s="11"/>
-      <c r="C168" s="26"/>
-      <c r="D168" s="26"/>
-      <c r="E168" s="28"/>
+      <c r="C168" s="15"/>
+      <c r="D168" s="15"/>
+      <c r="E168" s="17"/>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="11"/>
       <c r="B169" s="11"/>
-      <c r="C169" s="26"/>
-      <c r="D169" s="26"/>
-      <c r="E169" s="28"/>
+      <c r="C169" s="15"/>
+      <c r="D169" s="15"/>
+      <c r="E169" s="17"/>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="11"/>
       <c r="B170" s="11"/>
-      <c r="C170" s="26"/>
-      <c r="D170" s="26"/>
-      <c r="E170" s="28"/>
+      <c r="C170" s="15"/>
+      <c r="D170" s="15"/>
+      <c r="E170" s="17"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="11"/>
       <c r="B171" s="11"/>
-      <c r="C171" s="26"/>
-      <c r="D171" s="26"/>
-      <c r="E171" s="28"/>
+      <c r="C171" s="15"/>
+      <c r="D171" s="15"/>
+      <c r="E171" s="17"/>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="11"/>
       <c r="B172" s="11"/>
-      <c r="C172" s="26"/>
-      <c r="D172" s="26"/>
-      <c r="E172" s="28"/>
+      <c r="C172" s="15"/>
+      <c r="D172" s="15"/>
+      <c r="E172" s="17"/>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="11"/>
       <c r="B173" s="11"/>
-      <c r="C173" s="26"/>
-      <c r="D173" s="26"/>
-      <c r="E173" s="28"/>
+      <c r="C173" s="15"/>
+      <c r="D173" s="15"/>
+      <c r="E173" s="17"/>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="11"/>
       <c r="B174" s="11"/>
-      <c r="C174" s="26"/>
-      <c r="D174" s="26"/>
-      <c r="E174" s="28"/>
+      <c r="C174" s="15"/>
+      <c r="D174" s="15"/>
+      <c r="E174" s="17"/>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="11"/>
       <c r="B175" s="11"/>
-      <c r="C175" s="26"/>
-      <c r="D175" s="26"/>
-      <c r="E175" s="28"/>
+      <c r="C175" s="15"/>
+      <c r="D175" s="15"/>
+      <c r="E175" s="17"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="11"/>
       <c r="B176" s="11"/>
-      <c r="C176" s="26"/>
-      <c r="D176" s="26"/>
-      <c r="E176" s="28"/>
+      <c r="C176" s="15"/>
+      <c r="D176" s="15"/>
+      <c r="E176" s="17"/>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="11"/>
       <c r="B177" s="11"/>
-      <c r="C177" s="26"/>
-      <c r="D177" s="26"/>
-      <c r="E177" s="28"/>
+      <c r="C177" s="15"/>
+      <c r="D177" s="15"/>
+      <c r="E177" s="17"/>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="11"/>
       <c r="B178" s="11"/>
-      <c r="C178" s="26"/>
-      <c r="D178" s="26"/>
-      <c r="E178" s="28"/>
+      <c r="C178" s="15"/>
+      <c r="D178" s="15"/>
+      <c r="E178" s="17"/>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="11"/>
       <c r="B179" s="11"/>
-      <c r="C179" s="26"/>
-      <c r="D179" s="26"/>
-      <c r="E179" s="28"/>
+      <c r="C179" s="15"/>
+      <c r="D179" s="15"/>
+      <c r="E179" s="17"/>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="11"/>
       <c r="B180" s="11"/>
-      <c r="C180" s="26"/>
-      <c r="D180" s="26"/>
-      <c r="E180" s="28"/>
+      <c r="C180" s="15"/>
+      <c r="D180" s="15"/>
+      <c r="E180" s="17"/>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="11"/>
       <c r="B181" s="11"/>
-      <c r="C181" s="26"/>
-      <c r="D181" s="26"/>
-      <c r="E181" s="28"/>
+      <c r="C181" s="15"/>
+      <c r="D181" s="15"/>
+      <c r="E181" s="17"/>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="11"/>
       <c r="B182" s="11"/>
-      <c r="C182" s="26"/>
-      <c r="D182" s="26"/>
-      <c r="E182" s="28"/>
+      <c r="C182" s="15"/>
+      <c r="D182" s="15"/>
+      <c r="E182" s="17"/>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="11"/>
       <c r="B183" s="11"/>
-      <c r="C183" s="26"/>
-      <c r="D183" s="26"/>
-      <c r="E183" s="28"/>
+      <c r="C183" s="15"/>
+      <c r="D183" s="15"/>
+      <c r="E183" s="17"/>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="11"/>
       <c r="B184" s="11"/>
-      <c r="C184" s="26"/>
-      <c r="D184" s="26"/>
-      <c r="E184" s="28"/>
+      <c r="C184" s="15"/>
+      <c r="D184" s="15"/>
+      <c r="E184" s="17"/>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="11"/>
       <c r="B185" s="11"/>
-      <c r="C185" s="26"/>
-      <c r="D185" s="26"/>
-      <c r="E185" s="28"/>
+      <c r="C185" s="15"/>
+      <c r="D185" s="15"/>
+      <c r="E185" s="17"/>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="11"/>
       <c r="B186" s="11"/>
-      <c r="C186" s="26"/>
-      <c r="D186" s="26"/>
-      <c r="E186" s="28"/>
+      <c r="C186" s="15"/>
+      <c r="D186" s="15"/>
+      <c r="E186" s="17"/>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="11"/>
       <c r="B187" s="11"/>
-      <c r="C187" s="26"/>
-      <c r="D187" s="26"/>
-      <c r="E187" s="28"/>
+      <c r="C187" s="15"/>
+      <c r="D187" s="15"/>
+      <c r="E187" s="17"/>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="11"/>
       <c r="B188" s="11"/>
-      <c r="C188" s="26"/>
-      <c r="D188" s="26"/>
-      <c r="E188" s="28"/>
+      <c r="C188" s="15"/>
+      <c r="D188" s="15"/>
+      <c r="E188" s="17"/>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="11"/>
       <c r="B189" s="11"/>
-      <c r="C189" s="26"/>
-      <c r="D189" s="26"/>
-      <c r="E189" s="28"/>
+      <c r="C189" s="15"/>
+      <c r="D189" s="15"/>
+      <c r="E189" s="17"/>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="11"/>
       <c r="B190" s="11"/>
-      <c r="C190" s="26"/>
-      <c r="D190" s="26"/>
-      <c r="E190" s="28"/>
+      <c r="C190" s="15"/>
+      <c r="D190" s="15"/>
+      <c r="E190" s="17"/>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="11"/>
       <c r="B191" s="11"/>
-      <c r="C191" s="26"/>
-      <c r="D191" s="26"/>
-      <c r="E191" s="28"/>
+      <c r="C191" s="15"/>
+      <c r="D191" s="15"/>
+      <c r="E191" s="17"/>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="11"/>
       <c r="B192" s="11"/>
-      <c r="C192" s="26"/>
-      <c r="D192" s="26"/>
-      <c r="E192" s="28"/>
+      <c r="C192" s="15"/>
+      <c r="D192" s="15"/>
+      <c r="E192" s="17"/>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="11"/>
       <c r="B193" s="11"/>
-      <c r="C193" s="26"/>
-      <c r="D193" s="26"/>
-      <c r="E193" s="28"/>
+      <c r="C193" s="15"/>
+      <c r="D193" s="15"/>
+      <c r="E193" s="17"/>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="11"/>
       <c r="B194" s="11"/>
-      <c r="C194" s="26"/>
-      <c r="D194" s="26"/>
-      <c r="E194" s="28"/>
+      <c r="C194" s="15"/>
+      <c r="D194" s="15"/>
+      <c r="E194" s="17"/>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="11"/>
       <c r="B195" s="11"/>
-      <c r="C195" s="26"/>
-      <c r="D195" s="26"/>
-      <c r="E195" s="28"/>
+      <c r="C195" s="15"/>
+      <c r="D195" s="15"/>
+      <c r="E195" s="17"/>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="11"/>
       <c r="B196" s="11"/>
-      <c r="C196" s="26"/>
-      <c r="D196" s="26"/>
-      <c r="E196" s="28"/>
+      <c r="C196" s="15"/>
+      <c r="D196" s="15"/>
+      <c r="E196" s="17"/>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="11"/>
       <c r="B197" s="11"/>
-      <c r="C197" s="26"/>
-      <c r="D197" s="26"/>
-      <c r="E197" s="28"/>
+      <c r="C197" s="15"/>
+      <c r="D197" s="15"/>
+      <c r="E197" s="17"/>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="11"/>
       <c r="B198" s="11"/>
-      <c r="C198" s="26"/>
-      <c r="D198" s="26"/>
-      <c r="E198" s="28"/>
+      <c r="C198" s="15"/>
+      <c r="D198" s="15"/>
+      <c r="E198" s="17"/>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="11"/>
       <c r="B199" s="11"/>
-      <c r="C199" s="26"/>
-      <c r="D199" s="26"/>
-      <c r="E199" s="28"/>
+      <c r="C199" s="15"/>
+      <c r="D199" s="15"/>
+      <c r="E199" s="17"/>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="11"/>
       <c r="B200" s="11"/>
-      <c r="C200" s="26"/>
-      <c r="D200" s="26"/>
-      <c r="E200" s="28"/>
+      <c r="C200" s="15"/>
+      <c r="D200" s="15"/>
+      <c r="E200" s="17"/>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="11"/>
       <c r="B201" s="11"/>
-      <c r="C201" s="26"/>
-      <c r="D201" s="26"/>
-      <c r="E201" s="28"/>
+      <c r="C201" s="15"/>
+      <c r="D201" s="15"/>
+      <c r="E201" s="17"/>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="11"/>
       <c r="B202" s="11"/>
-      <c r="C202" s="26"/>
-      <c r="D202" s="26"/>
-      <c r="E202" s="28"/>
+      <c r="C202" s="15"/>
+      <c r="D202" s="15"/>
+      <c r="E202" s="17"/>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="11"/>
       <c r="B203" s="11"/>
-      <c r="C203" s="26"/>
-      <c r="D203" s="26"/>
-      <c r="E203" s="28"/>
+      <c r="C203" s="15"/>
+      <c r="D203" s="15"/>
+      <c r="E203" s="17"/>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="11"/>
       <c r="B204" s="11"/>
-      <c r="C204" s="26"/>
-      <c r="D204" s="26"/>
-      <c r="E204" s="28"/>
+      <c r="C204" s="15"/>
+      <c r="D204" s="15"/>
+      <c r="E204" s="17"/>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="11"/>
       <c r="B205" s="11"/>
-      <c r="C205" s="26"/>
-      <c r="D205" s="26"/>
-      <c r="E205" s="28"/>
+      <c r="C205" s="15"/>
+      <c r="D205" s="15"/>
+      <c r="E205" s="17"/>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="11"/>
       <c r="B206" s="11"/>
-      <c r="C206" s="26"/>
-      <c r="D206" s="26"/>
-      <c r="E206" s="28"/>
+      <c r="C206" s="15"/>
+      <c r="D206" s="15"/>
+      <c r="E206" s="17"/>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="11"/>
       <c r="B207" s="11"/>
-      <c r="C207" s="26"/>
-      <c r="D207" s="26"/>
-      <c r="E207" s="28"/>
+      <c r="C207" s="15"/>
+      <c r="D207" s="15"/>
+      <c r="E207" s="17"/>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="11"/>
       <c r="B208" s="11"/>
-      <c r="C208" s="26"/>
-      <c r="D208" s="26"/>
-      <c r="E208" s="28"/>
+      <c r="C208" s="15"/>
+      <c r="D208" s="15"/>
+      <c r="E208" s="17"/>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="11"/>
       <c r="B209" s="11"/>
-      <c r="C209" s="26"/>
-      <c r="D209" s="26"/>
-      <c r="E209" s="28"/>
+      <c r="C209" s="15"/>
+      <c r="D209" s="15"/>
+      <c r="E209" s="17"/>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="11"/>
       <c r="B210" s="11"/>
-      <c r="C210" s="26"/>
-      <c r="D210" s="26"/>
-      <c r="E210" s="28"/>
+      <c r="C210" s="15"/>
+      <c r="D210" s="15"/>
+      <c r="E210" s="17"/>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="11"/>
       <c r="B211" s="11"/>
-      <c r="C211" s="26"/>
-      <c r="D211" s="26"/>
-      <c r="E211" s="28"/>
+      <c r="C211" s="15"/>
+      <c r="D211" s="15"/>
+      <c r="E211" s="17"/>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="11"/>
       <c r="B212" s="11"/>
-      <c r="C212" s="26"/>
-      <c r="D212" s="26"/>
-      <c r="E212" s="28"/>
+      <c r="C212" s="15"/>
+      <c r="D212" s="15"/>
+      <c r="E212" s="17"/>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="11"/>
       <c r="B213" s="11"/>
-      <c r="C213" s="26"/>
-      <c r="D213" s="26"/>
-      <c r="E213" s="28"/>
+      <c r="C213" s="15"/>
+      <c r="D213" s="15"/>
+      <c r="E213" s="17"/>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="11"/>
       <c r="B214" s="11"/>
-      <c r="C214" s="26"/>
-      <c r="D214" s="26"/>
-      <c r="E214" s="28"/>
+      <c r="C214" s="15"/>
+      <c r="D214" s="15"/>
+      <c r="E214" s="17"/>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="11"/>
       <c r="B215" s="11"/>
-      <c r="C215" s="26"/>
-      <c r="D215" s="26"/>
-      <c r="E215" s="28"/>
+      <c r="C215" s="15"/>
+      <c r="D215" s="15"/>
+      <c r="E215" s="17"/>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="11"/>
       <c r="B216" s="11"/>
-      <c r="C216" s="26"/>
-      <c r="D216" s="26"/>
-      <c r="E216" s="28"/>
+      <c r="C216" s="15"/>
+      <c r="D216" s="15"/>
+      <c r="E216" s="17"/>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="11"/>
       <c r="B217" s="11"/>
-      <c r="C217" s="26"/>
-      <c r="D217" s="26"/>
-      <c r="E217" s="28"/>
+      <c r="C217" s="15"/>
+      <c r="D217" s="15"/>
+      <c r="E217" s="17"/>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="11"/>
       <c r="B218" s="11"/>
-      <c r="C218" s="26"/>
-      <c r="D218" s="26"/>
-      <c r="E218" s="28"/>
+      <c r="C218" s="15"/>
+      <c r="D218" s="15"/>
+      <c r="E218" s="17"/>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="11"/>
       <c r="B219" s="11"/>
-      <c r="C219" s="26"/>
-      <c r="D219" s="26"/>
-      <c r="E219" s="28"/>
+      <c r="C219" s="15"/>
+      <c r="D219" s="15"/>
+      <c r="E219" s="17"/>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="11"/>
       <c r="B220" s="11"/>
-      <c r="C220" s="26"/>
-      <c r="D220" s="26"/>
-      <c r="E220" s="28"/>
+      <c r="C220" s="15"/>
+      <c r="D220" s="15"/>
+      <c r="E220" s="17"/>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="11"/>
       <c r="B221" s="11"/>
-      <c r="C221" s="26"/>
-      <c r="D221" s="26"/>
-      <c r="E221" s="28"/>
+      <c r="C221" s="15"/>
+      <c r="D221" s="15"/>
+      <c r="E221" s="17"/>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="11"/>
       <c r="B222" s="11"/>
-      <c r="C222" s="26"/>
-      <c r="D222" s="26"/>
-      <c r="E222" s="28"/>
+      <c r="C222" s="15"/>
+      <c r="D222" s="15"/>
+      <c r="E222" s="17"/>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="11"/>
       <c r="B223" s="11"/>
-      <c r="C223" s="26"/>
-      <c r="D223" s="26"/>
-      <c r="E223" s="28"/>
+      <c r="C223" s="15"/>
+      <c r="D223" s="15"/>
+      <c r="E223" s="17"/>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="11"/>
       <c r="B224" s="11"/>
-      <c r="C224" s="26"/>
-      <c r="D224" s="26"/>
-      <c r="E224" s="28"/>
+      <c r="C224" s="15"/>
+      <c r="D224" s="15"/>
+      <c r="E224" s="17"/>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="11"/>
       <c r="B225" s="11"/>
-      <c r="C225" s="26"/>
-      <c r="D225" s="26"/>
-      <c r="E225" s="28"/>
+      <c r="C225" s="15"/>
+      <c r="D225" s="15"/>
+      <c r="E225" s="17"/>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="11"/>
       <c r="B226" s="11"/>
-      <c r="C226" s="26"/>
-      <c r="D226" s="26"/>
-      <c r="E226" s="28"/>
+      <c r="C226" s="15"/>
+      <c r="D226" s="15"/>
+      <c r="E226" s="17"/>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="11"/>
       <c r="B227" s="11"/>
-      <c r="C227" s="26"/>
-      <c r="D227" s="26"/>
-      <c r="E227" s="28"/>
+      <c r="C227" s="15"/>
+      <c r="D227" s="15"/>
+      <c r="E227" s="17"/>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="11"/>
       <c r="B228" s="11"/>
-      <c r="C228" s="26"/>
-      <c r="D228" s="26"/>
-      <c r="E228" s="28"/>
+      <c r="C228" s="15"/>
+      <c r="D228" s="15"/>
+      <c r="E228" s="17"/>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="11"/>
       <c r="B229" s="11"/>
-      <c r="C229" s="26"/>
-      <c r="D229" s="26"/>
-      <c r="E229" s="28"/>
+      <c r="C229" s="15"/>
+      <c r="D229" s="15"/>
+      <c r="E229" s="17"/>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="11"/>
       <c r="B230" s="11"/>
-      <c r="C230" s="26"/>
-      <c r="D230" s="26"/>
-      <c r="E230" s="28"/>
+      <c r="C230" s="15"/>
+      <c r="D230" s="15"/>
+      <c r="E230" s="17"/>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="11"/>
       <c r="B231" s="11"/>
-      <c r="C231" s="26"/>
-      <c r="D231" s="26"/>
-      <c r="E231" s="28"/>
+      <c r="C231" s="15"/>
+      <c r="D231" s="15"/>
+      <c r="E231" s="17"/>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="11"/>
       <c r="B232" s="11"/>
-      <c r="C232" s="26"/>
-      <c r="D232" s="26"/>
-      <c r="E232" s="28"/>
+      <c r="C232" s="15"/>
+      <c r="D232" s="15"/>
+      <c r="E232" s="17"/>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="11"/>
       <c r="B233" s="11"/>
-      <c r="C233" s="26"/>
-      <c r="D233" s="26"/>
-      <c r="E233" s="28"/>
+      <c r="C233" s="15"/>
+      <c r="D233" s="15"/>
+      <c r="E233" s="17"/>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="11"/>
       <c r="B234" s="11"/>
-      <c r="C234" s="26"/>
-      <c r="D234" s="26"/>
-      <c r="E234" s="28"/>
+      <c r="C234" s="15"/>
+      <c r="D234" s="15"/>
+      <c r="E234" s="17"/>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="11"/>
       <c r="B235" s="11"/>
-      <c r="C235" s="26"/>
-      <c r="D235" s="26"/>
-      <c r="E235" s="28"/>
+      <c r="C235" s="15"/>
+      <c r="D235" s="15"/>
+      <c r="E235" s="17"/>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="11"/>
       <c r="B236" s="11"/>
-      <c r="C236" s="26"/>
-      <c r="D236" s="26"/>
-      <c r="E236" s="28"/>
+      <c r="C236" s="15"/>
+      <c r="D236" s="15"/>
+      <c r="E236" s="17"/>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="11"/>
       <c r="B237" s="11"/>
-      <c r="C237" s="26"/>
-      <c r="D237" s="26"/>
-      <c r="E237" s="28"/>
+      <c r="C237" s="15"/>
+      <c r="D237" s="15"/>
+      <c r="E237" s="17"/>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="11"/>
       <c r="B238" s="11"/>
-      <c r="C238" s="26"/>
-      <c r="D238" s="26"/>
-      <c r="E238" s="28"/>
+      <c r="C238" s="15"/>
+      <c r="D238" s="15"/>
+      <c r="E238" s="17"/>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="11"/>
       <c r="B239" s="11"/>
-      <c r="C239" s="26"/>
-      <c r="D239" s="26"/>
-      <c r="E239" s="28"/>
+      <c r="C239" s="15"/>
+      <c r="D239" s="15"/>
+      <c r="E239" s="17"/>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="11"/>
       <c r="B240" s="11"/>
-      <c r="C240" s="26"/>
-      <c r="D240" s="26"/>
-      <c r="E240" s="28"/>
+      <c r="C240" s="15"/>
+      <c r="D240" s="15"/>
+      <c r="E240" s="17"/>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="11"/>
       <c r="B241" s="11"/>
-      <c r="C241" s="26"/>
-      <c r="D241" s="26"/>
-      <c r="E241" s="28"/>
+      <c r="C241" s="15"/>
+      <c r="D241" s="15"/>
+      <c r="E241" s="17"/>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="11"/>
       <c r="B242" s="11"/>
-      <c r="C242" s="26"/>
-      <c r="D242" s="26"/>
-      <c r="E242" s="28"/>
+      <c r="C242" s="15"/>
+      <c r="D242" s="15"/>
+      <c r="E242" s="17"/>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="11"/>
       <c r="B243" s="11"/>
-      <c r="C243" s="26"/>
-      <c r="D243" s="26"/>
-      <c r="E243" s="28"/>
+      <c r="C243" s="15"/>
+      <c r="D243" s="15"/>
+      <c r="E243" s="17"/>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="11"/>
       <c r="B244" s="11"/>
-      <c r="C244" s="26"/>
-      <c r="D244" s="26"/>
-      <c r="E244" s="28"/>
+      <c r="C244" s="15"/>
+      <c r="D244" s="15"/>
+      <c r="E244" s="17"/>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="11"/>
       <c r="B245" s="11"/>
-      <c r="C245" s="26"/>
-      <c r="D245" s="26"/>
-      <c r="E245" s="28"/>
+      <c r="C245" s="15"/>
+      <c r="D245" s="15"/>
+      <c r="E245" s="17"/>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="11"/>
       <c r="B246" s="11"/>
-      <c r="C246" s="26"/>
-      <c r="D246" s="26"/>
-      <c r="E246" s="28"/>
+      <c r="C246" s="15"/>
+      <c r="D246" s="15"/>
+      <c r="E246" s="17"/>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="11"/>
       <c r="B247" s="11"/>
-      <c r="C247" s="26"/>
-      <c r="D247" s="26"/>
-      <c r="E247" s="28"/>
+      <c r="C247" s="15"/>
+      <c r="D247" s="15"/>
+      <c r="E247" s="17"/>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" s="11"/>
       <c r="B248" s="11"/>
-      <c r="C248" s="26"/>
-      <c r="D248" s="26"/>
-      <c r="E248" s="28"/>
+      <c r="C248" s="15"/>
+      <c r="D248" s="15"/>
+      <c r="E248" s="17"/>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="11"/>
       <c r="B249" s="11"/>
-      <c r="C249" s="26"/>
-      <c r="D249" s="26"/>
-      <c r="E249" s="28"/>
+      <c r="C249" s="15"/>
+      <c r="D249" s="15"/>
+      <c r="E249" s="17"/>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="11"/>
       <c r="B250" s="11"/>
-      <c r="C250" s="26"/>
-      <c r="D250" s="26"/>
-      <c r="E250" s="28"/>
+      <c r="C250" s="15"/>
+      <c r="D250" s="15"/>
+      <c r="E250" s="17"/>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="11"/>
       <c r="B251" s="11"/>
-      <c r="C251" s="26"/>
-      <c r="D251" s="26"/>
-      <c r="E251" s="28"/>
+      <c r="C251" s="15"/>
+      <c r="D251" s="15"/>
+      <c r="E251" s="17"/>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" s="11"/>
       <c r="B252" s="11"/>
-      <c r="C252" s="26"/>
-      <c r="D252" s="26"/>
-      <c r="E252" s="28"/>
+      <c r="C252" s="15"/>
+      <c r="D252" s="15"/>
+      <c r="E252" s="17"/>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" s="11"/>
       <c r="B253" s="11"/>
-      <c r="C253" s="26"/>
-      <c r="D253" s="26"/>
-      <c r="E253" s="28"/>
+      <c r="C253" s="15"/>
+      <c r="D253" s="15"/>
+      <c r="E253" s="17"/>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="11"/>
       <c r="B254" s="11"/>
-      <c r="C254" s="26"/>
-      <c r="D254" s="26"/>
-      <c r="E254" s="28"/>
+      <c r="C254" s="15"/>
+      <c r="D254" s="15"/>
+      <c r="E254" s="17"/>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="11"/>
       <c r="B255" s="11"/>
-      <c r="C255" s="26"/>
-      <c r="D255" s="26"/>
-      <c r="E255" s="28"/>
+      <c r="C255" s="15"/>
+      <c r="D255" s="15"/>
+      <c r="E255" s="17"/>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="11"/>
       <c r="B256" s="11"/>
-      <c r="C256" s="26"/>
-      <c r="D256" s="26"/>
-      <c r="E256" s="28"/>
+      <c r="C256" s="15"/>
+      <c r="D256" s="15"/>
+      <c r="E256" s="17"/>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="11"/>
       <c r="B257" s="11"/>
-      <c r="C257" s="26"/>
-      <c r="D257" s="26"/>
-      <c r="E257" s="28"/>
+      <c r="C257" s="15"/>
+      <c r="D257" s="15"/>
+      <c r="E257" s="17"/>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" s="11"/>
       <c r="B258" s="11"/>
-      <c r="C258" s="26"/>
-      <c r="D258" s="26"/>
-      <c r="E258" s="28"/>
+      <c r="C258" s="15"/>
+      <c r="D258" s="15"/>
+      <c r="E258" s="17"/>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" s="11"/>
       <c r="B259" s="11"/>
-      <c r="C259" s="26"/>
-      <c r="D259" s="26"/>
-      <c r="E259" s="28"/>
+      <c r="C259" s="15"/>
+      <c r="D259" s="15"/>
+      <c r="E259" s="17"/>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" s="11"/>
       <c r="B260" s="11"/>
-      <c r="C260" s="26"/>
-      <c r="D260" s="26"/>
-      <c r="E260" s="28"/>
+      <c r="C260" s="15"/>
+      <c r="D260" s="15"/>
+      <c r="E260" s="17"/>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" s="11"/>
       <c r="B261" s="11"/>
-      <c r="C261" s="26"/>
-      <c r="D261" s="26"/>
-      <c r="E261" s="28"/>
+      <c r="C261" s="15"/>
+      <c r="D261" s="15"/>
+      <c r="E261" s="17"/>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" s="11"/>
       <c r="B262" s="11"/>
-      <c r="C262" s="26"/>
-      <c r="D262" s="26"/>
-      <c r="E262" s="28"/>
+      <c r="C262" s="15"/>
+      <c r="D262" s="15"/>
+      <c r="E262" s="17"/>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" s="11"/>
       <c r="B263" s="11"/>
-      <c r="C263" s="26"/>
-      <c r="D263" s="26"/>
-      <c r="E263" s="28"/>
+      <c r="C263" s="15"/>
+      <c r="D263" s="15"/>
+      <c r="E263" s="17"/>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="11"/>
       <c r="B264" s="11"/>
-      <c r="C264" s="26"/>
-      <c r="D264" s="26"/>
-      <c r="E264" s="28"/>
+      <c r="C264" s="15"/>
+      <c r="D264" s="15"/>
+      <c r="E264" s="17"/>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" s="11"/>
       <c r="B265" s="11"/>
-      <c r="C265" s="26"/>
-      <c r="D265" s="26"/>
-      <c r="E265" s="28"/>
+      <c r="C265" s="15"/>
+      <c r="D265" s="15"/>
+      <c r="E265" s="17"/>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" s="11"/>
       <c r="B266" s="11"/>
-      <c r="C266" s="26"/>
-      <c r="D266" s="26"/>
-      <c r="E266" s="28"/>
+      <c r="C266" s="15"/>
+      <c r="D266" s="15"/>
+      <c r="E266" s="17"/>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" s="11"/>
       <c r="B267" s="11"/>
-      <c r="C267" s="26"/>
-      <c r="D267" s="26"/>
-      <c r="E267" s="28"/>
+      <c r="C267" s="15"/>
+      <c r="D267" s="15"/>
+      <c r="E267" s="17"/>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" s="11"/>
       <c r="B268" s="11"/>
-      <c r="C268" s="26"/>
-      <c r="D268" s="26"/>
-      <c r="E268" s="28"/>
+      <c r="C268" s="15"/>
+      <c r="D268" s="15"/>
+      <c r="E268" s="17"/>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" s="11"/>
       <c r="B269" s="11"/>
-      <c r="C269" s="26"/>
-      <c r="D269" s="26"/>
-      <c r="E269" s="28"/>
+      <c r="C269" s="15"/>
+      <c r="D269" s="15"/>
+      <c r="E269" s="17"/>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" s="11"/>
       <c r="B270" s="11"/>
-      <c r="C270" s="26"/>
-      <c r="D270" s="26"/>
-      <c r="E270" s="28"/>
+      <c r="C270" s="15"/>
+      <c r="D270" s="15"/>
+      <c r="E270" s="17"/>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" s="11"/>
       <c r="B271" s="11"/>
-      <c r="C271" s="26"/>
-      <c r="D271" s="26"/>
-      <c r="E271" s="28"/>
+      <c r="C271" s="15"/>
+      <c r="D271" s="15"/>
+      <c r="E271" s="17"/>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" s="11"/>
       <c r="B272" s="11"/>
-      <c r="C272" s="26"/>
-      <c r="D272" s="26"/>
-      <c r="E272" s="28"/>
+      <c r="C272" s="15"/>
+      <c r="D272" s="15"/>
+      <c r="E272" s="17"/>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" s="11"/>
       <c r="B273" s="11"/>
-      <c r="C273" s="26"/>
-      <c r="D273" s="26"/>
-      <c r="E273" s="28"/>
+      <c r="C273" s="15"/>
+      <c r="D273" s="15"/>
+      <c r="E273" s="17"/>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" s="11"/>
       <c r="B274" s="11"/>
-      <c r="C274" s="26"/>
-      <c r="D274" s="26"/>
-      <c r="E274" s="28"/>
+      <c r="C274" s="15"/>
+      <c r="D274" s="15"/>
+      <c r="E274" s="17"/>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" s="11"/>
       <c r="B275" s="11"/>
-      <c r="C275" s="26"/>
-      <c r="D275" s="26"/>
-      <c r="E275" s="28"/>
+      <c r="C275" s="15"/>
+      <c r="D275" s="15"/>
+      <c r="E275" s="17"/>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" s="11"/>
       <c r="B276" s="11"/>
-      <c r="C276" s="26"/>
-      <c r="D276" s="26"/>
-      <c r="E276" s="28"/>
+      <c r="C276" s="15"/>
+      <c r="D276" s="15"/>
+      <c r="E276" s="17"/>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" s="11"/>
       <c r="B277" s="11"/>
-      <c r="C277" s="26"/>
-      <c r="D277" s="26"/>
-      <c r="E277" s="28"/>
+      <c r="C277" s="15"/>
+      <c r="D277" s="15"/>
+      <c r="E277" s="17"/>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" s="11"/>
       <c r="B278" s="11"/>
-      <c r="C278" s="26"/>
-      <c r="D278" s="26"/>
-      <c r="E278" s="28"/>
+      <c r="C278" s="15"/>
+      <c r="D278" s="15"/>
+      <c r="E278" s="17"/>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" s="11"/>
       <c r="B279" s="11"/>
-      <c r="C279" s="26"/>
-      <c r="D279" s="26"/>
-      <c r="E279" s="28"/>
+      <c r="C279" s="15"/>
+      <c r="D279" s="15"/>
+      <c r="E279" s="17"/>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" s="11"/>
       <c r="B280" s="11"/>
-      <c r="C280" s="26"/>
-      <c r="D280" s="26"/>
-      <c r="E280" s="28"/>
+      <c r="C280" s="15"/>
+      <c r="D280" s="15"/>
+      <c r="E280" s="17"/>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" s="11"/>
       <c r="B281" s="11"/>
-      <c r="C281" s="26"/>
-      <c r="D281" s="26"/>
-      <c r="E281" s="28"/>
+      <c r="C281" s="15"/>
+      <c r="D281" s="15"/>
+      <c r="E281" s="17"/>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" s="11"/>
       <c r="B282" s="11"/>
-      <c r="C282" s="26"/>
-      <c r="D282" s="26"/>
-      <c r="E282" s="28"/>
+      <c r="C282" s="15"/>
+      <c r="D282" s="15"/>
+      <c r="E282" s="17"/>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" s="11"/>
       <c r="B283" s="11"/>
-      <c r="C283" s="26"/>
-      <c r="D283" s="26"/>
-      <c r="E283" s="28"/>
+      <c r="C283" s="15"/>
+      <c r="D283" s="15"/>
+      <c r="E283" s="17"/>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" s="11"/>
       <c r="B284" s="11"/>
-      <c r="C284" s="26"/>
-      <c r="D284" s="26"/>
-      <c r="E284" s="28"/>
+      <c r="C284" s="15"/>
+      <c r="D284" s="15"/>
+      <c r="E284" s="17"/>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" s="11"/>
       <c r="B285" s="11"/>
-      <c r="C285" s="26"/>
-      <c r="D285" s="26"/>
-      <c r="E285" s="28"/>
+      <c r="C285" s="15"/>
+      <c r="D285" s="15"/>
+      <c r="E285" s="17"/>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" s="11"/>
       <c r="B286" s="11"/>
-      <c r="C286" s="26"/>
-      <c r="D286" s="26"/>
-      <c r="E286" s="28"/>
+      <c r="C286" s="15"/>
+      <c r="D286" s="15"/>
+      <c r="E286" s="17"/>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" s="11"/>
       <c r="B287" s="11"/>
-      <c r="C287" s="26"/>
-      <c r="D287" s="26"/>
-      <c r="E287" s="28"/>
+      <c r="C287" s="15"/>
+      <c r="D287" s="15"/>
+      <c r="E287" s="17"/>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" s="11"/>
       <c r="B288" s="11"/>
-      <c r="C288" s="26"/>
-      <c r="D288" s="26"/>
-      <c r="E288" s="28"/>
+      <c r="C288" s="15"/>
+      <c r="D288" s="15"/>
+      <c r="E288" s="17"/>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" s="11"/>
       <c r="B289" s="11"/>
-      <c r="C289" s="26"/>
-      <c r="D289" s="26"/>
-      <c r="E289" s="28"/>
+      <c r="C289" s="15"/>
+      <c r="D289" s="15"/>
+      <c r="E289" s="17"/>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" s="11"/>
       <c r="B290" s="11"/>
-      <c r="C290" s="26"/>
-      <c r="D290" s="26"/>
-      <c r="E290" s="28"/>
+      <c r="C290" s="15"/>
+      <c r="D290" s="15"/>
+      <c r="E290" s="17"/>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" s="11"/>
       <c r="B291" s="11"/>
-      <c r="C291" s="26"/>
-      <c r="D291" s="26"/>
-      <c r="E291" s="28"/>
+      <c r="C291" s="15"/>
+      <c r="D291" s="15"/>
+      <c r="E291" s="17"/>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" s="11"/>
       <c r="B292" s="11"/>
-      <c r="C292" s="26"/>
-      <c r="D292" s="26"/>
-      <c r="E292" s="28"/>
+      <c r="C292" s="15"/>
+      <c r="D292" s="15"/>
+      <c r="E292" s="17"/>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" s="11"/>
       <c r="B293" s="11"/>
-      <c r="C293" s="26"/>
-      <c r="D293" s="26"/>
-      <c r="E293" s="28"/>
+      <c r="C293" s="15"/>
+      <c r="D293" s="15"/>
+      <c r="E293" s="17"/>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" s="11"/>
       <c r="B294" s="11"/>
-      <c r="C294" s="26"/>
-      <c r="D294" s="26"/>
-      <c r="E294" s="28"/>
+      <c r="C294" s="15"/>
+      <c r="D294" s="15"/>
+      <c r="E294" s="17"/>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" s="11"/>
       <c r="B295" s="11"/>
-      <c r="C295" s="26"/>
-      <c r="D295" s="26"/>
-      <c r="E295" s="28"/>
+      <c r="C295" s="15"/>
+      <c r="D295" s="15"/>
+      <c r="E295" s="17"/>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" s="11"/>
       <c r="B296" s="11"/>
-      <c r="C296" s="26"/>
-      <c r="D296" s="26"/>
-      <c r="E296" s="28"/>
+      <c r="C296" s="15"/>
+      <c r="D296" s="15"/>
+      <c r="E296" s="17"/>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" s="11"/>
       <c r="B297" s="11"/>
-      <c r="C297" s="26"/>
-      <c r="D297" s="26"/>
-      <c r="E297" s="28"/>
+      <c r="C297" s="15"/>
+      <c r="D297" s="15"/>
+      <c r="E297" s="17"/>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" s="11"/>
       <c r="B298" s="11"/>
-      <c r="C298" s="26"/>
-      <c r="D298" s="26"/>
-      <c r="E298" s="28"/>
+      <c r="C298" s="15"/>
+      <c r="D298" s="15"/>
+      <c r="E298" s="17"/>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" s="11"/>
       <c r="B299" s="11"/>
-      <c r="C299" s="26"/>
-      <c r="D299" s="26"/>
-      <c r="E299" s="28"/>
+      <c r="C299" s="15"/>
+      <c r="D299" s="15"/>
+      <c r="E299" s="17"/>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" s="11"/>
       <c r="B300" s="11"/>
-      <c r="C300" s="26"/>
-      <c r="D300" s="26"/>
-      <c r="E300" s="28"/>
+      <c r="C300" s="15"/>
+      <c r="D300" s="15"/>
+      <c r="E300" s="17"/>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" s="11"/>
       <c r="B301" s="11"/>
-      <c r="C301" s="26"/>
-      <c r="D301" s="26"/>
-      <c r="E301" s="28"/>
+      <c r="C301" s="15"/>
+      <c r="D301" s="15"/>
+      <c r="E301" s="17"/>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" s="11"/>
       <c r="B302" s="11"/>
-      <c r="C302" s="26"/>
-      <c r="D302" s="26"/>
-      <c r="E302" s="28"/>
+      <c r="C302" s="15"/>
+      <c r="D302" s="15"/>
+      <c r="E302" s="17"/>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" s="11"/>
       <c r="B303" s="11"/>
-      <c r="C303" s="26"/>
-      <c r="D303" s="26"/>
-      <c r="E303" s="28"/>
+      <c r="C303" s="15"/>
+      <c r="D303" s="15"/>
+      <c r="E303" s="17"/>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" s="11"/>
       <c r="B304" s="11"/>
-      <c r="C304" s="26"/>
-      <c r="D304" s="26"/>
-      <c r="E304" s="28"/>
+      <c r="C304" s="15"/>
+      <c r="D304" s="15"/>
+      <c r="E304" s="17"/>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" s="11"/>
       <c r="B305" s="11"/>
-      <c r="C305" s="26"/>
-      <c r="D305" s="26"/>
-      <c r="E305" s="28"/>
+      <c r="C305" s="15"/>
+      <c r="D305" s="15"/>
+      <c r="E305" s="17"/>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" s="11"/>
       <c r="B306" s="11"/>
-      <c r="C306" s="26"/>
-      <c r="D306" s="26"/>
-      <c r="E306" s="28"/>
+      <c r="C306" s="15"/>
+      <c r="D306" s="15"/>
+      <c r="E306" s="17"/>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" s="11"/>
       <c r="B307" s="11"/>
-      <c r="C307" s="26"/>
-      <c r="D307" s="26"/>
-      <c r="E307" s="28"/>
+      <c r="C307" s="15"/>
+      <c r="D307" s="15"/>
+      <c r="E307" s="17"/>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" s="11"/>
       <c r="B308" s="11"/>
-      <c r="C308" s="26"/>
-      <c r="D308" s="26"/>
-      <c r="E308" s="28"/>
+      <c r="C308" s="15"/>
+      <c r="D308" s="15"/>
+      <c r="E308" s="17"/>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" s="11"/>
       <c r="B309" s="11"/>
-      <c r="C309" s="26"/>
-      <c r="D309" s="26"/>
-      <c r="E309" s="28"/>
+      <c r="C309" s="15"/>
+      <c r="D309" s="15"/>
+      <c r="E309" s="17"/>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" s="11"/>
       <c r="B310" s="11"/>
-      <c r="C310" s="26"/>
-      <c r="D310" s="26"/>
-      <c r="E310" s="28"/>
+      <c r="C310" s="15"/>
+      <c r="D310" s="15"/>
+      <c r="E310" s="17"/>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" s="11"/>
       <c r="B311" s="11"/>
-      <c r="C311" s="26"/>
-      <c r="D311" s="26"/>
-      <c r="E311" s="28"/>
+      <c r="C311" s="15"/>
+      <c r="D311" s="15"/>
+      <c r="E311" s="17"/>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" s="11"/>
       <c r="B312" s="11"/>
-      <c r="C312" s="26"/>
-      <c r="D312" s="26"/>
-      <c r="E312" s="28"/>
+      <c r="C312" s="15"/>
+      <c r="D312" s="15"/>
+      <c r="E312" s="17"/>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" s="11"/>
       <c r="B313" s="11"/>
-      <c r="C313" s="26"/>
-      <c r="D313" s="26"/>
-      <c r="E313" s="28"/>
+      <c r="C313" s="15"/>
+      <c r="D313" s="15"/>
+      <c r="E313" s="17"/>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" s="11"/>
       <c r="B314" s="11"/>
-      <c r="C314" s="26"/>
-      <c r="D314" s="26"/>
-      <c r="E314" s="28"/>
+      <c r="C314" s="15"/>
+      <c r="D314" s="15"/>
+      <c r="E314" s="17"/>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" s="11"/>
       <c r="B315" s="11"/>
-      <c r="C315" s="26"/>
-      <c r="D315" s="26"/>
-      <c r="E315" s="28"/>
+      <c r="C315" s="15"/>
+      <c r="D315" s="15"/>
+      <c r="E315" s="17"/>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" s="11"/>
       <c r="B316" s="11"/>
-      <c r="C316" s="26"/>
-      <c r="D316" s="26"/>
-      <c r="E316" s="28"/>
+      <c r="C316" s="15"/>
+      <c r="D316" s="15"/>
+      <c r="E316" s="17"/>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" s="11"/>
       <c r="B317" s="11"/>
-      <c r="C317" s="26"/>
-      <c r="D317" s="26"/>
-      <c r="E317" s="28"/>
+      <c r="C317" s="15"/>
+      <c r="D317" s="15"/>
+      <c r="E317" s="17"/>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" s="11"/>
       <c r="B318" s="11"/>
-      <c r="C318" s="26"/>
-      <c r="D318" s="26"/>
-      <c r="E318" s="28"/>
+      <c r="C318" s="15"/>
+      <c r="D318" s="15"/>
+      <c r="E318" s="17"/>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" s="11"/>
       <c r="B319" s="11"/>
-      <c r="C319" s="26"/>
-      <c r="D319" s="26"/>
-      <c r="E319" s="28"/>
+      <c r="C319" s="15"/>
+      <c r="D319" s="15"/>
+      <c r="E319" s="17"/>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" s="11"/>
       <c r="B320" s="11"/>
-      <c r="C320" s="26"/>
-      <c r="D320" s="26"/>
-      <c r="E320" s="28"/>
+      <c r="C320" s="15"/>
+      <c r="D320" s="15"/>
+      <c r="E320" s="17"/>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" s="11"/>
       <c r="B321" s="11"/>
-      <c r="C321" s="26"/>
-      <c r="D321" s="26"/>
-      <c r="E321" s="28"/>
+      <c r="C321" s="15"/>
+      <c r="D321" s="15"/>
+      <c r="E321" s="17"/>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" s="11"/>
       <c r="B322" s="11"/>
-      <c r="C322" s="26"/>
-      <c r="D322" s="26"/>
-      <c r="E322" s="28"/>
+      <c r="C322" s="15"/>
+      <c r="D322" s="15"/>
+      <c r="E322" s="17"/>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" s="11"/>
       <c r="B323" s="11"/>
-      <c r="C323" s="26"/>
-      <c r="D323" s="26"/>
-      <c r="E323" s="28"/>
+      <c r="C323" s="15"/>
+      <c r="D323" s="15"/>
+      <c r="E323" s="17"/>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" s="11"/>
       <c r="B324" s="11"/>
-      <c r="C324" s="26"/>
-      <c r="D324" s="26"/>
-      <c r="E324" s="28"/>
+      <c r="C324" s="15"/>
+      <c r="D324" s="15"/>
+      <c r="E324" s="17"/>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" s="11"/>
       <c r="B325" s="11"/>
-      <c r="C325" s="26"/>
-      <c r="D325" s="26"/>
-      <c r="E325" s="28"/>
+      <c r="C325" s="15"/>
+      <c r="D325" s="15"/>
+      <c r="E325" s="17"/>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" s="11"/>
       <c r="B326" s="11"/>
-      <c r="C326" s="26"/>
-      <c r="D326" s="26"/>
-      <c r="E326" s="28"/>
+      <c r="C326" s="15"/>
+      <c r="D326" s="15"/>
+      <c r="E326" s="17"/>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" s="11"/>
       <c r="B327" s="11"/>
-      <c r="C327" s="26"/>
-      <c r="D327" s="26"/>
-      <c r="E327" s="28"/>
+      <c r="C327" s="15"/>
+      <c r="D327" s="15"/>
+      <c r="E327" s="17"/>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" s="11"/>
       <c r="B328" s="11"/>
-      <c r="C328" s="26"/>
-      <c r="D328" s="26"/>
-      <c r="E328" s="28"/>
+      <c r="C328" s="15"/>
+      <c r="D328" s="15"/>
+      <c r="E328" s="17"/>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" s="11"/>
       <c r="B329" s="11"/>
-      <c r="C329" s="26"/>
-      <c r="D329" s="26"/>
-      <c r="E329" s="28"/>
+      <c r="C329" s="15"/>
+      <c r="D329" s="15"/>
+      <c r="E329" s="17"/>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" s="11"/>
       <c r="B330" s="11"/>
-      <c r="C330" s="26"/>
-      <c r="D330" s="26"/>
-      <c r="E330" s="28"/>
+      <c r="C330" s="15"/>
+      <c r="D330" s="15"/>
+      <c r="E330" s="17"/>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" s="11"/>
       <c r="B331" s="11"/>
-      <c r="C331" s="26"/>
-      <c r="D331" s="26"/>
-      <c r="E331" s="28"/>
+      <c r="C331" s="15"/>
+      <c r="D331" s="15"/>
+      <c r="E331" s="17"/>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" s="11"/>
       <c r="B332" s="11"/>
-      <c r="C332" s="26"/>
-      <c r="D332" s="26"/>
-      <c r="E332" s="28"/>
+      <c r="C332" s="15"/>
+      <c r="D332" s="15"/>
+      <c r="E332" s="17"/>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" s="11"/>
       <c r="B333" s="11"/>
-      <c r="C333" s="26"/>
-      <c r="D333" s="26"/>
-      <c r="E333" s="28"/>
+      <c r="C333" s="15"/>
+      <c r="D333" s="15"/>
+      <c r="E333" s="17"/>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" s="11"/>
       <c r="B334" s="11"/>
-      <c r="C334" s="26"/>
-      <c r="D334" s="26"/>
-      <c r="E334" s="28"/>
+      <c r="C334" s="15"/>
+      <c r="D334" s="15"/>
+      <c r="E334" s="17"/>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" s="11"/>
       <c r="B335" s="11"/>
-      <c r="C335" s="26"/>
-      <c r="D335" s="26"/>
-      <c r="E335" s="28"/>
+      <c r="C335" s="15"/>
+      <c r="D335" s="15"/>
+      <c r="E335" s="17"/>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" s="11"/>
       <c r="B336" s="11"/>
-      <c r="C336" s="26"/>
-      <c r="D336" s="26"/>
-      <c r="E336" s="28"/>
+      <c r="C336" s="15"/>
+      <c r="D336" s="15"/>
+      <c r="E336" s="17"/>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" s="11"/>
       <c r="B337" s="11"/>
-      <c r="C337" s="26"/>
-      <c r="D337" s="26"/>
-      <c r="E337" s="28"/>
+      <c r="C337" s="15"/>
+      <c r="D337" s="15"/>
+      <c r="E337" s="17"/>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" s="11"/>
       <c r="B338" s="11"/>
-      <c r="C338" s="26"/>
-      <c r="D338" s="26"/>
-      <c r="E338" s="28"/>
+      <c r="C338" s="15"/>
+      <c r="D338" s="15"/>
+      <c r="E338" s="17"/>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" s="11"/>
       <c r="B339" s="11"/>
-      <c r="C339" s="26"/>
-      <c r="D339" s="26"/>
-      <c r="E339" s="28"/>
+      <c r="C339" s="15"/>
+      <c r="D339" s="15"/>
+      <c r="E339" s="17"/>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" s="11"/>
       <c r="B340" s="11"/>
-      <c r="C340" s="26"/>
-      <c r="D340" s="26"/>
-      <c r="E340" s="28"/>
+      <c r="C340" s="15"/>
+      <c r="D340" s="15"/>
+      <c r="E340" s="17"/>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" s="11"/>
       <c r="B341" s="11"/>
-      <c r="C341" s="26"/>
-      <c r="D341" s="26"/>
-      <c r="E341" s="28"/>
+      <c r="C341" s="15"/>
+      <c r="D341" s="15"/>
+      <c r="E341" s="17"/>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" s="11"/>
       <c r="B342" s="11"/>
-      <c r="C342" s="26"/>
-      <c r="D342" s="26"/>
-      <c r="E342" s="28"/>
+      <c r="C342" s="15"/>
+      <c r="D342" s="15"/>
+      <c r="E342" s="17"/>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" s="11"/>
       <c r="B343" s="11"/>
-      <c r="C343" s="26"/>
-      <c r="D343" s="26"/>
-      <c r="E343" s="28"/>
+      <c r="C343" s="15"/>
+      <c r="D343" s="15"/>
+      <c r="E343" s="17"/>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" s="11"/>
       <c r="B344" s="11"/>
-      <c r="C344" s="26"/>
-      <c r="D344" s="26"/>
-      <c r="E344" s="28"/>
+      <c r="C344" s="15"/>
+      <c r="D344" s="15"/>
+      <c r="E344" s="17"/>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" s="11"/>
       <c r="B345" s="11"/>
-      <c r="C345" s="26"/>
-      <c r="D345" s="26"/>
-      <c r="E345" s="28"/>
+      <c r="C345" s="15"/>
+      <c r="D345" s="15"/>
+      <c r="E345" s="17"/>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" s="11"/>
       <c r="B346" s="11"/>
-      <c r="C346" s="26"/>
-      <c r="D346" s="26"/>
-      <c r="E346" s="28"/>
+      <c r="C346" s="15"/>
+      <c r="D346" s="15"/>
+      <c r="E346" s="17"/>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347" s="11"/>
       <c r="B347" s="11"/>
-      <c r="C347" s="26"/>
-      <c r="D347" s="26"/>
-      <c r="E347" s="28"/>
+      <c r="C347" s="15"/>
+      <c r="D347" s="15"/>
+      <c r="E347" s="17"/>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" s="11"/>
       <c r="B348" s="11"/>
-      <c r="C348" s="26"/>
-      <c r="D348" s="26"/>
-      <c r="E348" s="28"/>
+      <c r="C348" s="15"/>
+      <c r="D348" s="15"/>
+      <c r="E348" s="17"/>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" s="11"/>
       <c r="B349" s="11"/>
-      <c r="C349" s="26"/>
-      <c r="D349" s="26"/>
-      <c r="E349" s="28"/>
+      <c r="C349" s="15"/>
+      <c r="D349" s="15"/>
+      <c r="E349" s="17"/>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" s="11"/>
       <c r="B350" s="11"/>
-      <c r="C350" s="26"/>
-      <c r="D350" s="26"/>
-      <c r="E350" s="28"/>
+      <c r="C350" s="15"/>
+      <c r="D350" s="15"/>
+      <c r="E350" s="17"/>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" s="11"/>
       <c r="B351" s="11"/>
-      <c r="C351" s="26"/>
-      <c r="D351" s="26"/>
-      <c r="E351" s="28"/>
+      <c r="C351" s="15"/>
+      <c r="D351" s="15"/>
+      <c r="E351" s="17"/>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" s="11"/>
       <c r="B352" s="11"/>
-      <c r="C352" s="26"/>
-      <c r="D352" s="26"/>
-      <c r="E352" s="28"/>
+      <c r="C352" s="15"/>
+      <c r="D352" s="15"/>
+      <c r="E352" s="17"/>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" s="11"/>
       <c r="B353" s="11"/>
-      <c r="C353" s="26"/>
-      <c r="D353" s="26"/>
-      <c r="E353" s="28"/>
+      <c r="C353" s="15"/>
+      <c r="D353" s="15"/>
+      <c r="E353" s="17"/>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" s="11"/>
       <c r="B354" s="11"/>
-      <c r="C354" s="26"/>
-      <c r="D354" s="26"/>
-      <c r="E354" s="28"/>
+      <c r="C354" s="15"/>
+      <c r="D354" s="15"/>
+      <c r="E354" s="17"/>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" s="11"/>
       <c r="B355" s="11"/>
-      <c r="C355" s="26"/>
-      <c r="D355" s="26"/>
-      <c r="E355" s="28"/>
+      <c r="C355" s="15"/>
+      <c r="D355" s="15"/>
+      <c r="E355" s="17"/>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" s="11"/>
       <c r="B356" s="11"/>
-      <c r="C356" s="26"/>
-      <c r="D356" s="26"/>
-      <c r="E356" s="28"/>
+      <c r="C356" s="15"/>
+      <c r="D356" s="15"/>
+      <c r="E356" s="17"/>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" s="11"/>
       <c r="B357" s="11"/>
-      <c r="C357" s="26"/>
-      <c r="D357" s="26"/>
-      <c r="E357" s="28"/>
+      <c r="C357" s="15"/>
+      <c r="D357" s="15"/>
+      <c r="E357" s="17"/>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" s="11"/>
       <c r="B358" s="11"/>
-      <c r="C358" s="26"/>
-      <c r="D358" s="26"/>
-      <c r="E358" s="28"/>
+      <c r="C358" s="15"/>
+      <c r="D358" s="15"/>
+      <c r="E358" s="17"/>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359" s="11"/>
       <c r="B359" s="11"/>
-      <c r="C359" s="26"/>
-      <c r="D359" s="26"/>
-      <c r="E359" s="28"/>
+      <c r="C359" s="15"/>
+      <c r="D359" s="15"/>
+      <c r="E359" s="17"/>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360" s="11"/>
       <c r="B360" s="11"/>
-      <c r="C360" s="26"/>
-      <c r="D360" s="26"/>
-      <c r="E360" s="28"/>
+      <c r="C360" s="15"/>
+      <c r="D360" s="15"/>
+      <c r="E360" s="17"/>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" s="11"/>
       <c r="B361" s="11"/>
-      <c r="C361" s="26"/>
-      <c r="D361" s="26"/>
-      <c r="E361" s="28"/>
+      <c r="C361" s="15"/>
+      <c r="D361" s="15"/>
+      <c r="E361" s="17"/>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" s="11"/>
       <c r="B362" s="11"/>
-      <c r="C362" s="26"/>
-      <c r="D362" s="26"/>
-      <c r="E362" s="28"/>
+      <c r="C362" s="15"/>
+      <c r="D362" s="15"/>
+      <c r="E362" s="17"/>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" s="11"/>
       <c r="B363" s="11"/>
-      <c r="C363" s="26"/>
-      <c r="D363" s="26"/>
-      <c r="E363" s="28"/>
+      <c r="C363" s="15"/>
+      <c r="D363" s="15"/>
+      <c r="E363" s="17"/>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" s="11"/>
       <c r="B364" s="11"/>
-      <c r="C364" s="26"/>
-      <c r="D364" s="26"/>
-      <c r="E364" s="28"/>
+      <c r="C364" s="15"/>
+      <c r="D364" s="15"/>
+      <c r="E364" s="17"/>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" s="11"/>
       <c r="B365" s="11"/>
-      <c r="C365" s="26"/>
-      <c r="D365" s="26"/>
-      <c r="E365" s="28"/>
+      <c r="C365" s="15"/>
+      <c r="D365" s="15"/>
+      <c r="E365" s="17"/>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" s="11"/>
       <c r="B366" s="11"/>
-      <c r="C366" s="26"/>
-      <c r="D366" s="26"/>
-      <c r="E366" s="28"/>
+      <c r="C366" s="15"/>
+      <c r="D366" s="15"/>
+      <c r="E366" s="17"/>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" s="11"/>
       <c r="B367" s="11"/>
-      <c r="C367" s="26"/>
-      <c r="D367" s="26"/>
-      <c r="E367" s="28"/>
+      <c r="C367" s="15"/>
+      <c r="D367" s="15"/>
+      <c r="E367" s="17"/>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" s="11"/>
       <c r="B368" s="11"/>
-      <c r="C368" s="26"/>
-      <c r="D368" s="26"/>
-      <c r="E368" s="28"/>
+      <c r="C368" s="15"/>
+      <c r="D368" s="15"/>
+      <c r="E368" s="17"/>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369" s="11"/>
       <c r="B369" s="11"/>
-      <c r="C369" s="26"/>
-      <c r="D369" s="26"/>
-      <c r="E369" s="28"/>
+      <c r="C369" s="15"/>
+      <c r="D369" s="15"/>
+      <c r="E369" s="17"/>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370" s="11"/>
       <c r="B370" s="11"/>
-      <c r="C370" s="26"/>
-      <c r="D370" s="26"/>
-      <c r="E370" s="28"/>
+      <c r="C370" s="15"/>
+      <c r="D370" s="15"/>
+      <c r="E370" s="17"/>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" s="11"/>
       <c r="B371" s="11"/>
-      <c r="C371" s="26"/>
-      <c r="D371" s="26"/>
-      <c r="E371" s="28"/>
+      <c r="C371" s="15"/>
+      <c r="D371" s="15"/>
+      <c r="E371" s="17"/>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372" s="11"/>
       <c r="B372" s="11"/>
-      <c r="C372" s="26"/>
-      <c r="D372" s="26"/>
-      <c r="E372" s="28"/>
+      <c r="C372" s="15"/>
+      <c r="D372" s="15"/>
+      <c r="E372" s="17"/>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" s="11"/>
       <c r="B373" s="11"/>
-      <c r="C373" s="26"/>
-      <c r="D373" s="26"/>
-      <c r="E373" s="28"/>
+      <c r="C373" s="15"/>
+      <c r="D373" s="15"/>
+      <c r="E373" s="17"/>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374" s="11"/>
       <c r="B374" s="11"/>
-      <c r="C374" s="26"/>
-      <c r="D374" s="26"/>
-      <c r="E374" s="28"/>
+      <c r="C374" s="15"/>
+      <c r="D374" s="15"/>
+      <c r="E374" s="17"/>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" s="11"/>
       <c r="B375" s="11"/>
-      <c r="C375" s="26"/>
-      <c r="D375" s="26"/>
-      <c r="E375" s="28"/>
+      <c r="C375" s="15"/>
+      <c r="D375" s="15"/>
+      <c r="E375" s="17"/>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376" s="11"/>
       <c r="B376" s="11"/>
-      <c r="C376" s="26"/>
-      <c r="D376" s="26"/>
-      <c r="E376" s="28"/>
+      <c r="C376" s="15"/>
+      <c r="D376" s="15"/>
+      <c r="E376" s="17"/>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377" s="11"/>
       <c r="B377" s="11"/>
-      <c r="C377" s="26"/>
-      <c r="D377" s="26"/>
-      <c r="E377" s="28"/>
+      <c r="C377" s="15"/>
+      <c r="D377" s="15"/>
+      <c r="E377" s="17"/>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" s="11"/>
       <c r="B378" s="11"/>
-      <c r="C378" s="26"/>
-      <c r="D378" s="26"/>
-      <c r="E378" s="28"/>
+      <c r="C378" s="15"/>
+      <c r="D378" s="15"/>
+      <c r="E378" s="17"/>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379" s="11"/>
       <c r="B379" s="11"/>
-      <c r="C379" s="26"/>
-      <c r="D379" s="26"/>
-      <c r="E379" s="28"/>
+      <c r="C379" s="15"/>
+      <c r="D379" s="15"/>
+      <c r="E379" s="17"/>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" s="11"/>
       <c r="B380" s="11"/>
-      <c r="C380" s="26"/>
-      <c r="D380" s="26"/>
-      <c r="E380" s="28"/>
+      <c r="C380" s="15"/>
+      <c r="D380" s="15"/>
+      <c r="E380" s="17"/>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" s="11"/>
       <c r="B381" s="11"/>
-      <c r="C381" s="26"/>
-      <c r="D381" s="26"/>
-      <c r="E381" s="28"/>
+      <c r="C381" s="15"/>
+      <c r="D381" s="15"/>
+      <c r="E381" s="17"/>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" s="11"/>
       <c r="B382" s="11"/>
-      <c r="C382" s="26"/>
-      <c r="D382" s="26"/>
-      <c r="E382" s="28"/>
+      <c r="C382" s="15"/>
+      <c r="D382" s="15"/>
+      <c r="E382" s="17"/>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" s="11"/>
       <c r="B383" s="11"/>
-      <c r="C383" s="26"/>
-      <c r="D383" s="26"/>
-      <c r="E383" s="28"/>
+      <c r="C383" s="15"/>
+      <c r="D383" s="15"/>
+      <c r="E383" s="17"/>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" s="11"/>
       <c r="B384" s="11"/>
-      <c r="C384" s="26"/>
-      <c r="D384" s="26"/>
-      <c r="E384" s="28"/>
+      <c r="C384" s="15"/>
+      <c r="D384" s="15"/>
+      <c r="E384" s="17"/>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" s="11"/>
       <c r="B385" s="11"/>
-      <c r="C385" s="26"/>
-      <c r="D385" s="26"/>
-      <c r="E385" s="28"/>
+      <c r="C385" s="15"/>
+      <c r="D385" s="15"/>
+      <c r="E385" s="17"/>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" s="11"/>
       <c r="B386" s="11"/>
-      <c r="C386" s="26"/>
-      <c r="D386" s="26"/>
-      <c r="E386" s="28"/>
+      <c r="C386" s="15"/>
+      <c r="D386" s="15"/>
+      <c r="E386" s="17"/>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" s="11"/>
       <c r="B387" s="11"/>
-      <c r="C387" s="26"/>
-      <c r="D387" s="26"/>
-      <c r="E387" s="28"/>
+      <c r="C387" s="15"/>
+      <c r="D387" s="15"/>
+      <c r="E387" s="17"/>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" s="11"/>
       <c r="B388" s="11"/>
-      <c r="C388" s="26"/>
-      <c r="D388" s="26"/>
-      <c r="E388" s="28"/>
+      <c r="C388" s="15"/>
+      <c r="D388" s="15"/>
+      <c r="E388" s="17"/>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" s="11"/>
       <c r="B389" s="11"/>
-      <c r="C389" s="26"/>
-      <c r="D389" s="26"/>
-      <c r="E389" s="28"/>
+      <c r="C389" s="15"/>
+      <c r="D389" s="15"/>
+      <c r="E389" s="17"/>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" s="11"/>
       <c r="B390" s="11"/>
-      <c r="C390" s="26"/>
-      <c r="D390" s="26"/>
-      <c r="E390" s="28"/>
+      <c r="C390" s="15"/>
+      <c r="D390" s="15"/>
+      <c r="E390" s="17"/>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" s="11"/>
       <c r="B391" s="11"/>
-      <c r="C391" s="26"/>
-      <c r="D391" s="26"/>
-      <c r="E391" s="28"/>
+      <c r="C391" s="15"/>
+      <c r="D391" s="15"/>
+      <c r="E391" s="17"/>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" s="11"/>
       <c r="B392" s="11"/>
-      <c r="C392" s="26"/>
-      <c r="D392" s="26"/>
-      <c r="E392" s="28"/>
+      <c r="C392" s="15"/>
+      <c r="D392" s="15"/>
+      <c r="E392" s="17"/>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" s="11"/>
       <c r="B393" s="11"/>
-      <c r="C393" s="26"/>
-      <c r="D393" s="26"/>
-      <c r="E393" s="28"/>
+      <c r="C393" s="15"/>
+      <c r="D393" s="15"/>
+      <c r="E393" s="17"/>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" s="11"/>
       <c r="B394" s="11"/>
-      <c r="C394" s="26"/>
-      <c r="D394" s="26"/>
-      <c r="E394" s="28"/>
+      <c r="C394" s="15"/>
+      <c r="D394" s="15"/>
+      <c r="E394" s="17"/>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" s="11"/>
       <c r="B395" s="11"/>
-      <c r="C395" s="26"/>
-      <c r="D395" s="26"/>
-      <c r="E395" s="28"/>
+      <c r="C395" s="15"/>
+      <c r="D395" s="15"/>
+      <c r="E395" s="17"/>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" s="11"/>
       <c r="B396" s="11"/>
-      <c r="C396" s="26"/>
-      <c r="D396" s="26"/>
-      <c r="E396" s="28"/>
+      <c r="C396" s="15"/>
+      <c r="D396" s="15"/>
+      <c r="E396" s="17"/>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" s="11"/>
       <c r="B397" s="11"/>
-      <c r="C397" s="26"/>
-      <c r="D397" s="26"/>
-      <c r="E397" s="28"/>
+      <c r="C397" s="15"/>
+      <c r="D397" s="15"/>
+      <c r="E397" s="17"/>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" s="11"/>
       <c r="B398" s="11"/>
-      <c r="C398" s="26"/>
-      <c r="D398" s="26"/>
-      <c r="E398" s="28"/>
+      <c r="C398" s="15"/>
+      <c r="D398" s="15"/>
+      <c r="E398" s="17"/>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" s="11"/>
       <c r="B399" s="11"/>
-      <c r="C399" s="26"/>
-      <c r="D399" s="26"/>
-      <c r="E399" s="28"/>
+      <c r="C399" s="15"/>
+      <c r="D399" s="15"/>
+      <c r="E399" s="17"/>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" s="11"/>
       <c r="B400" s="11"/>
-      <c r="C400" s="26"/>
-      <c r="D400" s="26"/>
-      <c r="E400" s="28"/>
+      <c r="C400" s="15"/>
+      <c r="D400" s="15"/>
+      <c r="E400" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rss_islandr/templates/report_template.xlsx
+++ b/rss_islandr/templates/report_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11385" activeTab="4"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11385"/>
   </bookViews>
   <sheets>
     <sheet name="On-site on-site" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="48">
   <si>
     <t>Soil</t>
   </si>
@@ -172,6 +172,9 @@
   </si>
   <si>
     <t>Name</t>
+  </si>
+  <si>
+    <t>CRS type</t>
   </si>
 </sst>
 </file>
@@ -471,26 +474,14 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -503,6 +494,18 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -828,23 +831,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
@@ -861,103 +864,105 @@
       <c r="H2" s="3"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="21"/>
+      <c r="L2" s="29"/>
       <c r="M2" s="3"/>
       <c r="N2" s="1"/>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="22"/>
+      <c r="B3" s="19"/>
       <c r="C3" s="9"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="22"/>
+      <c r="G3" s="19"/>
       <c r="H3" s="3"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="22"/>
+      <c r="L3" s="19"/>
       <c r="M3" s="9"/>
       <c r="N3" s="1"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="23"/>
+      <c r="A4" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="26"/>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="23"/>
+      <c r="G4" s="26"/>
       <c r="H4" s="3"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="23" t="s">
+      <c r="K4" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="23"/>
+      <c r="L4" s="26"/>
       <c r="M4" s="9"/>
       <c r="N4" s="1"/>
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="25"/>
+      <c r="A5" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="28"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="25"/>
+      <c r="F5" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="28"/>
       <c r="H5" s="3"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="25"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="28"/>
       <c r="M5" s="9"/>
       <c r="N5" s="1"/>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="21"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="29"/>
+      <c r="B7" s="25"/>
       <c r="C7" s="4"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -973,10 +978,10 @@
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="29"/>
+      <c r="B8" s="25"/>
       <c r="C8" s="4"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -992,10 +997,10 @@
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="29"/>
+      <c r="B9" s="25"/>
       <c r="C9" s="13"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -1011,50 +1016,50 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="21"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="26" t="s">
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="27"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="26" t="s">
+      <c r="E11" s="23"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="H11" s="27"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="26" t="s">
+      <c r="H11" s="23"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="27"/>
-      <c r="L11" s="28"/>
-      <c r="M11" s="26" t="s">
+      <c r="K11" s="23"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="N11" s="27"/>
-      <c r="O11" s="28"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="24"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
@@ -1084,180 +1089,180 @@
       <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="22"/>
+      <c r="B13" s="19"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="22"/>
+      <c r="E13" s="19"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="22"/>
+      <c r="H13" s="19"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="22" t="s">
+      <c r="J13" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="K13" s="22"/>
+      <c r="K13" s="19"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="22" t="s">
+      <c r="M13" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="N13" s="22"/>
+      <c r="N13" s="19"/>
       <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="22"/>
+      <c r="B14" s="19"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="22"/>
+      <c r="E14" s="19"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="22"/>
+      <c r="H14" s="19"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="22" t="s">
+      <c r="J14" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="22"/>
+      <c r="K14" s="19"/>
       <c r="L14" s="4"/>
-      <c r="M14" s="22" t="s">
+      <c r="M14" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="22"/>
+      <c r="N14" s="19"/>
       <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="22"/>
+      <c r="B15" s="19"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="22"/>
+      <c r="E15" s="19"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="22" t="s">
+      <c r="J15" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="22"/>
+      <c r="K15" s="19"/>
       <c r="L15" s="4"/>
-      <c r="M15" s="22" t="s">
+      <c r="M15" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="N15" s="22"/>
+      <c r="N15" s="19"/>
       <c r="O15" s="7"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="22"/>
+      <c r="B16" s="19"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
       <c r="I16" s="6"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
       <c r="L16" s="5"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="22"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
       <c r="O16" s="8"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="22"/>
+      <c r="B17" s="19"/>
       <c r="C17" s="13"/>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="22"/>
+      <c r="E17" s="19"/>
       <c r="F17" s="13"/>
-      <c r="G17" s="22" t="s">
+      <c r="G17" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="22"/>
+      <c r="H17" s="19"/>
       <c r="I17" s="13"/>
-      <c r="J17" s="22" t="s">
+      <c r="J17" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="K17" s="22"/>
+      <c r="K17" s="19"/>
       <c r="L17" s="13"/>
-      <c r="M17" s="22" t="s">
+      <c r="M17" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="N17" s="22"/>
+      <c r="N17" s="19"/>
       <c r="O17" s="13"/>
     </row>
     <row r="18" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="21"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="26" t="str">
+      <c r="A19" s="22" t="str">
         <f>A11</f>
         <v>Soil</v>
       </c>
-      <c r="B19" s="27"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="26" t="str">
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="22" t="str">
         <f t="shared" ref="D19" si="0">D11</f>
         <v>Ground water</v>
       </c>
-      <c r="E19" s="27"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="26" t="str">
+      <c r="E19" s="23"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="22" t="str">
         <f t="shared" ref="G19" si="1">G11</f>
         <v>Surface water</v>
       </c>
-      <c r="H19" s="27"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="26" t="str">
+      <c r="H19" s="23"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="22" t="str">
         <f t="shared" ref="J19" si="2">J11</f>
         <v>Air</v>
       </c>
-      <c r="K19" s="27"/>
-      <c r="L19" s="28"/>
-      <c r="M19" s="26" t="str">
+      <c r="K19" s="23"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="22" t="str">
         <f t="shared" ref="M19" si="3">M11</f>
         <v>Sediment</v>
       </c>
-      <c r="N19" s="27"/>
-      <c r="O19" s="28"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="24"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
@@ -1287,128 +1292,61 @@
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="22"/>
+      <c r="B21" s="19"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="22"/>
+      <c r="E21" s="19"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="22" t="s">
+      <c r="G21" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="22"/>
+      <c r="H21" s="19"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="22" t="s">
+      <c r="J21" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="22"/>
+      <c r="K21" s="19"/>
       <c r="L21" s="4"/>
-      <c r="M21" s="22" t="s">
+      <c r="M21" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="N21" s="22"/>
+      <c r="N21" s="19"/>
       <c r="O21" s="7"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="22"/>
+      <c r="B22" s="19"/>
       <c r="C22" s="13"/>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="22"/>
+      <c r="E22" s="19"/>
       <c r="F22" s="13"/>
-      <c r="G22" s="22" t="s">
+      <c r="G22" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="H22" s="22"/>
+      <c r="H22" s="19"/>
       <c r="I22" s="13"/>
-      <c r="J22" s="22" t="s">
+      <c r="J22" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="K22" s="22"/>
+      <c r="K22" s="19"/>
       <c r="L22" s="13"/>
-      <c r="M22" s="22" t="s">
+      <c r="M22" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="N22" s="22"/>
+      <c r="N22" s="19"/>
       <c r="O22" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="74">
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="A18:O18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="A6:O6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="K5:L5"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="F2:G2"/>
@@ -1416,6 +1354,73 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="K3:L3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="A6:O6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="M22:N22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -1440,23 +1445,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
@@ -1473,103 +1478,103 @@
       <c r="H2" s="3"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="21"/>
+      <c r="L2" s="29"/>
       <c r="M2" s="3"/>
       <c r="N2" s="1"/>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="22"/>
+      <c r="B3" s="19"/>
       <c r="C3" s="9"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="22"/>
+      <c r="G3" s="19"/>
       <c r="H3" s="3"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="22"/>
+      <c r="L3" s="19"/>
       <c r="M3" s="9"/>
       <c r="N3" s="1"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="23"/>
+      <c r="B4" s="26"/>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="23"/>
+      <c r="G4" s="26"/>
       <c r="H4" s="3"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="23" t="s">
+      <c r="K4" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="23"/>
+      <c r="L4" s="26"/>
       <c r="M4" s="9"/>
       <c r="N4" s="1"/>
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="25"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="25"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="28"/>
       <c r="H5" s="3"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="25"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="28"/>
       <c r="M5" s="9"/>
       <c r="N5" s="1"/>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="21"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="29"/>
+      <c r="B7" s="25"/>
       <c r="C7" s="4"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -1585,10 +1590,10 @@
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="29"/>
+      <c r="B8" s="25"/>
       <c r="C8" s="4"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -1604,10 +1609,10 @@
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="29"/>
+      <c r="B9" s="25"/>
       <c r="C9" s="13"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -1623,50 +1628,50 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="21"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="26" t="s">
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="27"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="26" t="s">
+      <c r="E11" s="23"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="H11" s="27"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="26" t="s">
+      <c r="H11" s="23"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="27"/>
-      <c r="L11" s="28"/>
-      <c r="M11" s="26" t="s">
+      <c r="K11" s="23"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="N11" s="27"/>
-      <c r="O11" s="28"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="24"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
@@ -1696,180 +1701,180 @@
       <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="22"/>
+      <c r="B13" s="19"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="22"/>
+      <c r="E13" s="19"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="22"/>
+      <c r="H13" s="19"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="22" t="s">
+      <c r="J13" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="K13" s="22"/>
+      <c r="K13" s="19"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="22" t="s">
+      <c r="M13" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="N13" s="22"/>
+      <c r="N13" s="19"/>
       <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="22"/>
+      <c r="B14" s="19"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="22"/>
+      <c r="E14" s="19"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="22"/>
+      <c r="H14" s="19"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="22" t="s">
+      <c r="J14" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="22"/>
+      <c r="K14" s="19"/>
       <c r="L14" s="4"/>
-      <c r="M14" s="22" t="s">
+      <c r="M14" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="22"/>
+      <c r="N14" s="19"/>
       <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="22"/>
+      <c r="B15" s="19"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="22"/>
+      <c r="E15" s="19"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="22" t="s">
+      <c r="J15" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="22"/>
+      <c r="K15" s="19"/>
       <c r="L15" s="4"/>
-      <c r="M15" s="22" t="s">
+      <c r="M15" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="N15" s="22"/>
+      <c r="N15" s="19"/>
       <c r="O15" s="7"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="22"/>
+      <c r="B16" s="19"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
       <c r="I16" s="6"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
       <c r="L16" s="5"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="22"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
       <c r="O16" s="8"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="22"/>
+      <c r="B17" s="19"/>
       <c r="C17" s="13"/>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="22"/>
+      <c r="E17" s="19"/>
       <c r="F17" s="13"/>
-      <c r="G17" s="22" t="s">
+      <c r="G17" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="22"/>
+      <c r="H17" s="19"/>
       <c r="I17" s="13"/>
-      <c r="J17" s="22" t="s">
+      <c r="J17" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="K17" s="22"/>
+      <c r="K17" s="19"/>
       <c r="L17" s="13"/>
-      <c r="M17" s="22" t="s">
+      <c r="M17" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="N17" s="22"/>
+      <c r="N17" s="19"/>
       <c r="O17" s="13"/>
     </row>
     <row r="18" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="21"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="26" t="str">
+      <c r="A19" s="22" t="str">
         <f>A11</f>
         <v>Soil</v>
       </c>
-      <c r="B19" s="27"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="26" t="str">
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="22" t="str">
         <f t="shared" ref="D19" si="0">D11</f>
         <v>Ground water</v>
       </c>
-      <c r="E19" s="27"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="26" t="str">
+      <c r="E19" s="23"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="22" t="str">
         <f t="shared" ref="G19" si="1">G11</f>
         <v>Surface water</v>
       </c>
-      <c r="H19" s="27"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="26" t="str">
+      <c r="H19" s="23"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="22" t="str">
         <f t="shared" ref="J19" si="2">J11</f>
         <v>Air</v>
       </c>
-      <c r="K19" s="27"/>
-      <c r="L19" s="28"/>
-      <c r="M19" s="26" t="str">
+      <c r="K19" s="23"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="22" t="str">
         <f t="shared" ref="M19" si="3">M11</f>
         <v>Sediment</v>
       </c>
-      <c r="N19" s="27"/>
-      <c r="O19" s="28"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="24"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
@@ -1899,128 +1904,61 @@
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="22"/>
+      <c r="B21" s="19"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="22"/>
+      <c r="E21" s="19"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="22" t="s">
+      <c r="G21" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="22"/>
+      <c r="H21" s="19"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="22" t="s">
+      <c r="J21" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="22"/>
+      <c r="K21" s="19"/>
       <c r="L21" s="4"/>
-      <c r="M21" s="22" t="s">
+      <c r="M21" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="N21" s="22"/>
+      <c r="N21" s="19"/>
       <c r="O21" s="7"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="22"/>
+      <c r="B22" s="19"/>
       <c r="C22" s="13"/>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="22"/>
+      <c r="E22" s="19"/>
       <c r="F22" s="13"/>
-      <c r="G22" s="22" t="s">
+      <c r="G22" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="H22" s="22"/>
+      <c r="H22" s="19"/>
       <c r="I22" s="13"/>
-      <c r="J22" s="22" t="s">
+      <c r="J22" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="K22" s="22"/>
+      <c r="K22" s="19"/>
       <c r="L22" s="13"/>
-      <c r="M22" s="22" t="s">
+      <c r="M22" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="N22" s="22"/>
+      <c r="N22" s="19"/>
       <c r="O22" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="74">
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="A18:O18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="A6:O6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="K5:L5"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="F2:G2"/>
@@ -2028,6 +1966,73 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="K3:L3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="A6:O6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="M22:N22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -2052,23 +2057,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
@@ -2085,103 +2090,103 @@
       <c r="H2" s="3"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="21"/>
+      <c r="L2" s="29"/>
       <c r="M2" s="3"/>
       <c r="N2" s="1"/>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="22"/>
+      <c r="B3" s="19"/>
       <c r="C3" s="9"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="22"/>
+      <c r="G3" s="19"/>
       <c r="H3" s="3"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="22"/>
+      <c r="L3" s="19"/>
       <c r="M3" s="9"/>
       <c r="N3" s="1"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="23"/>
+      <c r="B4" s="26"/>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="23"/>
+      <c r="G4" s="26"/>
       <c r="H4" s="3"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="23" t="s">
+      <c r="K4" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="23"/>
+      <c r="L4" s="26"/>
       <c r="M4" s="9"/>
       <c r="N4" s="1"/>
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="25"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="25"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="28"/>
       <c r="H5" s="3"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="25"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="28"/>
       <c r="M5" s="9"/>
       <c r="N5" s="1"/>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="21"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="29"/>
+      <c r="B7" s="25"/>
       <c r="C7" s="4"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -2197,10 +2202,10 @@
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="29"/>
+      <c r="B8" s="25"/>
       <c r="C8" s="4"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -2216,10 +2221,10 @@
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="29"/>
+      <c r="B9" s="25"/>
       <c r="C9" s="13"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -2235,50 +2240,50 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="21"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="26" t="s">
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="27"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="26" t="s">
+      <c r="E11" s="23"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="H11" s="27"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="26" t="s">
+      <c r="H11" s="23"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="27"/>
-      <c r="L11" s="28"/>
-      <c r="M11" s="26" t="s">
+      <c r="K11" s="23"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="N11" s="27"/>
-      <c r="O11" s="28"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="24"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
@@ -2308,180 +2313,180 @@
       <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="22"/>
+      <c r="B13" s="19"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="22"/>
+      <c r="E13" s="19"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="22"/>
+      <c r="H13" s="19"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="22" t="s">
+      <c r="J13" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="K13" s="22"/>
+      <c r="K13" s="19"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="22" t="s">
+      <c r="M13" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="N13" s="22"/>
+      <c r="N13" s="19"/>
       <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="22"/>
+      <c r="B14" s="19"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="22"/>
+      <c r="E14" s="19"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="22"/>
+      <c r="H14" s="19"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="22" t="s">
+      <c r="J14" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="22"/>
+      <c r="K14" s="19"/>
       <c r="L14" s="4"/>
-      <c r="M14" s="22" t="s">
+      <c r="M14" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="22"/>
+      <c r="N14" s="19"/>
       <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="22"/>
+      <c r="B15" s="19"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="22"/>
+      <c r="E15" s="19"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="22" t="s">
+      <c r="J15" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="22"/>
+      <c r="K15" s="19"/>
       <c r="L15" s="4"/>
-      <c r="M15" s="22" t="s">
+      <c r="M15" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="N15" s="22"/>
+      <c r="N15" s="19"/>
       <c r="O15" s="7"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="22"/>
+      <c r="B16" s="19"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
       <c r="I16" s="6"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
       <c r="L16" s="5"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="22"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
       <c r="O16" s="8"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="22"/>
+      <c r="B17" s="19"/>
       <c r="C17" s="13"/>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="22"/>
+      <c r="E17" s="19"/>
       <c r="F17" s="13"/>
-      <c r="G17" s="22" t="s">
+      <c r="G17" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="22"/>
+      <c r="H17" s="19"/>
       <c r="I17" s="13"/>
-      <c r="J17" s="22" t="s">
+      <c r="J17" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="K17" s="22"/>
+      <c r="K17" s="19"/>
       <c r="L17" s="13"/>
-      <c r="M17" s="22" t="s">
+      <c r="M17" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="N17" s="22"/>
+      <c r="N17" s="19"/>
       <c r="O17" s="13"/>
     </row>
     <row r="18" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="21"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="26" t="str">
+      <c r="A19" s="22" t="str">
         <f>A11</f>
         <v>Soil</v>
       </c>
-      <c r="B19" s="27"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="26" t="str">
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="22" t="str">
         <f t="shared" ref="D19" si="0">D11</f>
         <v>Ground water</v>
       </c>
-      <c r="E19" s="27"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="26" t="str">
+      <c r="E19" s="23"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="22" t="str">
         <f t="shared" ref="G19" si="1">G11</f>
         <v>Surface water</v>
       </c>
-      <c r="H19" s="27"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="26" t="str">
+      <c r="H19" s="23"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="22" t="str">
         <f t="shared" ref="J19" si="2">J11</f>
         <v>Air</v>
       </c>
-      <c r="K19" s="27"/>
-      <c r="L19" s="28"/>
-      <c r="M19" s="26" t="str">
+      <c r="K19" s="23"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="22" t="str">
         <f t="shared" ref="M19" si="3">M11</f>
         <v>Sediment</v>
       </c>
-      <c r="N19" s="27"/>
-      <c r="O19" s="28"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="24"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
@@ -2511,103 +2516,77 @@
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="22"/>
+      <c r="B21" s="19"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="22"/>
+      <c r="E21" s="19"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="22" t="s">
+      <c r="G21" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="22"/>
+      <c r="H21" s="19"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="22" t="s">
+      <c r="J21" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="22"/>
+      <c r="K21" s="19"/>
       <c r="L21" s="4"/>
-      <c r="M21" s="22" t="s">
+      <c r="M21" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="N21" s="22"/>
+      <c r="N21" s="19"/>
       <c r="O21" s="7"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="22"/>
+      <c r="B22" s="19"/>
       <c r="C22" s="13"/>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="22"/>
+      <c r="E22" s="19"/>
       <c r="F22" s="13"/>
-      <c r="G22" s="22" t="s">
+      <c r="G22" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="H22" s="22"/>
+      <c r="H22" s="19"/>
       <c r="I22" s="13"/>
-      <c r="J22" s="22" t="s">
+      <c r="J22" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="K22" s="22"/>
+      <c r="K22" s="19"/>
       <c r="L22" s="13"/>
-      <c r="M22" s="22" t="s">
+      <c r="M22" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="N22" s="22"/>
+      <c r="N22" s="19"/>
       <c r="O22" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="74">
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="A18:O18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A6:O6"/>
     <mergeCell ref="A8:B8"/>
@@ -2624,22 +2603,48 @@
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="D17:E17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/rss_islandr/templates/report_template.xlsx
+++ b/rss_islandr/templates/report_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11385"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11385" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="On-site on-site" sheetId="3" r:id="rId1"/>
@@ -474,14 +474,26 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -494,18 +506,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -831,23 +831,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
@@ -864,105 +864,105 @@
       <c r="H2" s="3"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="29" t="s">
+      <c r="K2" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="29"/>
+      <c r="L2" s="21"/>
       <c r="M2" s="3"/>
       <c r="N2" s="1"/>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="19"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="9"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="19"/>
+      <c r="G3" s="22"/>
       <c r="H3" s="3"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="19" t="s">
+      <c r="K3" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="19"/>
+      <c r="L3" s="22"/>
       <c r="M3" s="9"/>
       <c r="N3" s="1"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="26"/>
+      <c r="B4" s="23"/>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="26"/>
+      <c r="G4" s="23"/>
       <c r="H4" s="3"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="26" t="s">
+      <c r="K4" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="26"/>
+      <c r="L4" s="23"/>
       <c r="M4" s="9"/>
       <c r="N4" s="1"/>
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="28"/>
+      <c r="B5" s="25"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="28"/>
+      <c r="G5" s="25"/>
       <c r="H5" s="3"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="28"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="25"/>
       <c r="M5" s="9"/>
       <c r="N5" s="1"/>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
-      <c r="O6" s="21"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="25"/>
+      <c r="B7" s="29"/>
       <c r="C7" s="4"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -978,10 +978,10 @@
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="25"/>
+      <c r="B8" s="29"/>
       <c r="C8" s="4"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -997,10 +997,10 @@
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="25"/>
+      <c r="B9" s="29"/>
       <c r="C9" s="13"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -1016,50 +1016,50 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
-      <c r="O10" s="21"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="22" t="s">
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="23"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="22" t="s">
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="H11" s="23"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="22" t="s">
+      <c r="H11" s="27"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="23"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="22" t="s">
+      <c r="K11" s="27"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="N11" s="23"/>
-      <c r="O11" s="24"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="28"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
@@ -1089,180 +1089,180 @@
       <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="19"/>
+      <c r="B13" s="22"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="19"/>
+      <c r="E13" s="22"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="19"/>
+      <c r="H13" s="22"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="19" t="s">
+      <c r="J13" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="K13" s="19"/>
+      <c r="K13" s="22"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="19" t="s">
+      <c r="M13" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="N13" s="19"/>
+      <c r="N13" s="22"/>
       <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="19"/>
+      <c r="B14" s="22"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="19"/>
+      <c r="E14" s="22"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="19"/>
+      <c r="H14" s="22"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="19" t="s">
+      <c r="J14" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="19"/>
+      <c r="K14" s="22"/>
       <c r="L14" s="4"/>
-      <c r="M14" s="19" t="s">
+      <c r="M14" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="19"/>
+      <c r="N14" s="22"/>
       <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="19"/>
+      <c r="B15" s="22"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="19"/>
+      <c r="E15" s="22"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="19" t="s">
+      <c r="J15" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="19"/>
+      <c r="K15" s="22"/>
       <c r="L15" s="4"/>
-      <c r="M15" s="19" t="s">
+      <c r="M15" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="N15" s="19"/>
+      <c r="N15" s="22"/>
       <c r="O15" s="7"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="19"/>
+      <c r="B16" s="22"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
       <c r="I16" s="6"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
       <c r="L16" s="5"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
       <c r="O16" s="8"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="19"/>
+      <c r="B17" s="22"/>
       <c r="C17" s="13"/>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="19"/>
+      <c r="E17" s="22"/>
       <c r="F17" s="13"/>
-      <c r="G17" s="19" t="s">
+      <c r="G17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="19"/>
+      <c r="H17" s="22"/>
       <c r="I17" s="13"/>
-      <c r="J17" s="19" t="s">
+      <c r="J17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="K17" s="19"/>
+      <c r="K17" s="22"/>
       <c r="L17" s="13"/>
-      <c r="M17" s="19" t="s">
+      <c r="M17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="N17" s="19"/>
+      <c r="N17" s="22"/>
       <c r="O17" s="13"/>
     </row>
     <row r="18" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="21"/>
-      <c r="N18" s="21"/>
-      <c r="O18" s="21"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="22" t="str">
+      <c r="A19" s="26" t="str">
         <f>A11</f>
         <v>Soil</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="22" t="str">
+      <c r="B19" s="27"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="26" t="str">
         <f t="shared" ref="D19" si="0">D11</f>
         <v>Ground water</v>
       </c>
-      <c r="E19" s="23"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="22" t="str">
+      <c r="E19" s="27"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="26" t="str">
         <f t="shared" ref="G19" si="1">G11</f>
         <v>Surface water</v>
       </c>
-      <c r="H19" s="23"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="22" t="str">
+      <c r="H19" s="27"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="26" t="str">
         <f t="shared" ref="J19" si="2">J11</f>
         <v>Air</v>
       </c>
-      <c r="K19" s="23"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="22" t="str">
+      <c r="K19" s="27"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="26" t="str">
         <f t="shared" ref="M19" si="3">M11</f>
         <v>Sediment</v>
       </c>
-      <c r="N19" s="23"/>
-      <c r="O19" s="24"/>
+      <c r="N19" s="27"/>
+      <c r="O19" s="28"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
@@ -1292,61 +1292,128 @@
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="19"/>
+      <c r="B21" s="22"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="19"/>
+      <c r="E21" s="22"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="19" t="s">
+      <c r="G21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="19"/>
+      <c r="H21" s="22"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="19" t="s">
+      <c r="J21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="19"/>
+      <c r="K21" s="22"/>
       <c r="L21" s="4"/>
-      <c r="M21" s="19" t="s">
+      <c r="M21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="N21" s="19"/>
+      <c r="N21" s="22"/>
       <c r="O21" s="7"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="19"/>
+      <c r="B22" s="22"/>
       <c r="C22" s="13"/>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="19"/>
+      <c r="E22" s="22"/>
       <c r="F22" s="13"/>
-      <c r="G22" s="19" t="s">
+      <c r="G22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="H22" s="19"/>
+      <c r="H22" s="22"/>
       <c r="I22" s="13"/>
-      <c r="J22" s="19" t="s">
+      <c r="J22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="K22" s="19"/>
+      <c r="K22" s="22"/>
       <c r="L22" s="13"/>
-      <c r="M22" s="19" t="s">
+      <c r="M22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="N22" s="19"/>
+      <c r="N22" s="22"/>
       <c r="O22" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="74">
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="A6:O6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="K5:L5"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="F2:G2"/>
@@ -1354,73 +1421,6 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="K3:L3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="A6:O6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A18:O18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="M22:N22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -1445,23 +1445,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
@@ -1478,103 +1478,103 @@
       <c r="H2" s="3"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="29" t="s">
+      <c r="K2" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="29"/>
+      <c r="L2" s="21"/>
       <c r="M2" s="3"/>
       <c r="N2" s="1"/>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="19"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="9"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="19"/>
+      <c r="G3" s="22"/>
       <c r="H3" s="3"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="19" t="s">
+      <c r="K3" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="19"/>
+      <c r="L3" s="22"/>
       <c r="M3" s="9"/>
       <c r="N3" s="1"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="26"/>
+      <c r="B4" s="23"/>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="26"/>
+      <c r="G4" s="23"/>
       <c r="H4" s="3"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="26" t="s">
+      <c r="K4" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="26"/>
+      <c r="L4" s="23"/>
       <c r="M4" s="9"/>
       <c r="N4" s="1"/>
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="28"/>
+      <c r="B5" s="25"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="28"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="25"/>
       <c r="H5" s="3"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="28"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="25"/>
       <c r="M5" s="9"/>
       <c r="N5" s="1"/>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
-      <c r="O6" s="21"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="25"/>
+      <c r="B7" s="29"/>
       <c r="C7" s="4"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -1590,10 +1590,10 @@
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="25"/>
+      <c r="B8" s="29"/>
       <c r="C8" s="4"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -1609,10 +1609,10 @@
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="25"/>
+      <c r="B9" s="29"/>
       <c r="C9" s="13"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -1628,50 +1628,50 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
-      <c r="O10" s="21"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="22" t="s">
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="23"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="22" t="s">
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="H11" s="23"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="22" t="s">
+      <c r="H11" s="27"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="23"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="22" t="s">
+      <c r="K11" s="27"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="N11" s="23"/>
-      <c r="O11" s="24"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="28"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
@@ -1701,180 +1701,180 @@
       <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="19"/>
+      <c r="B13" s="22"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="19"/>
+      <c r="E13" s="22"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="19"/>
+      <c r="H13" s="22"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="19" t="s">
+      <c r="J13" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="K13" s="19"/>
+      <c r="K13" s="22"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="19" t="s">
+      <c r="M13" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="N13" s="19"/>
+      <c r="N13" s="22"/>
       <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="19"/>
+      <c r="B14" s="22"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="19"/>
+      <c r="E14" s="22"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="19"/>
+      <c r="H14" s="22"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="19" t="s">
+      <c r="J14" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="19"/>
+      <c r="K14" s="22"/>
       <c r="L14" s="4"/>
-      <c r="M14" s="19" t="s">
+      <c r="M14" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="19"/>
+      <c r="N14" s="22"/>
       <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="19"/>
+      <c r="B15" s="22"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="19"/>
+      <c r="E15" s="22"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="19" t="s">
+      <c r="J15" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="19"/>
+      <c r="K15" s="22"/>
       <c r="L15" s="4"/>
-      <c r="M15" s="19" t="s">
+      <c r="M15" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="N15" s="19"/>
+      <c r="N15" s="22"/>
       <c r="O15" s="7"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="19"/>
+      <c r="B16" s="22"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
       <c r="I16" s="6"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
       <c r="L16" s="5"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
       <c r="O16" s="8"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="19"/>
+      <c r="B17" s="22"/>
       <c r="C17" s="13"/>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="19"/>
+      <c r="E17" s="22"/>
       <c r="F17" s="13"/>
-      <c r="G17" s="19" t="s">
+      <c r="G17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="19"/>
+      <c r="H17" s="22"/>
       <c r="I17" s="13"/>
-      <c r="J17" s="19" t="s">
+      <c r="J17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="K17" s="19"/>
+      <c r="K17" s="22"/>
       <c r="L17" s="13"/>
-      <c r="M17" s="19" t="s">
+      <c r="M17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="N17" s="19"/>
+      <c r="N17" s="22"/>
       <c r="O17" s="13"/>
     </row>
     <row r="18" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="21"/>
-      <c r="N18" s="21"/>
-      <c r="O18" s="21"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="22" t="str">
+      <c r="A19" s="26" t="str">
         <f>A11</f>
         <v>Soil</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="22" t="str">
+      <c r="B19" s="27"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="26" t="str">
         <f t="shared" ref="D19" si="0">D11</f>
         <v>Ground water</v>
       </c>
-      <c r="E19" s="23"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="22" t="str">
+      <c r="E19" s="27"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="26" t="str">
         <f t="shared" ref="G19" si="1">G11</f>
         <v>Surface water</v>
       </c>
-      <c r="H19" s="23"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="22" t="str">
+      <c r="H19" s="27"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="26" t="str">
         <f t="shared" ref="J19" si="2">J11</f>
         <v>Air</v>
       </c>
-      <c r="K19" s="23"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="22" t="str">
+      <c r="K19" s="27"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="26" t="str">
         <f t="shared" ref="M19" si="3">M11</f>
         <v>Sediment</v>
       </c>
-      <c r="N19" s="23"/>
-      <c r="O19" s="24"/>
+      <c r="N19" s="27"/>
+      <c r="O19" s="28"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
@@ -1904,61 +1904,128 @@
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="19"/>
+      <c r="B21" s="22"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="19"/>
+      <c r="E21" s="22"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="19" t="s">
+      <c r="G21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="19"/>
+      <c r="H21" s="22"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="19" t="s">
+      <c r="J21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="19"/>
+      <c r="K21" s="22"/>
       <c r="L21" s="4"/>
-      <c r="M21" s="19" t="s">
+      <c r="M21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="N21" s="19"/>
+      <c r="N21" s="22"/>
       <c r="O21" s="7"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="19"/>
+      <c r="B22" s="22"/>
       <c r="C22" s="13"/>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="19"/>
+      <c r="E22" s="22"/>
       <c r="F22" s="13"/>
-      <c r="G22" s="19" t="s">
+      <c r="G22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="H22" s="19"/>
+      <c r="H22" s="22"/>
       <c r="I22" s="13"/>
-      <c r="J22" s="19" t="s">
+      <c r="J22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="K22" s="19"/>
+      <c r="K22" s="22"/>
       <c r="L22" s="13"/>
-      <c r="M22" s="19" t="s">
+      <c r="M22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="N22" s="19"/>
+      <c r="N22" s="22"/>
       <c r="O22" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="74">
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="A6:O6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="K5:L5"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="F2:G2"/>
@@ -1966,73 +2033,6 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="K3:L3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="A6:O6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A18:O18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="M22:N22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -2057,23 +2057,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
@@ -2090,103 +2090,103 @@
       <c r="H2" s="3"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="29" t="s">
+      <c r="K2" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="29"/>
+      <c r="L2" s="21"/>
       <c r="M2" s="3"/>
       <c r="N2" s="1"/>
       <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="19"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="9"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="19"/>
+      <c r="G3" s="22"/>
       <c r="H3" s="3"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="19" t="s">
+      <c r="K3" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="19"/>
+      <c r="L3" s="22"/>
       <c r="M3" s="9"/>
       <c r="N3" s="1"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="26"/>
+      <c r="B4" s="23"/>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="26"/>
+      <c r="G4" s="23"/>
       <c r="H4" s="3"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="26" t="s">
+      <c r="K4" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="26"/>
+      <c r="L4" s="23"/>
       <c r="M4" s="9"/>
       <c r="N4" s="1"/>
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="28"/>
+      <c r="B5" s="25"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="28"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="25"/>
       <c r="H5" s="3"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="28"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="25"/>
       <c r="M5" s="9"/>
       <c r="N5" s="1"/>
       <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
-      <c r="O6" s="21"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="25"/>
+      <c r="B7" s="29"/>
       <c r="C7" s="4"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -2202,10 +2202,10 @@
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="25"/>
+      <c r="B8" s="29"/>
       <c r="C8" s="4"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -2221,10 +2221,10 @@
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="25"/>
+      <c r="B9" s="29"/>
       <c r="C9" s="13"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -2240,50 +2240,50 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
-      <c r="O10" s="21"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="22" t="s">
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="23"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="22" t="s">
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="H11" s="23"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="22" t="s">
+      <c r="H11" s="27"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="23"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="22" t="s">
+      <c r="K11" s="27"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="N11" s="23"/>
-      <c r="O11" s="24"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="28"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
@@ -2313,180 +2313,180 @@
       <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="19"/>
+      <c r="B13" s="22"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="19"/>
+      <c r="E13" s="22"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="19"/>
+      <c r="H13" s="22"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="19" t="s">
+      <c r="J13" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="K13" s="19"/>
+      <c r="K13" s="22"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="19" t="s">
+      <c r="M13" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="N13" s="19"/>
+      <c r="N13" s="22"/>
       <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="19"/>
+      <c r="B14" s="22"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="19"/>
+      <c r="E14" s="22"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="19"/>
+      <c r="H14" s="22"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="19" t="s">
+      <c r="J14" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="19"/>
+      <c r="K14" s="22"/>
       <c r="L14" s="4"/>
-      <c r="M14" s="19" t="s">
+      <c r="M14" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="19"/>
+      <c r="N14" s="22"/>
       <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="19"/>
+      <c r="B15" s="22"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="19"/>
+      <c r="E15" s="22"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="19" t="s">
+      <c r="J15" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="19"/>
+      <c r="K15" s="22"/>
       <c r="L15" s="4"/>
-      <c r="M15" s="19" t="s">
+      <c r="M15" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="N15" s="19"/>
+      <c r="N15" s="22"/>
       <c r="O15" s="7"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="19"/>
+      <c r="B16" s="22"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
       <c r="I16" s="6"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
       <c r="L16" s="5"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
       <c r="O16" s="8"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="19"/>
+      <c r="B17" s="22"/>
       <c r="C17" s="13"/>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="19"/>
+      <c r="E17" s="22"/>
       <c r="F17" s="13"/>
-      <c r="G17" s="19" t="s">
+      <c r="G17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="19"/>
+      <c r="H17" s="22"/>
       <c r="I17" s="13"/>
-      <c r="J17" s="19" t="s">
+      <c r="J17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="K17" s="19"/>
+      <c r="K17" s="22"/>
       <c r="L17" s="13"/>
-      <c r="M17" s="19" t="s">
+      <c r="M17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="N17" s="19"/>
+      <c r="N17" s="22"/>
       <c r="O17" s="13"/>
     </row>
     <row r="18" spans="1:15" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="21"/>
-      <c r="N18" s="21"/>
-      <c r="O18" s="21"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="22" t="str">
+      <c r="A19" s="26" t="str">
         <f>A11</f>
         <v>Soil</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="22" t="str">
+      <c r="B19" s="27"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="26" t="str">
         <f t="shared" ref="D19" si="0">D11</f>
         <v>Ground water</v>
       </c>
-      <c r="E19" s="23"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="22" t="str">
+      <c r="E19" s="27"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="26" t="str">
         <f t="shared" ref="G19" si="1">G11</f>
         <v>Surface water</v>
       </c>
-      <c r="H19" s="23"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="22" t="str">
+      <c r="H19" s="27"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="26" t="str">
         <f t="shared" ref="J19" si="2">J11</f>
         <v>Air</v>
       </c>
-      <c r="K19" s="23"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="22" t="str">
+      <c r="K19" s="27"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="26" t="str">
         <f t="shared" ref="M19" si="3">M11</f>
         <v>Sediment</v>
       </c>
-      <c r="N19" s="23"/>
-      <c r="O19" s="24"/>
+      <c r="N19" s="27"/>
+      <c r="O19" s="28"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
@@ -2516,61 +2516,119 @@
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="19"/>
+      <c r="B21" s="22"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="19"/>
+      <c r="E21" s="22"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="19" t="s">
+      <c r="G21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="19"/>
+      <c r="H21" s="22"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="19" t="s">
+      <c r="J21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="19"/>
+      <c r="K21" s="22"/>
       <c r="L21" s="4"/>
-      <c r="M21" s="19" t="s">
+      <c r="M21" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="N21" s="19"/>
+      <c r="N21" s="22"/>
       <c r="O21" s="7"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="19"/>
+      <c r="B22" s="22"/>
       <c r="C22" s="13"/>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="19"/>
+      <c r="E22" s="22"/>
       <c r="F22" s="13"/>
-      <c r="G22" s="19" t="s">
+      <c r="G22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="H22" s="19"/>
+      <c r="H22" s="22"/>
       <c r="I22" s="13"/>
-      <c r="J22" s="19" t="s">
+      <c r="J22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="K22" s="19"/>
+      <c r="K22" s="22"/>
       <c r="L22" s="13"/>
-      <c r="M22" s="19" t="s">
+      <c r="M22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="N22" s="19"/>
+      <c r="N22" s="22"/>
       <c r="O22" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="74">
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A6:O6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="M11:O11"/>
@@ -2587,64 +2645,6 @@
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="D13:E13"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A6:O6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="A18:O18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="D17:E17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -2665,11 +2665,10 @@
   <dimension ref="A1:E400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="18" customWidth="1"/>
+    <col min="3" max="4" width="20.7109375" style="16" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" style="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
